--- a/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
+++ b/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
@@ -249,9 +249,6 @@
     <t>Flytgödsel</t>
   </si>
   <si>
-    <t>MachineryAndEnergyMgmt_field_operations.csv</t>
-  </si>
-  <si>
     <t>field_operations</t>
   </si>
   <si>
@@ -659,6 +656,9 @@
   </si>
   <si>
     <t>biodiesel</t>
+  </si>
+  <si>
+    <t>MachineryAndEnergyMgmt-field_operations.csv</t>
   </si>
 </sst>
 </file>
@@ -1126,22 +1126,22 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>44</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>1</v>
@@ -1161,92 +1161,92 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G2" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H2" s="9">
         <v>0</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
       <c r="I4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H5" s="18">
         <f>100-H4</f>
         <v>2.8839238995413581</v>
       </c>
       <c r="I5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H7" s="10">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1256,161 +1256,161 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H9" s="11">
         <v>6.4777062142923141</v>
       </c>
       <c r="I9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H10" s="11">
         <v>8.7567853491111922</v>
       </c>
       <c r="I10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H11" s="18">
         <v>59.671114354829328</v>
       </c>
       <c r="I11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H12" s="18">
         <v>16.802918820320372</v>
       </c>
       <c r="I12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H13" s="11">
         <v>7.4851294970113242</v>
       </c>
       <c r="I13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="H14" s="11">
         <v>0.80634576443547301</v>
       </c>
       <c r="I14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H16" s="15">
         <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H17" s="15">
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H18" s="15">
         <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1488,13 +1488,13 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J24" s="7"/>
     </row>
@@ -1562,14 +1562,14 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="9">
         <v>1</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="18" x14ac:dyDescent="0.35">
@@ -1581,67 +1581,67 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29">
         <v>0.26</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H30">
         <v>0.26</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H31">
         <v>0.45</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B32" s="4"/>
       <c r="C32" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32">
         <v>0.76</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -1680,7 +1680,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H36">
         <v>4</v>
@@ -1794,123 +1794,123 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G46" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J46" s="9"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G47" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J47" s="9"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G48" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J48" s="9"/>
     </row>
     <row r="49" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G49" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J49" s="9"/>
     </row>
     <row r="50" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G50" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J50" s="9"/>
     </row>
     <row r="51" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G51" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H51" s="9">
         <v>1</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G52" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J52" s="9"/>
     </row>
     <row r="53" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G53" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J53" s="9"/>
     </row>
     <row r="54" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G54" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J54" s="9"/>
     </row>
     <row r="55" spans="4:11" x14ac:dyDescent="0.25">
       <c r="G55" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J55" s="9"/>
     </row>
@@ -1922,26 +1922,26 @@
     </row>
     <row r="57" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H57" s="10">
         <v>364</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K57" s="10"/>
     </row>
     <row r="58" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H58" s="10">
         <v>18.8</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="59" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H59" s="10">
         <v>0</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="60" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H60" s="10">
         <v>10</v>
@@ -1980,13 +1980,13 @@
     </row>
     <row r="61" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H61" s="12">
         <v>1</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="62" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H62" s="10">
         <v>0.88</v>
@@ -2014,13 +2014,13 @@
     </row>
     <row r="63" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H63" s="10">
         <v>0.78</v>
@@ -2038,26 +2038,26 @@
     </row>
     <row r="65" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H65" s="10">
         <v>652</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K65" s="10"/>
     </row>
     <row r="66" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H66" s="10">
         <v>0</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="67" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H67" s="10">
         <v>5.0999999999999996</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="68" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H68" s="10">
         <v>20</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="69" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H69" s="12">
         <v>1</v>
@@ -2113,13 +2113,13 @@
     </row>
     <row r="70" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H70" s="12">
         <v>0.7</v>
@@ -2130,13 +2130,13 @@
     </row>
     <row r="71" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H71" s="10">
         <v>0.45</v>
@@ -2154,26 +2154,26 @@
     </row>
     <row r="73" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H73" s="10">
         <v>46</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K73" s="10"/>
     </row>
     <row r="74" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H74" s="10">
         <v>2.8</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="75" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H75" s="10">
         <v>0</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="76" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H76" s="10">
         <v>5</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="77" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H77" s="12">
         <v>1</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="78" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H78" s="10">
         <v>0.85</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="79" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E79" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H79" s="10">
         <v>0.65</v>
@@ -2270,38 +2270,38 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H81" s="12">
         <v>5.0999999999999996</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H82" s="12">
         <v>7.1</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K82" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
@@ -2313,46 +2313,46 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H84" s="12">
         <v>3.7353333333333332</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K84" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H85" s="11">
         <v>17.096931944444446</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K85" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H86" s="12">
         <v>1.2451111111111113</v>
@@ -2362,15 +2362,15 @@
         <v>47</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H87" s="12">
         <v>3.1127777777777781</v>
@@ -2380,233 +2380,233 @@
         <v>48</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H88" s="12">
         <v>4.6691666666666665</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K88" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D89" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H89" s="12">
         <v>3.1127777777777781</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H90" s="11">
         <v>11.828555555555555</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K90" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H91" s="11">
         <v>26.302972222222223</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K91" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H92" s="11">
         <v>11.3</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K92" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="K92" s="10" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H93" s="11">
         <v>23.278130416666666</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H94" s="10">
         <v>13.15</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K94" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D95" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H95" s="10">
         <v>5.26</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H96" s="12">
         <v>1.7546281240590185</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K96" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D97" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H97" s="12">
         <v>5.1828516694033944</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H98" s="13">
         <v>4.0531064740502947</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H99" s="13">
         <v>4.3591310772039646</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -2617,71 +2617,71 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H101" s="13">
         <v>14.6</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F102" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H102" s="13">
         <v>37.744765138888887</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H103" s="13">
         <v>50.107162083333336</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D104" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F104" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H104" s="13">
         <v>36.955675972222224</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -2692,58 +2692,58 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H106" s="13">
         <v>1.6176327916666666</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H107" s="13">
         <v>3.0774477499999997</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H108" s="13">
         <v>0.25</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -2758,26 +2758,26 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G111" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H111" s="9">
         <v>0</v>
       </c>
       <c r="J111" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G112" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H112" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -2792,144 +2792,144 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G115" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H115" s="9">
         <v>0</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J115" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G116" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H116">
         <v>302</v>
       </c>
       <c r="I116" t="s">
+        <v>169</v>
+      </c>
+      <c r="J116" t="s">
         <v>170</v>
       </c>
-      <c r="J116" t="s">
-        <v>171</v>
-      </c>
       <c r="K116" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G117" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H117">
         <v>197</v>
       </c>
       <c r="I117" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J117" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K117" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G118" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H118">
         <v>216</v>
       </c>
       <c r="I118" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J118" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G119" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H119">
         <v>216</v>
       </c>
       <c r="I119" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J119" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G120" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H120">
         <v>216</v>
       </c>
       <c r="I120" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J120" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G121" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H121">
         <v>216</v>
       </c>
       <c r="I121" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J121" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
+        <v>167</v>
+      </c>
+      <c r="G122" t="s">
         <v>168</v>
-      </c>
-      <c r="G122" t="s">
-        <v>169</v>
       </c>
       <c r="H122">
         <v>216</v>
       </c>
       <c r="I122" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J122" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2945,52 +2945,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
+++ b/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18240" windowHeight="10650"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="201">
   <si>
     <t>f_crop</t>
   </si>
@@ -660,15 +660,85 @@
   <si>
     <t>MachineryAndEnergyMgmt-field_operations.csv</t>
   </si>
+  <si>
+    <t>f_compound</t>
+  </si>
+  <si>
+    <t>combustion_EF</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>N2O</t>
+  </si>
+  <si>
+    <r>
+      <t>Fuel combustion emission factors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (add non-GHG compunds?)</t>
+    </r>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2006. Chapter 3, Table 3.2.1</t>
+  </si>
+  <si>
+    <t>Gas/ Diesel Oil</t>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2006. Chapter 3, Table 3.2.2</t>
+  </si>
+  <si>
+    <t>assume same as diesel</t>
+  </si>
+  <si>
+    <t>no emissions?</t>
+  </si>
+  <si>
+    <t>CH4fos</t>
+  </si>
+  <si>
+    <t>CH4bio</t>
+  </si>
+  <si>
+    <t>kg/TJ</t>
+  </si>
+  <si>
+    <t>Wood / Wood Waste</t>
+  </si>
+  <si>
+    <t>Natural Gas</t>
+  </si>
+  <si>
+    <t>Crude Oil</t>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2006. Chapter 2, Table 2.5</t>
+  </si>
+  <si>
+    <t>grain drying</t>
+  </si>
+  <si>
+    <t>Fallback</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -740,6 +810,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -810,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -833,6 +910,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,18 +1195,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="31.7109375" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="3" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="31.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>152</v>
       </c>
@@ -1144,1791 +1226,2326 @@
         <v>129</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G2" s="20" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H2" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="18">
+      <c r="I4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>128</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H5" s="18">
-        <f>100-H4</f>
+      <c r="I5" s="18">
+        <f>100-I4</f>
         <v>2.8839238995413581</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>128</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>153</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="10">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H7" s="10">
+      <c r="I7" s="10">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H8" s="6"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>159</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="11">
         <v>6.4777062142923141</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>128</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>159</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="11">
         <v>8.7567853491111922</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>128</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>176</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>159</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H11" s="18">
+      <c r="I11" s="18">
         <v>59.671114354829328</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>128</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="K11" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>159</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H12" s="18">
+      <c r="I12" s="18">
         <v>16.802918820320372</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>159</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H13" s="11">
+      <c r="I13" s="11">
         <v>7.4851294970113242</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>159</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H14" s="11">
+      <c r="I14" s="11">
         <v>0.80634576443547301</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
         <v>121</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="15">
+      <c r="I16" s="15">
         <v>80</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
         <v>122</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>130</v>
       </c>
-      <c r="H17" s="15">
+      <c r="I17" s="15">
         <v>10</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
         <v>123</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="15">
+      <c r="I18" s="15">
         <v>10</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C20" s="4"/>
+      <c r="H20" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="26">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C21" s="4"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" t="s">
+        <v>183</v>
+      </c>
+      <c r="I22" s="18">
+        <f>74100</f>
+        <v>74100</v>
+      </c>
+      <c r="J22" t="s">
+        <v>194</v>
+      </c>
+      <c r="K22" t="s">
+        <v>188</v>
+      </c>
+      <c r="L22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" t="s">
+        <v>192</v>
+      </c>
+      <c r="H23" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="11">
+        <f>3.9</f>
+        <v>3.9</v>
+      </c>
+      <c r="J23" t="s">
+        <v>194</v>
+      </c>
+      <c r="L23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="11">
+        <f>3.9</f>
+        <v>3.9</v>
+      </c>
+      <c r="J24" t="s">
+        <v>194</v>
+      </c>
+      <c r="L24" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" t="s">
+        <v>184</v>
+      </c>
+      <c r="H25" t="s">
+        <v>183</v>
+      </c>
+      <c r="I25" s="18">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" t="s">
+        <v>183</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" ref="I26:I27" si="0">I23</f>
+        <v>3.9</v>
+      </c>
+      <c r="J26" t="s">
+        <v>194</v>
+      </c>
+      <c r="K26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" t="s">
+        <v>183</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>3.9</v>
+      </c>
+      <c r="J27" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H28" t="s">
+        <v>183</v>
+      </c>
+      <c r="I28" s="18">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" t="s">
+        <v>183</v>
+      </c>
+      <c r="I29" s="18">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>194</v>
+      </c>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="4"/>
+      <c r="I30" s="22"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" t="s">
+        <v>184</v>
+      </c>
+      <c r="H31" t="s">
+        <v>183</v>
+      </c>
+      <c r="I31" s="18">
+        <v>73300</v>
+      </c>
+      <c r="J31" t="s">
+        <v>194</v>
+      </c>
+      <c r="K31" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+      <c r="J32" t="s">
+        <v>194</v>
+      </c>
+      <c r="L32" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" t="s">
+        <v>183</v>
+      </c>
+      <c r="I33">
+        <v>0.6</v>
+      </c>
+      <c r="J33" t="s">
+        <v>194</v>
+      </c>
+      <c r="L33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" t="s">
+        <v>183</v>
+      </c>
+      <c r="I34" s="18">
+        <v>56100</v>
+      </c>
+      <c r="J34" t="s">
+        <v>194</v>
+      </c>
+      <c r="K34" t="s">
+        <v>196</v>
+      </c>
+      <c r="L34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G35" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35" t="s">
+        <v>183</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35" t="s">
+        <v>194</v>
+      </c>
+      <c r="L35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" t="s">
+        <v>185</v>
+      </c>
+      <c r="H36" t="s">
+        <v>183</v>
+      </c>
+      <c r="I36">
+        <v>0.1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>194</v>
+      </c>
+      <c r="L36" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G37" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" t="s">
+        <v>183</v>
+      </c>
+      <c r="I37" s="18">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>194</v>
+      </c>
+      <c r="K37" t="s">
+        <v>195</v>
+      </c>
+      <c r="L37" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G38" t="s">
+        <v>193</v>
+      </c>
+      <c r="H38" t="s">
+        <v>183</v>
+      </c>
+      <c r="I38" s="18">
+        <v>300</v>
+      </c>
+      <c r="J38" t="s">
+        <v>194</v>
+      </c>
+      <c r="L38" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" t="s">
+        <v>183</v>
+      </c>
+      <c r="I39" s="18">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>194</v>
+      </c>
+      <c r="L39" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="18">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>194</v>
+      </c>
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H41" t="s">
+        <v>183</v>
+      </c>
+      <c r="I41" s="18">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>194</v>
+      </c>
+      <c r="K41" s="15"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H42" t="s">
+        <v>183</v>
+      </c>
+      <c r="I42" s="18">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>194</v>
+      </c>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="6"/>
+      <c r="I43" s="18"/>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="I44" s="25">
+        <v>0</v>
+      </c>
+      <c r="K44" s="15"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I45" s="22"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H22">
+      <c r="I48">
         <v>10800</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J48" t="s">
         <v>11</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="K48" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4" t="s">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H23">
+      <c r="I49">
         <v>5</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J49" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="K49" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6" t="s">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="H24">
+      <c r="I50">
         <v>2</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J50" t="s">
         <v>126</v>
       </c>
-      <c r="J24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H25">
+      <c r="I51">
         <v>0.2</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J51" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="K51" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H26">
+      <c r="I52">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J52" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="K52" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="6" t="s">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H27">
+      <c r="I53">
         <v>250</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J53" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="K53" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="20" t="s">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="H28" s="9">
+      <c r="I54" s="9">
         <v>1</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="21" t="s">
+      <c r="J54" s="9"/>
+      <c r="K54" s="21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4" t="s">
+    <row r="55" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="B55" s="4"/>
+      <c r="C55" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="6" t="s">
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H29">
+      <c r="I55">
         <v>0.26</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4" t="s">
+    <row r="56" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="B56" s="4"/>
+      <c r="C56" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="6" t="s">
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H30">
+      <c r="I56">
         <v>0.26</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="K56" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4" t="s">
+    <row r="57" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6" t="s">
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H31">
+      <c r="I57">
         <v>0.45</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="K57" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="B32" s="4"/>
-      <c r="C32" s="6" t="s">
+    <row r="58" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="B58" s="4"/>
+      <c r="C58" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6" t="s">
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H32">
+      <c r="I58">
         <v>0.76</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="K58" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H33">
+      <c r="I59">
         <v>4</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J59" t="s">
         <v>21</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="K59" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G36" t="s">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H62" t="s">
         <v>127</v>
       </c>
-      <c r="H36">
+      <c r="I62">
         <v>4</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J62" t="s">
         <v>29</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K62" t="s">
         <v>28</v>
       </c>
-      <c r="O36" s="6"/>
-    </row>
-    <row r="37" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="G37" t="s">
+      <c r="P62" s="6"/>
+    </row>
+    <row r="63" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H63" t="s">
         <v>45</v>
       </c>
-      <c r="H37">
+      <c r="I63">
         <v>0.9</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K63" t="s">
         <v>30</v>
       </c>
-      <c r="O37" s="6"/>
-    </row>
-    <row r="38" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="G38" t="s">
+      <c r="P63" s="6"/>
+    </row>
+    <row r="64" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H64" t="s">
         <v>38</v>
       </c>
-      <c r="H38">
+      <c r="I64">
         <v>1.2250000000000001</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J64" t="s">
         <v>32</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K64" t="s">
         <v>31</v>
       </c>
-      <c r="O38" s="6"/>
-    </row>
-    <row r="39" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="G39" t="s">
+      <c r="P64" s="6"/>
+    </row>
+    <row r="65" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H65" t="s">
         <v>39</v>
       </c>
-      <c r="H39">
+      <c r="I65">
         <v>0.1</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K65" t="s">
         <v>33</v>
       </c>
-      <c r="O39" s="6"/>
-    </row>
-    <row r="40" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="G40" t="s">
+      <c r="P65" s="6"/>
+    </row>
+    <row r="66" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H66" t="s">
         <v>40</v>
       </c>
-      <c r="H40">
+      <c r="I66">
         <v>0.01</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K66" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G41" t="s">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H67" t="s">
         <v>41</v>
       </c>
-      <c r="H41">
+      <c r="I67">
         <v>0.2</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K67" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="G42" t="s">
+    <row r="68" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H68" t="s">
         <v>42</v>
       </c>
-      <c r="H42">
+      <c r="I68">
         <v>0.8</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K68" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="G43" t="s">
+    <row r="69" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H69" t="s">
         <v>43</v>
       </c>
-      <c r="H43">
+      <c r="I69">
         <v>55</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K69" t="s">
         <v>37</v>
       </c>
-      <c r="N43" s="4"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="O69" s="4"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G46" s="9" t="s">
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H72" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H46" s="9">
+      <c r="I72" s="9">
         <v>0</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="J72" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="J46" s="9"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G47" s="9" t="s">
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H73" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H47" s="9">
+      <c r="I73" s="9">
         <v>0</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="J73" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="J47" s="9"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G48" s="9" t="s">
+      <c r="K73" s="9"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H74" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H48" s="9">
+      <c r="I74" s="9">
         <v>0</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="J74" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="J48" s="9"/>
-    </row>
-    <row r="49" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G49" s="9" t="s">
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H75" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H49" s="9">
+      <c r="I75" s="9">
         <v>0</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="J75" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="J49" s="9"/>
-    </row>
-    <row r="50" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G50" s="9" t="s">
+      <c r="K75" s="9"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H76" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H50" s="9">
+      <c r="I76" s="9">
         <v>0</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="J76" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J50" s="9"/>
-    </row>
-    <row r="51" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G51" s="9" t="s">
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H77" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H51" s="9">
+      <c r="I77" s="9">
         <v>1</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="J77" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="K77" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G52" s="9" t="s">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H78" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H52" s="9">
+      <c r="I78" s="9">
         <v>0</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="J78" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="J52" s="9"/>
-    </row>
-    <row r="53" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G53" s="9" t="s">
+      <c r="K78" s="9"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H79" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H53" s="9">
+      <c r="I79" s="9">
         <v>0</v>
       </c>
-      <c r="I53" s="9" t="s">
+      <c r="J79" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="J53" s="9"/>
-    </row>
-    <row r="54" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G54" s="9" t="s">
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H80" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="H54" s="9">
+      <c r="I80" s="9">
         <v>0</v>
       </c>
-      <c r="I54" s="9" t="s">
+      <c r="J80" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="J54" s="9"/>
-    </row>
-    <row r="55" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G55" s="9" t="s">
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H81" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H55" s="9">
+      <c r="I81" s="9">
         <v>0</v>
       </c>
-      <c r="I55" s="9" t="s">
+      <c r="J81" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="J55" s="9"/>
-    </row>
-    <row r="56" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-    </row>
-    <row r="57" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D57" t="s">
+      <c r="K81" s="9"/>
+    </row>
+    <row r="82" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+    </row>
+    <row r="83" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
         <v>60</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="H83" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H57" s="10">
+      <c r="I83" s="10">
         <v>364</v>
       </c>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10" t="s">
+      <c r="J83" s="10"/>
+      <c r="K83" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K57" s="10"/>
-    </row>
-    <row r="58" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D58" t="s">
+      <c r="L83" s="10"/>
+    </row>
+    <row r="84" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
         <v>60</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="H84" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H58" s="10">
+      <c r="I84" s="10">
         <v>18.8</v>
       </c>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-    </row>
-    <row r="59" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D59" t="s">
+      <c r="J84" s="10"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="10"/>
+    </row>
+    <row r="85" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
         <v>60</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H59" s="10">
+      <c r="I85" s="10">
         <v>0</v>
       </c>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-    </row>
-    <row r="60" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D60" t="s">
+      <c r="J85" s="10"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="10"/>
+    </row>
+    <row r="86" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
         <v>60</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="H86" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H60" s="10">
+      <c r="I86" s="10">
         <v>10</v>
       </c>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-    </row>
-    <row r="61" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D61" t="s">
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="10"/>
+    </row>
+    <row r="87" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
         <v>60</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E87" t="s">
         <v>74</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="H87" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H61" s="12">
+      <c r="I87" s="12">
         <v>1</v>
       </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-    </row>
-    <row r="62" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D62" t="s">
+      <c r="J87" s="10"/>
+      <c r="K87" s="10"/>
+      <c r="L87" s="10"/>
+    </row>
+    <row r="88" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
         <v>60</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E88" t="s">
         <v>73</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="H88" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H62" s="10">
+      <c r="I88" s="10">
         <v>0.88</v>
       </c>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-    </row>
-    <row r="63" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D63" t="s">
+      <c r="J88" s="10"/>
+      <c r="K88" s="10"/>
+      <c r="L88" s="10"/>
+    </row>
+    <row r="89" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
         <v>60</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E89" t="s">
         <v>72</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="H89" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H63" s="10">
+      <c r="I89" s="10">
         <v>0.78</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-    </row>
-    <row r="64" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-    </row>
-    <row r="65" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D65" t="s">
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10"/>
+    </row>
+    <row r="90" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H90" s="10"/>
+      <c r="I90" s="10"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="10"/>
+      <c r="L90" s="10"/>
+    </row>
+    <row r="91" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
         <v>63</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="H91" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H65" s="10">
+      <c r="I91" s="10">
         <v>652</v>
       </c>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10" t="s">
+      <c r="J91" s="10"/>
+      <c r="K91" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="K65" s="10"/>
-    </row>
-    <row r="66" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D66" t="s">
+      <c r="L91" s="10"/>
+    </row>
+    <row r="92" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
         <v>63</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="H92" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H66" s="10">
+      <c r="I92" s="10">
         <v>0</v>
       </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-    </row>
-    <row r="67" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D67" t="s">
+      <c r="J92" s="10"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="10"/>
+    </row>
+    <row r="93" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
         <v>63</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="H93" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H67" s="10">
+      <c r="I93" s="10">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-    </row>
-    <row r="68" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D68" t="s">
+      <c r="J93" s="10"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="10"/>
+    </row>
+    <row r="94" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
         <v>63</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="H94" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H68" s="10">
+      <c r="I94" s="10">
         <v>20</v>
       </c>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-    </row>
-    <row r="69" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D69" t="s">
+      <c r="J94" s="10"/>
+      <c r="K94" s="10"/>
+      <c r="L94" s="10"/>
+    </row>
+    <row r="95" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
         <v>63</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E95" t="s">
         <v>74</v>
       </c>
-      <c r="G69" s="10" t="s">
+      <c r="H95" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H69" s="12">
+      <c r="I95" s="12">
         <v>1</v>
       </c>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-    </row>
-    <row r="70" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D70" t="s">
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+    </row>
+    <row r="96" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
         <v>63</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E96" t="s">
         <v>73</v>
       </c>
-      <c r="G70" s="10" t="s">
+      <c r="H96" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H70" s="12">
+      <c r="I96" s="12">
         <v>0.7</v>
       </c>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-    </row>
-    <row r="71" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D71" t="s">
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
+    </row>
+    <row r="97" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
         <v>63</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E97" t="s">
         <v>72</v>
       </c>
-      <c r="G71" s="10" t="s">
+      <c r="H97" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H71" s="10">
+      <c r="I97" s="10">
         <v>0.45</v>
       </c>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-    </row>
-    <row r="72" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-    </row>
-    <row r="73" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D73" t="s">
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="10"/>
+    </row>
+    <row r="98" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H98" s="10"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="10"/>
+      <c r="K98" s="10"/>
+      <c r="L98" s="10"/>
+    </row>
+    <row r="99" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
         <v>62</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="H99" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H73" s="10">
+      <c r="I99" s="10">
         <v>46</v>
       </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10" t="s">
+      <c r="J99" s="10"/>
+      <c r="K99" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="K73" s="10"/>
-    </row>
-    <row r="74" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D74" t="s">
+      <c r="L99" s="10"/>
+    </row>
+    <row r="100" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
         <v>62</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="H100" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H74" s="10">
+      <c r="I100" s="10">
         <v>2.8</v>
       </c>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-    </row>
-    <row r="75" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D75" t="s">
+      <c r="J100" s="10"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="10"/>
+    </row>
+    <row r="101" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
         <v>62</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="H101" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H75" s="10">
+      <c r="I101" s="10">
         <v>0</v>
       </c>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-    </row>
-    <row r="76" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D76" t="s">
+      <c r="J101" s="10"/>
+      <c r="K101" s="10"/>
+      <c r="L101" s="10"/>
+    </row>
+    <row r="102" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
         <v>62</v>
       </c>
-      <c r="G76" s="10" t="s">
+      <c r="H102" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="10">
+      <c r="I102" s="10">
         <v>5</v>
       </c>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-    </row>
-    <row r="77" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D77" t="s">
+      <c r="J102" s="10"/>
+      <c r="K102" s="10"/>
+      <c r="L102" s="10"/>
+    </row>
+    <row r="103" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
         <v>62</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E103" t="s">
         <v>74</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="H103" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H77" s="12">
+      <c r="I103" s="12">
         <v>1</v>
       </c>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-    </row>
-    <row r="78" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D78" t="s">
+      <c r="J103" s="10"/>
+      <c r="K103" s="10"/>
+      <c r="L103" s="10"/>
+    </row>
+    <row r="104" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
         <v>62</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E104" t="s">
         <v>73</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="H104" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H78" s="10">
+      <c r="I104" s="10">
         <v>0.85</v>
       </c>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-    </row>
-    <row r="79" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D79" t="s">
+      <c r="J104" s="10"/>
+      <c r="K104" s="10"/>
+      <c r="L104" s="10"/>
+    </row>
+    <row r="105" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
         <v>62</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E105" t="s">
         <v>72</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="H105" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H79" s="10">
+      <c r="I105" s="10">
         <v>0.65</v>
       </c>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-    </row>
-    <row r="80" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D81" t="s">
+      <c r="J105" s="10"/>
+      <c r="K105" s="10"/>
+      <c r="L105" s="10"/>
+    </row>
+    <row r="106" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H106" s="10"/>
+      <c r="I106" s="10"/>
+      <c r="J106" s="10"/>
+      <c r="K106" s="10"/>
+      <c r="L106" s="10"/>
+    </row>
+    <row r="107" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
         <v>65</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="H107" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="H81" s="12">
+      <c r="I107" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I81" s="10"/>
-      <c r="J81" s="6" t="s">
+      <c r="J107" s="10"/>
+      <c r="K107" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K81" s="4" t="s">
+      <c r="L107" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D82" t="s">
+    <row r="108" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
         <v>66</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="H108" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="H82" s="12">
+      <c r="I108" s="12">
         <v>7.1</v>
       </c>
-      <c r="I82" s="10"/>
-      <c r="J82" s="6" t="s">
+      <c r="J108" s="10"/>
+      <c r="K108" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="K82" s="4" t="s">
+      <c r="L108" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D84" t="s">
+    <row r="109" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H109" s="10"/>
+      <c r="I109" s="10"/>
+      <c r="J109" s="10"/>
+      <c r="K109" s="10"/>
+      <c r="L109" s="10"/>
+    </row>
+    <row r="110" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
         <v>61</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="H110" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H84" s="12">
+      <c r="I110" s="12">
         <v>3.7353333333333332</v>
       </c>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10" t="s">
+      <c r="J110" s="10"/>
+      <c r="K110" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="K84" s="6" t="s">
+      <c r="L110" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D85" t="s">
+    <row r="111" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
         <v>64</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H111" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H85" s="11">
+      <c r="I111" s="11">
         <v>17.096931944444446</v>
       </c>
-      <c r="I85" s="10"/>
-      <c r="J85" s="6" t="s">
+      <c r="J111" s="10"/>
+      <c r="K111" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K85" s="4" t="s">
+      <c r="L111" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D86" t="s">
+    <row r="112" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
         <v>67</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="H112" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H86" s="12">
+      <c r="I112" s="12">
         <v>1.2451111111111113</v>
       </c>
-      <c r="I86" s="10"/>
-      <c r="J86" s="6" t="s">
+      <c r="J112" s="10"/>
+      <c r="K112" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="K86" s="10" t="s">
+      <c r="L112" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D87" t="s">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
         <v>68</v>
       </c>
-      <c r="G87" s="10" t="s">
+      <c r="H113" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H87" s="12">
+      <c r="I113" s="12">
         <v>3.1127777777777781</v>
       </c>
-      <c r="I87" s="10"/>
-      <c r="J87" s="6" t="s">
+      <c r="J113" s="10"/>
+      <c r="K113" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K87" s="10" t="s">
+      <c r="L113" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D88" t="s">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
         <v>97</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="H114" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H88" s="12">
+      <c r="I114" s="12">
         <v>4.6691666666666665</v>
       </c>
-      <c r="I88" s="10"/>
-      <c r="J88" s="4" t="s">
+      <c r="J114" s="10"/>
+      <c r="K114" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K88" s="10" t="s">
+      <c r="L114" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D89" t="s">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
         <v>69</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="H115" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H89" s="12">
+      <c r="I115" s="12">
         <v>3.1127777777777781</v>
       </c>
-      <c r="I89" s="10"/>
-      <c r="J89" s="4" t="s">
+      <c r="J115" s="10"/>
+      <c r="K115" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="K89" s="6" t="s">
+      <c r="L115" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D90" t="s">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
         <v>70</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="H116" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H90" s="11">
+      <c r="I116" s="11">
         <v>11.828555555555555</v>
       </c>
-      <c r="I90" s="10"/>
-      <c r="J90" s="4" t="s">
+      <c r="J116" s="10"/>
+      <c r="K116" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="K90" s="10" t="s">
+      <c r="L116" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D91" t="s">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
         <v>100</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="H117" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H91" s="11">
+      <c r="I117" s="11">
         <v>26.302972222222223</v>
       </c>
-      <c r="I91" s="10"/>
-      <c r="J91" s="6" t="s">
+      <c r="J117" s="10"/>
+      <c r="K117" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K91" s="10" t="s">
+      <c r="L117" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D92" t="s">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
         <v>101</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="H118" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H92" s="11">
+      <c r="I118" s="11">
         <v>11.3</v>
       </c>
-      <c r="I92" s="10"/>
-      <c r="J92" s="6" t="s">
+      <c r="J118" s="10"/>
+      <c r="K118" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K92" s="10" t="s">
+      <c r="L118" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D93" t="s">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
         <v>102</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="H119" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H93" s="11">
+      <c r="I119" s="11">
         <v>23.278130416666666</v>
       </c>
-      <c r="I93" s="10"/>
-      <c r="J93" s="6" t="s">
+      <c r="J119" s="10"/>
+      <c r="K119" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="K93" s="10" t="s">
+      <c r="L119" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D94" t="s">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
         <v>71</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="H120" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H94" s="10">
+      <c r="I120" s="10">
         <v>13.15</v>
       </c>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10" t="s">
+      <c r="J120" s="10"/>
+      <c r="K120" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K94" s="10" t="s">
+      <c r="L120" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D95" t="s">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
         <v>71</v>
       </c>
-      <c r="G95" s="10" t="s">
+      <c r="H121" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H95" s="10">
+      <c r="I121" s="10">
         <v>5.26</v>
       </c>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10" t="s">
+      <c r="J121" s="10"/>
+      <c r="K121" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K95" s="10" t="s">
+      <c r="L121" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
         <v>110</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D122" t="s">
         <v>71</v>
       </c>
-      <c r="G96" s="10" t="s">
+      <c r="H122" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H96" s="12">
+      <c r="I122" s="12">
         <v>1.7546281240590185</v>
       </c>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10" t="s">
+      <c r="J122" s="10"/>
+      <c r="K122" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K96" s="4" t="s">
+      <c r="L122" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
         <v>113</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D123" t="s">
         <v>71</v>
       </c>
-      <c r="G97" s="10" t="s">
+      <c r="H123" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H97" s="12">
+      <c r="I123" s="12">
         <v>5.1828516694033944</v>
       </c>
-      <c r="I97" s="10"/>
-      <c r="J97" s="6" t="s">
+      <c r="J123" s="10"/>
+      <c r="K123" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="K97" s="4" t="s">
+      <c r="L123" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
         <v>114</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D124" t="s">
         <v>71</v>
       </c>
-      <c r="G98" s="10" t="s">
+      <c r="H124" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H98" s="13">
+      <c r="I124" s="13">
         <v>4.0531064740502947</v>
       </c>
-      <c r="J98" s="6" t="s">
+      <c r="K124" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="K98" s="4" t="s">
+      <c r="L124" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
         <v>118</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D125" t="s">
         <v>71</v>
       </c>
-      <c r="G99" s="10" t="s">
+      <c r="H125" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H99" s="13">
+      <c r="I125" s="13">
         <v>4.3591310772039646</v>
       </c>
-      <c r="J99" s="6" t="s">
+      <c r="K125" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K99" s="6" t="s">
+      <c r="L125" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G100" s="10"/>
-      <c r="H100" s="13"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D101" t="s">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="H126" s="10"/>
+      <c r="I126" s="13"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+    </row>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
         <v>120</v>
       </c>
-      <c r="G101" s="10" t="s">
+      <c r="H127" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H101" s="13">
+      <c r="I127" s="13">
         <v>14.6</v>
       </c>
-      <c r="J101" s="6"/>
-      <c r="K101" s="4" t="s">
+      <c r="K127" s="6"/>
+      <c r="L127" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D102" t="s">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
         <v>124</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F128" t="s">
         <v>121</v>
       </c>
-      <c r="G102" s="10" t="s">
+      <c r="H128" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H102" s="13">
+      <c r="I128" s="13">
         <v>37.744765138888887</v>
       </c>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6" t="s">
+      <c r="K128" s="6"/>
+      <c r="L128" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D103" t="s">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
         <v>124</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F129" t="s">
         <v>122</v>
       </c>
-      <c r="G103" s="10" t="s">
+      <c r="H129" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H103" s="13">
+      <c r="I129" s="13">
         <v>50.107162083333336</v>
       </c>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6" t="s">
+      <c r="K129" s="6"/>
+      <c r="L129" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D104" t="s">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
         <v>124</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F130" t="s">
         <v>123</v>
       </c>
-      <c r="G104" s="10" t="s">
+      <c r="H130" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H104" s="13">
+      <c r="I130" s="13">
         <v>36.955675972222224</v>
       </c>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6" t="s">
+      <c r="K130" s="6"/>
+      <c r="L130" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G105" s="10"/>
-      <c r="H105" s="13"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D106" t="s">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H131" s="10"/>
+      <c r="I131" s="13"/>
+      <c r="K131" s="6"/>
+      <c r="L131" s="6"/>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
         <v>131</v>
       </c>
-      <c r="G106" s="10" t="s">
+      <c r="H132" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H106" s="13">
+      <c r="I132" s="13">
         <v>1.6176327916666666</v>
       </c>
-      <c r="J106" s="6" t="s">
+      <c r="K132" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K106" s="4" t="s">
+      <c r="L132" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D107" t="s">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
         <v>132</v>
       </c>
-      <c r="G107" s="10" t="s">
+      <c r="H133" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="H107" s="13">
+      <c r="I133" s="13">
         <v>3.0774477499999997</v>
       </c>
-      <c r="J107" s="6" t="s">
+      <c r="K133" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K107" s="4" t="s">
+      <c r="L133" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D108" t="s">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
         <v>133</v>
       </c>
-      <c r="G108" s="10" t="s">
+      <c r="H134" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H108" s="13">
+      <c r="I134" s="13">
         <v>0.25</v>
       </c>
-      <c r="J108" s="6" t="s">
+      <c r="K134" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="K108" s="4" t="s">
+      <c r="L134" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G111" s="9" t="s">
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="8"/>
+      <c r="L136" s="8"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H137" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H111" s="9">
+      <c r="I137" s="9">
         <v>0</v>
       </c>
-      <c r="J111" s="9" t="s">
+      <c r="K137" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G112" t="s">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H138" t="s">
         <v>49</v>
       </c>
-      <c r="H112" t="s">
+      <c r="I138" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="8"/>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="8"/>
-      <c r="K114" s="8"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G115" s="9" t="s">
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H141" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="H115" s="9">
+      <c r="I141" s="9">
         <v>0</v>
       </c>
-      <c r="I115" s="9" t="s">
+      <c r="J141" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="J115" s="9" t="s">
+      <c r="K141" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
         <v>161</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H142" t="s">
         <v>168</v>
       </c>
-      <c r="H116">
+      <c r="I142">
         <v>302</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J142" t="s">
         <v>169</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K142" t="s">
         <v>170</v>
       </c>
-      <c r="K116" t="s">
+      <c r="L142" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B117" t="s">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
         <v>162</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H143" t="s">
         <v>168</v>
       </c>
-      <c r="H117">
+      <c r="I143">
         <v>197</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J143" t="s">
         <v>169</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K143" t="s">
         <v>171</v>
       </c>
-      <c r="K117" t="s">
+      <c r="L143" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
         <v>163</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H144" t="s">
         <v>168</v>
       </c>
-      <c r="H118">
+      <c r="I144">
         <v>216</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J144" t="s">
         <v>169</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K144" t="s">
         <v>172</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L144" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
         <v>164</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H145" t="s">
         <v>168</v>
       </c>
-      <c r="H119">
+      <c r="I145">
         <v>216</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J145" t="s">
         <v>169</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K145" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
         <v>165</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H146" t="s">
         <v>168</v>
       </c>
-      <c r="H120">
+      <c r="I146">
         <v>216</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J146" t="s">
         <v>169</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K146" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
         <v>166</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H147" t="s">
         <v>168</v>
       </c>
-      <c r="H121">
+      <c r="I147">
         <v>216</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J147" t="s">
         <v>169</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K147" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
         <v>167</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H148" t="s">
         <v>168</v>
       </c>
-      <c r="H122">
+      <c r="I148">
         <v>216</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J148" t="s">
         <v>169</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K148" t="s">
         <v>172</v>
       </c>
     </row>

--- a/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
+++ b/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
-    <sheet name="references" sheetId="2" r:id="rId2"/>
+    <sheet name="energy stables" sheetId="3" r:id="rId2"/>
+    <sheet name="references" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="245">
   <si>
     <t>f_crop</t>
   </si>
@@ -567,9 +568,6 @@
     <t>electricity</t>
   </si>
   <si>
-    <t>Energy in greenhouses</t>
-  </si>
-  <si>
     <t>f_activity</t>
   </si>
   <si>
@@ -671,6 +669,48 @@
   </si>
   <si>
     <t>N2O</t>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2006. Chapter 3, Table 3.2.1</t>
+  </si>
+  <si>
+    <t>Gas/ Diesel Oil</t>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2006. Chapter 3, Table 3.2.2</t>
+  </si>
+  <si>
+    <t>assume same as diesel</t>
+  </si>
+  <si>
+    <t>no emissions?</t>
+  </si>
+  <si>
+    <t>CH4fos</t>
+  </si>
+  <si>
+    <t>CH4bio</t>
+  </si>
+  <si>
+    <t>kg/TJ</t>
+  </si>
+  <si>
+    <t>Wood / Wood Waste</t>
+  </si>
+  <si>
+    <t>Natural Gas</t>
+  </si>
+  <si>
+    <t>Crude Oil</t>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2006. Chapter 2, Table 2.5</t>
+  </si>
+  <si>
+    <t>Fallback</t>
+  </si>
+  <si>
+    <t>Energy use in greenhouses</t>
   </si>
   <si>
     <r>
@@ -684,50 +724,184 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> (add non-GHG compunds?)</t>
+      <t xml:space="preserve"> (add non-GHG compounds?)</t>
     </r>
   </si>
   <si>
-    <t>IPCC Guidelines 2006. Chapter 3, Table 3.2.1</t>
-  </si>
-  <si>
-    <t>Gas/ Diesel Oil</t>
-  </si>
-  <si>
-    <t>IPCC Guidelines 2006. Chapter 3, Table 3.2.2</t>
-  </si>
-  <si>
-    <t>assume same as diesel</t>
-  </si>
-  <si>
-    <t>no emissions?</t>
-  </si>
-  <si>
-    <t>CH4fos</t>
-  </si>
-  <si>
-    <t>CH4bio</t>
-  </si>
-  <si>
-    <t>kg/TJ</t>
-  </si>
-  <si>
-    <t>Wood / Wood Waste</t>
-  </si>
-  <si>
-    <t>Natural Gas</t>
-  </si>
-  <si>
-    <t>Crude Oil</t>
-  </si>
-  <si>
-    <t>IPCC Guidelines 2006. Chapter 2, Table 2.5</t>
-  </si>
-  <si>
-    <t>grain drying</t>
-  </si>
-  <si>
-    <t>Fallback</t>
+    <t>f_species</t>
+  </si>
+  <si>
+    <t>cattle</t>
+  </si>
+  <si>
+    <t>Energy use in stables</t>
+  </si>
+  <si>
+    <t>stable machinery</t>
+  </si>
+  <si>
+    <t>stable heating</t>
+  </si>
+  <si>
+    <t>stable milking</t>
+  </si>
+  <si>
+    <t>kWh/kg milk</t>
+  </si>
+  <si>
+    <t>stable misc</t>
+  </si>
+  <si>
+    <t>kWh/head</t>
+  </si>
+  <si>
+    <t>f_breed</t>
+  </si>
+  <si>
+    <t>f_animal</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>cows</t>
+  </si>
+  <si>
+    <t>Milk production</t>
+  </si>
+  <si>
+    <t>Gård A</t>
+  </si>
+  <si>
+    <t>Gård B</t>
+  </si>
+  <si>
+    <t>dairy cows</t>
+  </si>
+  <si>
+    <t>recruitment</t>
+  </si>
+  <si>
+    <t>milk prod.</t>
+  </si>
+  <si>
+    <t>heads</t>
+  </si>
+  <si>
+    <t>kg/cow</t>
+  </si>
+  <si>
+    <t>feeding</t>
+  </si>
+  <si>
+    <t>ventilation</t>
+  </si>
+  <si>
+    <t>manure mgmt</t>
+  </si>
+  <si>
+    <t>lighting</t>
+  </si>
+  <si>
+    <t>milking</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>of which electricity</t>
+  </si>
+  <si>
+    <t>share for recruitment</t>
+  </si>
+  <si>
+    <t>kWh/cow/year</t>
+  </si>
+  <si>
+    <t>recr.</t>
+  </si>
+  <si>
+    <t>per head</t>
+  </si>
+  <si>
+    <t>per kg milk</t>
+  </si>
+  <si>
+    <t>&lt;--- Assumes double feed consuption for dairy cows compared to recruitment</t>
+  </si>
+  <si>
+    <t>stable_energy_use_per_head</t>
+  </si>
+  <si>
+    <t>f_animal_prod</t>
+  </si>
+  <si>
+    <t>stable_energy_use_per_prod</t>
+  </si>
+  <si>
+    <t>kWh/kg</t>
+  </si>
+  <si>
+    <t>milk</t>
+  </si>
+  <si>
+    <t>&lt;--- Milking only dairy cows</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hörndahl, Torsten &amp; Neuman, Lars</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. (2012). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Energiförbrukning I jordbrukets driftsbyggnader - En kartläggning av 16 gårdar 2005-2006 kompletterat med mätningar på två gårdar 2010-2012</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Sveriges lantbruksuniversitet Fakulteten för landskapsplanering, trädgårds- och jordbruksvetenskap. Rapport 2012:19</t>
+    </r>
+  </si>
+  <si>
+    <t>Hörndahl, Torsten &amp; Neuman, Lars. (2012). Energiförbrukning I jordbrukets driftsbyggnader - En kartläggning av 16 gårdar 2005-2006 kompletterat med mätningar på två gårdar 2010-2012. Sveriges lantbruksuniversitet Fakulteten för landskapsplanering, trädgårds- och jordbruksvetenskap. Rapport 2012:19</t>
+  </si>
+  <si>
+    <t>Hörndahl &amp; Neuman (2012)</t>
+  </si>
+  <si>
+    <t>manure, lighting, ventilation, etc.</t>
   </si>
 </sst>
 </file>
@@ -736,9 +910,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -817,6 +991,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -838,7 +1050,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -883,11 +1095,94 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -910,14 +1205,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1195,2359 +1518,2603 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:T161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" customWidth="1"/>
-    <col min="11" max="11" width="31.7109375" customWidth="1"/>
-    <col min="12" max="12" width="22.7109375" customWidth="1"/>
+    <col min="7" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="31.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="H1" s="14" t="s">
+      <c r="K1" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="L1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H2" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="I2" s="9">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L2" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="9">
         <v>0</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="18">
+      <c r="L4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M4" s="18">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
-      <c r="J4" t="s">
+      <c r="N4" t="s">
         <v>128</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M5" s="18">
+        <f>100-M4</f>
+        <v>2.8839238995413581</v>
+      </c>
+      <c r="N5" t="s">
+        <v>128</v>
+      </c>
+      <c r="P5" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M9" s="10">
+        <v>100</v>
+      </c>
+      <c r="N9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M11" s="10">
+        <v>100</v>
+      </c>
+      <c r="N11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M12" s="10">
+        <v>100</v>
+      </c>
+      <c r="N12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I5" s="18">
-        <f>100-I4</f>
-        <v>2.8839238995413581</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="L14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M14" s="11">
+        <v>6.4777062142923141</v>
+      </c>
+      <c r="N14" t="s">
         <v>128</v>
       </c>
-      <c r="L5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I6" s="10">
+      <c r="P14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M15" s="11">
+        <v>8.7567853491111922</v>
+      </c>
+      <c r="N15" t="s">
+        <v>128</v>
+      </c>
+      <c r="O15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M16" s="18">
+        <v>59.671114354829328</v>
+      </c>
+      <c r="N16" t="s">
+        <v>128</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="P16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M17" s="18">
+        <v>16.802918820320372</v>
+      </c>
+      <c r="N17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M18" s="11">
+        <v>7.4851294970113242</v>
+      </c>
+      <c r="N18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0.80634576443547301</v>
+      </c>
+      <c r="N19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>121</v>
+      </c>
+      <c r="L21" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" s="15">
+        <v>80</v>
+      </c>
+      <c r="N21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>122</v>
+      </c>
+      <c r="L22" t="s">
+        <v>130</v>
+      </c>
+      <c r="M22" s="15">
+        <v>10</v>
+      </c>
+      <c r="N22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" t="s">
+        <v>130</v>
+      </c>
+      <c r="M23" s="15">
+        <v>10</v>
+      </c>
+      <c r="N23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G25" s="4"/>
+      <c r="L25" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="M25" s="23">
         <v>0</v>
       </c>
-      <c r="J6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="15"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I9" s="11">
-        <v>6.4777062142923141</v>
-      </c>
-      <c r="J9" t="s">
-        <v>128</v>
-      </c>
-      <c r="L9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I10" s="11">
-        <v>8.7567853491111922</v>
-      </c>
-      <c r="J10" t="s">
-        <v>128</v>
-      </c>
-      <c r="K10" t="s">
-        <v>176</v>
-      </c>
-      <c r="L10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I11" s="18">
-        <v>59.671114354829328</v>
-      </c>
-      <c r="J11" t="s">
-        <v>128</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="L11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I12" s="18">
-        <v>16.802918820320372</v>
-      </c>
-      <c r="J12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I13" s="11">
-        <v>7.4851294970113242</v>
-      </c>
-      <c r="J13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0.80634576443547301</v>
-      </c>
-      <c r="J14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F16" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" t="s">
-        <v>130</v>
-      </c>
-      <c r="I16" s="15">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" t="s">
-        <v>130</v>
-      </c>
-      <c r="I17" s="15">
-        <v>10</v>
-      </c>
-      <c r="J17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" t="s">
-        <v>130</v>
-      </c>
-      <c r="I18" s="15">
-        <v>10</v>
-      </c>
-      <c r="J18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C20" s="4"/>
-      <c r="H20" s="9" t="s">
+      <c r="N25" s="9"/>
+      <c r="O25" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G26" s="4"/>
+      <c r="M26" s="18"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" t="s">
         <v>183</v>
       </c>
-      <c r="I20" s="26">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="4"/>
-      <c r="I21" s="18"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" t="s">
-        <v>184</v>
-      </c>
-      <c r="H22" t="s">
-        <v>183</v>
-      </c>
-      <c r="I22" s="18">
+      <c r="L27" t="s">
+        <v>182</v>
+      </c>
+      <c r="M27" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
-      <c r="J22" t="s">
-        <v>194</v>
-      </c>
-      <c r="K22" t="s">
-        <v>188</v>
-      </c>
-      <c r="L22" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="N27" t="s">
+        <v>192</v>
+      </c>
+      <c r="O27" t="s">
+        <v>186</v>
+      </c>
+      <c r="P27" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G28" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G23" t="s">
-        <v>192</v>
-      </c>
-      <c r="H23" t="s">
-        <v>183</v>
-      </c>
-      <c r="I23" s="11">
+      <c r="K28" t="s">
+        <v>190</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="J23" t="s">
-        <v>194</v>
-      </c>
-      <c r="L23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="N28" t="s">
+        <v>192</v>
+      </c>
+      <c r="P28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G24" t="s">
-        <v>185</v>
-      </c>
-      <c r="H24" t="s">
-        <v>183</v>
-      </c>
-      <c r="I24" s="11">
+      <c r="K29" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" t="s">
+        <v>182</v>
+      </c>
+      <c r="M29" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="J24" t="s">
-        <v>194</v>
-      </c>
-      <c r="L24" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="N29" t="s">
+        <v>192</v>
+      </c>
+      <c r="P29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G30" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K30" t="s">
+        <v>183</v>
+      </c>
+      <c r="L30" t="s">
+        <v>182</v>
+      </c>
+      <c r="M30" s="18">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G31" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K31" t="s">
+        <v>191</v>
+      </c>
+      <c r="L31" t="s">
+        <v>182</v>
+      </c>
+      <c r="M31" s="22">
+        <f t="shared" ref="M31:M32" si="0">M28</f>
+        <v>3.9</v>
+      </c>
+      <c r="N31" t="s">
+        <v>192</v>
+      </c>
+      <c r="O31" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G32" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K32" t="s">
         <v>184</v>
       </c>
-      <c r="H25" t="s">
-        <v>183</v>
-      </c>
-      <c r="I25" s="18">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G26" t="s">
-        <v>193</v>
-      </c>
-      <c r="H26" t="s">
-        <v>183</v>
-      </c>
-      <c r="I26" s="23">
-        <f t="shared" ref="I26:I27" si="0">I23</f>
-        <v>3.9</v>
-      </c>
-      <c r="J26" t="s">
-        <v>194</v>
-      </c>
-      <c r="K26" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G27" t="s">
-        <v>185</v>
-      </c>
-      <c r="H27" t="s">
-        <v>183</v>
-      </c>
-      <c r="I27" s="23">
+      <c r="L32" t="s">
+        <v>182</v>
+      </c>
+      <c r="M32" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="J27" t="s">
+      <c r="N32" t="s">
+        <v>192</v>
+      </c>
+      <c r="O32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G33" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K33" t="s">
+        <v>183</v>
+      </c>
+      <c r="L33" t="s">
+        <v>182</v>
+      </c>
+      <c r="M33" s="18">
+        <v>73300</v>
+      </c>
+      <c r="N33" t="s">
+        <v>192</v>
+      </c>
+      <c r="O33" t="s">
+        <v>195</v>
+      </c>
+      <c r="P33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G34" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K34" t="s">
+        <v>190</v>
+      </c>
+      <c r="L34" t="s">
+        <v>182</v>
+      </c>
+      <c r="M34">
+        <v>10</v>
+      </c>
+      <c r="N34" t="s">
+        <v>192</v>
+      </c>
+      <c r="P34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G35" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K35" t="s">
+        <v>184</v>
+      </c>
+      <c r="L35" t="s">
+        <v>182</v>
+      </c>
+      <c r="M35">
+        <v>0.6</v>
+      </c>
+      <c r="N35" t="s">
+        <v>192</v>
+      </c>
+      <c r="P35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K36" t="s">
+        <v>183</v>
+      </c>
+      <c r="L36" t="s">
+        <v>182</v>
+      </c>
+      <c r="M36" s="18">
+        <v>56100</v>
+      </c>
+      <c r="N36" t="s">
+        <v>192</v>
+      </c>
+      <c r="O36" t="s">
         <v>194</v>
       </c>
-      <c r="K27" t="s">
+      <c r="P36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G37" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K37" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="L37" t="s">
+        <v>182</v>
+      </c>
+      <c r="M37">
+        <v>5</v>
+      </c>
+      <c r="N37" t="s">
+        <v>192</v>
+      </c>
+      <c r="P37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G38" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K38" t="s">
+        <v>184</v>
+      </c>
+      <c r="L38" t="s">
+        <v>182</v>
+      </c>
+      <c r="M38">
+        <v>0.1</v>
+      </c>
+      <c r="N38" t="s">
+        <v>192</v>
+      </c>
+      <c r="P38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G39" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K39" t="s">
+        <v>183</v>
+      </c>
+      <c r="L39" t="s">
+        <v>182</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>192</v>
+      </c>
+      <c r="O39" t="s">
+        <v>193</v>
+      </c>
+      <c r="P39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G40" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K40" t="s">
+        <v>191</v>
+      </c>
+      <c r="L40" t="s">
+        <v>182</v>
+      </c>
+      <c r="M40" s="18">
+        <v>300</v>
+      </c>
+      <c r="N40" t="s">
+        <v>192</v>
+      </c>
+      <c r="P40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G41" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K41" t="s">
+        <v>184</v>
+      </c>
+      <c r="L41" t="s">
+        <v>182</v>
+      </c>
+      <c r="M41" s="18">
+        <v>4</v>
+      </c>
+      <c r="N41" t="s">
+        <v>192</v>
+      </c>
+      <c r="P41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s">
+        <v>182</v>
+      </c>
+      <c r="M42" s="18">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>192</v>
+      </c>
+      <c r="O42" s="15"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G43" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L43" t="s">
+        <v>182</v>
+      </c>
+      <c r="M43" s="18">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>192</v>
+      </c>
+      <c r="O43" s="15"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G44" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H28" t="s">
-        <v>183</v>
-      </c>
-      <c r="I28" s="18">
+      <c r="L44" t="s">
+        <v>182</v>
+      </c>
+      <c r="M44" s="18">
         <v>0</v>
       </c>
-      <c r="J28" t="s">
-        <v>194</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>153</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="N44" t="s">
+        <v>192</v>
+      </c>
+      <c r="O44" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G45" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H29" t="s">
-        <v>183</v>
-      </c>
-      <c r="I29" s="18">
+      <c r="L45" t="s">
+        <v>182</v>
+      </c>
+      <c r="M45" s="18">
         <v>0</v>
       </c>
-      <c r="J29" t="s">
-        <v>194</v>
-      </c>
-      <c r="K29" s="15"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="4"/>
-      <c r="I30" s="22"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" t="s">
-        <v>184</v>
-      </c>
-      <c r="H31" t="s">
-        <v>183</v>
-      </c>
-      <c r="I31" s="18">
-        <v>73300</v>
-      </c>
-      <c r="J31" t="s">
-        <v>194</v>
-      </c>
-      <c r="K31" t="s">
-        <v>197</v>
-      </c>
-      <c r="L31" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>159</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="N45" t="s">
         <v>192</v>
       </c>
-      <c r="H32" t="s">
-        <v>183</v>
-      </c>
-      <c r="I32">
-        <v>10</v>
-      </c>
-      <c r="J32" t="s">
-        <v>194</v>
-      </c>
-      <c r="L32" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" t="s">
-        <v>183</v>
-      </c>
-      <c r="I33">
-        <v>0.6</v>
-      </c>
-      <c r="J33" t="s">
-        <v>194</v>
-      </c>
-      <c r="L33" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" t="s">
-        <v>184</v>
-      </c>
-      <c r="H34" t="s">
-        <v>183</v>
-      </c>
-      <c r="I34" s="18">
-        <v>56100</v>
-      </c>
-      <c r="J34" t="s">
-        <v>194</v>
-      </c>
-      <c r="K34" t="s">
-        <v>196</v>
-      </c>
-      <c r="L34" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G35" t="s">
-        <v>192</v>
-      </c>
-      <c r="H35" t="s">
-        <v>183</v>
-      </c>
-      <c r="I35">
-        <v>5</v>
-      </c>
-      <c r="J35" t="s">
-        <v>194</v>
-      </c>
-      <c r="L35" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G36" t="s">
-        <v>185</v>
-      </c>
-      <c r="H36" t="s">
-        <v>183</v>
-      </c>
-      <c r="I36">
-        <v>0.1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>194</v>
-      </c>
-      <c r="L36" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>159</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G37" t="s">
-        <v>184</v>
-      </c>
-      <c r="H37" t="s">
-        <v>183</v>
-      </c>
-      <c r="I37" s="18">
-        <v>0</v>
-      </c>
-      <c r="J37" t="s">
-        <v>194</v>
-      </c>
-      <c r="K37" t="s">
-        <v>195</v>
-      </c>
-      <c r="L37" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G38" t="s">
-        <v>193</v>
-      </c>
-      <c r="H38" t="s">
-        <v>183</v>
-      </c>
-      <c r="I38" s="18">
-        <v>300</v>
-      </c>
-      <c r="J38" t="s">
-        <v>194</v>
-      </c>
-      <c r="L38" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G39" t="s">
-        <v>185</v>
-      </c>
-      <c r="H39" t="s">
-        <v>183</v>
-      </c>
-      <c r="I39" s="18">
-        <v>4</v>
-      </c>
-      <c r="J39" t="s">
-        <v>194</v>
-      </c>
-      <c r="L39" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>159</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H40" t="s">
-        <v>183</v>
-      </c>
-      <c r="I40" s="18">
-        <v>0</v>
-      </c>
-      <c r="J40" t="s">
-        <v>194</v>
-      </c>
-      <c r="K40" s="15"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H41" t="s">
-        <v>183</v>
-      </c>
-      <c r="I41" s="18">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
-        <v>194</v>
-      </c>
-      <c r="K41" s="15"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>159</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H42" t="s">
-        <v>183</v>
-      </c>
-      <c r="I42" s="18">
-        <v>0</v>
-      </c>
-      <c r="J42" t="s">
-        <v>194</v>
-      </c>
-      <c r="K42" s="15"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="6"/>
-      <c r="I43" s="18"/>
-      <c r="K43" s="15"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="I44" s="25">
-        <v>0</v>
-      </c>
-      <c r="K44" s="15"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I45" s="22"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="O45" s="15"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G46" s="6"/>
+      <c r="M46" s="18"/>
+      <c r="O46" s="15"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I48">
-        <v>10800</v>
-      </c>
-      <c r="J48" t="s">
-        <v>11</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49">
-        <v>5</v>
-      </c>
-      <c r="J49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M49">
+        <v>10800</v>
+      </c>
+      <c r="N49" t="s">
+        <v>11</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I50">
-        <v>2</v>
-      </c>
-      <c r="J50" t="s">
-        <v>126</v>
-      </c>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+      <c r="N50" t="s">
+        <v>13</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
-      <c r="H51" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51">
-        <v>0.2</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M51">
+        <v>2</v>
+      </c>
+      <c r="N51" t="s">
+        <v>126</v>
+      </c>
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I52">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="J52" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52">
+        <v>0.2</v>
+      </c>
+      <c r="N52" t="s">
+        <v>15</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I53">
-        <v>250</v>
-      </c>
-      <c r="J53" t="s">
-        <v>19</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M53">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="N53" t="s">
+        <v>17</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="I54" s="9">
-        <v>1</v>
-      </c>
-      <c r="J54" s="9"/>
-      <c r="K54" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54">
+        <v>250</v>
+      </c>
+      <c r="N54" t="s">
+        <v>19</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B55" s="4"/>
-      <c r="C55" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
-      <c r="H55" s="6" t="s">
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="I55">
-        <v>0.26</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="M55" s="9">
+        <v>1</v>
+      </c>
+      <c r="N55" s="9"/>
+      <c r="O55" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="B56" s="4"/>
-      <c r="C56" s="4" t="s">
-        <v>180</v>
-      </c>
+      <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="6" t="s">
+      <c r="G56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>0.26</v>
       </c>
-      <c r="K56" s="5" t="s">
+      <c r="O56" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="6" t="s">
+      <c r="G57" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I57">
+      <c r="M57">
+        <v>0.26</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58">
         <v>0.45</v>
       </c>
-      <c r="K57" s="5" t="s">
+      <c r="O58" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="B58" s="4"/>
-      <c r="C58" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I58">
-        <v>0.76</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="6" t="s">
+      <c r="G59" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59">
+        <v>0.76</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I59">
+      <c r="M60">
         <v>4</v>
       </c>
-      <c r="J59" t="s">
+      <c r="N60" t="s">
         <v>21</v>
       </c>
-      <c r="K59" s="7" t="s">
+      <c r="O60" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H62" t="s">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L63" t="s">
         <v>127</v>
       </c>
-      <c r="I62">
+      <c r="M63">
         <v>4</v>
       </c>
-      <c r="J62" t="s">
+      <c r="N63" t="s">
         <v>29</v>
       </c>
-      <c r="K62" t="s">
+      <c r="O63" t="s">
         <v>28</v>
       </c>
-      <c r="P62" s="6"/>
-    </row>
-    <row r="63" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="H63" t="s">
+      <c r="T63" s="6"/>
+    </row>
+    <row r="64" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L64" t="s">
         <v>45</v>
       </c>
-      <c r="I63">
+      <c r="M64">
         <v>0.9</v>
       </c>
-      <c r="K63" t="s">
+      <c r="O64" t="s">
         <v>30</v>
       </c>
-      <c r="P63" s="6"/>
-    </row>
-    <row r="64" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="H64" t="s">
+      <c r="T64" s="6"/>
+    </row>
+    <row r="65" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L65" t="s">
         <v>38</v>
       </c>
-      <c r="I64">
+      <c r="M65">
         <v>1.2250000000000001</v>
       </c>
-      <c r="J64" t="s">
+      <c r="N65" t="s">
         <v>32</v>
       </c>
-      <c r="K64" t="s">
+      <c r="O65" t="s">
         <v>31</v>
       </c>
-      <c r="P64" s="6"/>
-    </row>
-    <row r="65" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="H65" t="s">
+      <c r="T65" s="6"/>
+    </row>
+    <row r="66" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L66" t="s">
         <v>39</v>
       </c>
-      <c r="I65">
+      <c r="M66">
         <v>0.1</v>
       </c>
-      <c r="K65" t="s">
+      <c r="O66" t="s">
         <v>33</v>
       </c>
-      <c r="P65" s="6"/>
-    </row>
-    <row r="66" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="H66" t="s">
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L67" t="s">
         <v>40</v>
       </c>
-      <c r="I66">
+      <c r="M67">
         <v>0.01</v>
       </c>
-      <c r="K66" t="s">
+      <c r="O67" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H67" t="s">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L68" t="s">
         <v>41</v>
       </c>
-      <c r="I67">
+      <c r="M68">
         <v>0.2</v>
       </c>
-      <c r="K67" t="s">
+      <c r="O68" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="H68" t="s">
+    <row r="69" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L69" t="s">
         <v>42</v>
       </c>
-      <c r="I68">
+      <c r="M69">
         <v>0.8</v>
       </c>
-      <c r="K68" t="s">
+      <c r="O69" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="H69" t="s">
+    <row r="70" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L70" t="s">
         <v>43</v>
       </c>
-      <c r="I69">
+      <c r="M70">
         <v>55</v>
       </c>
-      <c r="K69" t="s">
+      <c r="O70" t="s">
         <v>37</v>
       </c>
-      <c r="O69" s="4"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="S70" s="4"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H72" s="9" t="s">
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="N72" s="8"/>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L73" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="I72" s="9">
+      <c r="M73" s="9">
         <v>0</v>
       </c>
-      <c r="J72" s="9" t="s">
+      <c r="N73" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H73" s="9" t="s">
+      <c r="O73" s="9"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L74" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I73" s="9">
+      <c r="M74" s="9">
         <v>0</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="N74" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K73" s="9"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H74" s="9" t="s">
+      <c r="O74" s="9"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L75" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I74" s="9">
+      <c r="M75" s="9">
         <v>0</v>
       </c>
-      <c r="J74" s="9" t="s">
+      <c r="N75" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K74" s="9"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H75" s="9" t="s">
+      <c r="O75" s="9"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L76" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I75" s="9">
+      <c r="M76" s="9">
         <v>0</v>
       </c>
-      <c r="J75" s="9" t="s">
+      <c r="N76" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="9"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H76" s="9" t="s">
+      <c r="O76" s="9"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L77" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I76" s="9">
+      <c r="M77" s="9">
         <v>0</v>
       </c>
-      <c r="J76" s="9" t="s">
+      <c r="N77" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="K76" s="9"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H77" s="9" t="s">
+      <c r="O77" s="9"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L78" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="I77" s="9">
+      <c r="M78" s="9">
         <v>1</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="N78" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="O78" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H78" s="9" t="s">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L79" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I78" s="9">
+      <c r="M79" s="9">
         <v>0</v>
       </c>
-      <c r="J78" s="9" t="s">
+      <c r="N79" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="K78" s="9"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H79" s="9" t="s">
+      <c r="O79" s="9"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L80" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I79" s="9">
+      <c r="M80" s="9">
         <v>0</v>
       </c>
-      <c r="J79" s="9" t="s">
+      <c r="N80" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="K79" s="9"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H80" s="9" t="s">
+      <c r="O80" s="9"/>
+    </row>
+    <row r="81" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L81" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="I80" s="9">
+      <c r="M81" s="9">
         <v>0</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="N81" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="K80" s="9"/>
-    </row>
-    <row r="81" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="H81" s="9" t="s">
+      <c r="O81" s="9"/>
+    </row>
+    <row r="82" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L82" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I81" s="9">
+      <c r="M82" s="9">
         <v>0</v>
       </c>
-      <c r="J81" s="9" t="s">
+      <c r="N82" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="K81" s="9"/>
-    </row>
-    <row r="82" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="H82" s="9"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-    </row>
-    <row r="83" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D83" t="s">
+      <c r="O82" s="9"/>
+    </row>
+    <row r="83" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
+      <c r="N83" s="9"/>
+      <c r="O83" s="9"/>
+    </row>
+    <row r="84" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H84" t="s">
         <v>60</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="L84" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I83" s="10">
+      <c r="M84" s="10">
         <v>364</v>
       </c>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10" t="s">
+      <c r="N84" s="10"/>
+      <c r="O84" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="L83" s="10"/>
-    </row>
-    <row r="84" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D84" t="s">
+      <c r="P84" s="10"/>
+    </row>
+    <row r="85" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H85" t="s">
         <v>60</v>
       </c>
-      <c r="H84" s="10" t="s">
+      <c r="L85" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I84" s="10">
+      <c r="M85" s="10">
         <v>18.8</v>
       </c>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-    </row>
-    <row r="85" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D85" t="s">
+      <c r="N85" s="10"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
+    </row>
+    <row r="86" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H86" t="s">
         <v>60</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="L86" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I85" s="10">
+      <c r="M86" s="10">
         <v>0</v>
       </c>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-    </row>
-    <row r="86" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D86" t="s">
+      <c r="N86" s="10"/>
+      <c r="O86" s="10"/>
+      <c r="P86" s="10"/>
+    </row>
+    <row r="87" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H87" t="s">
         <v>60</v>
       </c>
-      <c r="H86" s="10" t="s">
+      <c r="L87" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I86" s="10">
+      <c r="M87" s="10">
         <v>10</v>
       </c>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-    </row>
-    <row r="87" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D87" t="s">
+      <c r="N87" s="10"/>
+      <c r="O87" s="10"/>
+      <c r="P87" s="10"/>
+    </row>
+    <row r="88" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
         <v>60</v>
       </c>
-      <c r="E87" t="s">
+      <c r="I88" t="s">
         <v>74</v>
       </c>
-      <c r="H87" s="10" t="s">
+      <c r="L88" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I87" s="12">
+      <c r="M88" s="12">
         <v>1</v>
       </c>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-    </row>
-    <row r="88" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D88" t="s">
+      <c r="N88" s="10"/>
+      <c r="O88" s="10"/>
+      <c r="P88" s="10"/>
+    </row>
+    <row r="89" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H89" t="s">
         <v>60</v>
       </c>
-      <c r="E88" t="s">
+      <c r="I89" t="s">
         <v>73</v>
       </c>
-      <c r="H88" s="10" t="s">
+      <c r="L89" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I88" s="10">
+      <c r="M89" s="10">
         <v>0.88</v>
       </c>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-    </row>
-    <row r="89" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D89" t="s">
+      <c r="N89" s="10"/>
+      <c r="O89" s="10"/>
+      <c r="P89" s="10"/>
+    </row>
+    <row r="90" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H90" t="s">
         <v>60</v>
       </c>
-      <c r="E89" t="s">
+      <c r="I90" t="s">
         <v>72</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="L90" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I89" s="10">
+      <c r="M90" s="10">
         <v>0.78</v>
       </c>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-    </row>
-    <row r="90" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-    </row>
-    <row r="91" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D91" t="s">
+      <c r="N90" s="10"/>
+      <c r="O90" s="10"/>
+      <c r="P90" s="10"/>
+    </row>
+    <row r="91" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L91" s="10"/>
+      <c r="M91" s="10"/>
+      <c r="N91" s="10"/>
+      <c r="O91" s="10"/>
+      <c r="P91" s="10"/>
+    </row>
+    <row r="92" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
         <v>63</v>
       </c>
-      <c r="H91" s="10" t="s">
+      <c r="L92" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I91" s="10">
+      <c r="M92" s="10">
         <v>652</v>
       </c>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10" t="s">
+      <c r="N92" s="10"/>
+      <c r="O92" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L91" s="10"/>
-    </row>
-    <row r="92" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D92" t="s">
+      <c r="P92" s="10"/>
+    </row>
+    <row r="93" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H93" t="s">
         <v>63</v>
       </c>
-      <c r="H92" s="10" t="s">
+      <c r="L93" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I92" s="10">
+      <c r="M93" s="10">
         <v>0</v>
       </c>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-    </row>
-    <row r="93" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D93" t="s">
+      <c r="N93" s="10"/>
+      <c r="O93" s="10"/>
+      <c r="P93" s="10"/>
+    </row>
+    <row r="94" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H94" t="s">
         <v>63</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="L94" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I93" s="10">
+      <c r="M94" s="10">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-    </row>
-    <row r="94" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D94" t="s">
+      <c r="N94" s="10"/>
+      <c r="O94" s="10"/>
+      <c r="P94" s="10"/>
+    </row>
+    <row r="95" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
         <v>63</v>
       </c>
-      <c r="H94" s="10" t="s">
+      <c r="L95" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I94" s="10">
+      <c r="M95" s="10">
         <v>20</v>
       </c>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-    </row>
-    <row r="95" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D95" t="s">
+      <c r="N95" s="10"/>
+      <c r="O95" s="10"/>
+      <c r="P95" s="10"/>
+    </row>
+    <row r="96" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
         <v>63</v>
       </c>
-      <c r="E95" t="s">
+      <c r="I96" t="s">
         <v>74</v>
       </c>
-      <c r="H95" s="10" t="s">
+      <c r="L96" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I95" s="12">
+      <c r="M96" s="12">
         <v>1</v>
       </c>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-    </row>
-    <row r="96" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D96" t="s">
+      <c r="N96" s="10"/>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
+    </row>
+    <row r="97" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H97" t="s">
         <v>63</v>
       </c>
-      <c r="E96" t="s">
+      <c r="I97" t="s">
         <v>73</v>
       </c>
-      <c r="H96" s="10" t="s">
+      <c r="L97" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I96" s="12">
+      <c r="M97" s="12">
         <v>0.7</v>
       </c>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-    </row>
-    <row r="97" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D97" t="s">
+      <c r="N97" s="10"/>
+      <c r="O97" s="10"/>
+      <c r="P97" s="10"/>
+    </row>
+    <row r="98" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H98" t="s">
         <v>63</v>
       </c>
-      <c r="E97" t="s">
+      <c r="I98" t="s">
         <v>72</v>
       </c>
-      <c r="H97" s="10" t="s">
+      <c r="L98" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I97" s="10">
+      <c r="M98" s="10">
         <v>0.45</v>
       </c>
-      <c r="J97" s="10"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="10"/>
-    </row>
-    <row r="98" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="H98" s="10"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-    </row>
-    <row r="99" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D99" t="s">
+      <c r="N98" s="10"/>
+      <c r="O98" s="10"/>
+      <c r="P98" s="10"/>
+    </row>
+    <row r="99" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L99" s="10"/>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10"/>
+      <c r="O99" s="10"/>
+      <c r="P99" s="10"/>
+    </row>
+    <row r="100" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H100" t="s">
         <v>62</v>
       </c>
-      <c r="H99" s="10" t="s">
+      <c r="L100" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I99" s="10">
+      <c r="M100" s="10">
         <v>46</v>
       </c>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10" t="s">
+      <c r="N100" s="10"/>
+      <c r="O100" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L99" s="10"/>
-    </row>
-    <row r="100" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D100" t="s">
+      <c r="P100" s="10"/>
+    </row>
+    <row r="101" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H101" t="s">
         <v>62</v>
       </c>
-      <c r="H100" s="10" t="s">
+      <c r="L101" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I100" s="10">
+      <c r="M101" s="10">
         <v>2.8</v>
       </c>
-      <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="10"/>
-    </row>
-    <row r="101" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D101" t="s">
+      <c r="N101" s="10"/>
+      <c r="O101" s="10"/>
+      <c r="P101" s="10"/>
+    </row>
+    <row r="102" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H102" t="s">
         <v>62</v>
       </c>
-      <c r="H101" s="10" t="s">
+      <c r="L102" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I101" s="10">
+      <c r="M102" s="10">
         <v>0</v>
       </c>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-    </row>
-    <row r="102" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D102" t="s">
+      <c r="N102" s="10"/>
+      <c r="O102" s="10"/>
+      <c r="P102" s="10"/>
+    </row>
+    <row r="103" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H103" t="s">
         <v>62</v>
       </c>
-      <c r="H102" s="10" t="s">
+      <c r="L103" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I102" s="10">
+      <c r="M103" s="10">
         <v>5</v>
       </c>
-      <c r="J102" s="10"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="10"/>
-    </row>
-    <row r="103" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D103" t="s">
+      <c r="N103" s="10"/>
+      <c r="O103" s="10"/>
+      <c r="P103" s="10"/>
+    </row>
+    <row r="104" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H104" t="s">
         <v>62</v>
       </c>
-      <c r="E103" t="s">
+      <c r="I104" t="s">
         <v>74</v>
       </c>
-      <c r="H103" s="10" t="s">
+      <c r="L104" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I103" s="12">
+      <c r="M104" s="12">
         <v>1</v>
       </c>
-      <c r="J103" s="10"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="10"/>
-    </row>
-    <row r="104" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D104" t="s">
+      <c r="N104" s="10"/>
+      <c r="O104" s="10"/>
+      <c r="P104" s="10"/>
+    </row>
+    <row r="105" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H105" t="s">
         <v>62</v>
       </c>
-      <c r="E104" t="s">
+      <c r="I105" t="s">
         <v>73</v>
       </c>
-      <c r="H104" s="10" t="s">
+      <c r="L105" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I104" s="10">
+      <c r="M105" s="10">
         <v>0.85</v>
       </c>
-      <c r="J104" s="10"/>
-      <c r="K104" s="10"/>
-      <c r="L104" s="10"/>
-    </row>
-    <row r="105" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D105" t="s">
+      <c r="N105" s="10"/>
+      <c r="O105" s="10"/>
+      <c r="P105" s="10"/>
+    </row>
+    <row r="106" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H106" t="s">
         <v>62</v>
       </c>
-      <c r="E105" t="s">
+      <c r="I106" t="s">
         <v>72</v>
       </c>
-      <c r="H105" s="10" t="s">
+      <c r="L106" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I105" s="10">
+      <c r="M106" s="10">
         <v>0.65</v>
       </c>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="10"/>
-    </row>
-    <row r="106" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="H106" s="10"/>
-      <c r="I106" s="10"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="10"/>
-      <c r="L106" s="10"/>
-    </row>
-    <row r="107" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D107" t="s">
+      <c r="N106" s="10"/>
+      <c r="O106" s="10"/>
+      <c r="P106" s="10"/>
+    </row>
+    <row r="107" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L107" s="10"/>
+      <c r="M107" s="10"/>
+      <c r="N107" s="10"/>
+      <c r="O107" s="10"/>
+      <c r="P107" s="10"/>
+    </row>
+    <row r="108" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H108" t="s">
         <v>65</v>
       </c>
-      <c r="H107" s="10" t="s">
+      <c r="L108" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I107" s="12">
+      <c r="M108" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J107" s="10"/>
-      <c r="K107" s="6" t="s">
+      <c r="N108" s="10"/>
+      <c r="O108" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="L107" s="4" t="s">
+      <c r="P108" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="108" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D108" t="s">
+    <row r="109" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H109" t="s">
         <v>66</v>
       </c>
-      <c r="H108" s="10" t="s">
+      <c r="L109" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I108" s="12">
+      <c r="M109" s="12">
         <v>7.1</v>
       </c>
-      <c r="J108" s="10"/>
-      <c r="K108" s="6" t="s">
+      <c r="N109" s="10"/>
+      <c r="O109" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L108" s="4" t="s">
+      <c r="P109" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="109" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="H109" s="10"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-    </row>
-    <row r="110" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D110" t="s">
+    <row r="110" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L110" s="10"/>
+      <c r="M110" s="10"/>
+      <c r="N110" s="10"/>
+      <c r="O110" s="10"/>
+      <c r="P110" s="10"/>
+    </row>
+    <row r="111" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H111" t="s">
         <v>61</v>
       </c>
-      <c r="H110" s="10" t="s">
+      <c r="L111" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I110" s="12">
+      <c r="M111" s="12">
         <v>3.7353333333333332</v>
       </c>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10" t="s">
+      <c r="N111" s="10"/>
+      <c r="O111" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="L110" s="6" t="s">
+      <c r="P111" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D111" t="s">
+    <row r="112" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H112" t="s">
         <v>64</v>
       </c>
-      <c r="H111" s="10" t="s">
+      <c r="L112" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I111" s="11">
+      <c r="M112" s="11">
         <v>17.096931944444446</v>
       </c>
-      <c r="J111" s="10"/>
-      <c r="K111" s="6" t="s">
+      <c r="N112" s="10"/>
+      <c r="O112" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L111" s="4" t="s">
+      <c r="P112" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="112" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D112" t="s">
+    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H113" t="s">
         <v>67</v>
       </c>
-      <c r="H112" s="10" t="s">
+      <c r="L113" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I112" s="12">
+      <c r="M113" s="12">
         <v>1.2451111111111113</v>
       </c>
-      <c r="J112" s="10"/>
-      <c r="K112" s="6" t="s">
+      <c r="N113" s="10"/>
+      <c r="O113" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="L112" s="10" t="s">
+      <c r="P113" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D113" t="s">
+    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H114" t="s">
         <v>68</v>
       </c>
-      <c r="H113" s="10" t="s">
+      <c r="L114" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I113" s="12">
+      <c r="M114" s="12">
         <v>3.1127777777777781</v>
       </c>
-      <c r="J113" s="10"/>
-      <c r="K113" s="6" t="s">
+      <c r="N114" s="10"/>
+      <c r="O114" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="L113" s="10" t="s">
+      <c r="P114" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D114" t="s">
+    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H115" t="s">
         <v>97</v>
       </c>
-      <c r="H114" s="10" t="s">
+      <c r="L115" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I114" s="12">
+      <c r="M115" s="12">
         <v>4.6691666666666665</v>
       </c>
-      <c r="J114" s="10"/>
-      <c r="K114" s="4" t="s">
+      <c r="N115" s="10"/>
+      <c r="O115" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="L114" s="10" t="s">
+      <c r="P115" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D115" t="s">
+    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H116" t="s">
         <v>69</v>
       </c>
-      <c r="H115" s="10" t="s">
+      <c r="L116" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I115" s="12">
+      <c r="M116" s="12">
         <v>3.1127777777777781</v>
       </c>
-      <c r="J115" s="10"/>
-      <c r="K115" s="4" t="s">
+      <c r="N116" s="10"/>
+      <c r="O116" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="L115" s="6" t="s">
+      <c r="P116" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D116" t="s">
+    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H117" t="s">
         <v>70</v>
       </c>
-      <c r="H116" s="10" t="s">
+      <c r="L117" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I116" s="11">
+      <c r="M117" s="11">
         <v>11.828555555555555</v>
       </c>
-      <c r="J116" s="10"/>
-      <c r="K116" s="4" t="s">
+      <c r="N117" s="10"/>
+      <c r="O117" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="L116" s="10" t="s">
+      <c r="P117" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D117" t="s">
+    <row r="118" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H118" t="s">
         <v>100</v>
       </c>
-      <c r="H117" s="10" t="s">
+      <c r="L118" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I117" s="11">
+      <c r="M118" s="11">
         <v>26.302972222222223</v>
       </c>
-      <c r="J117" s="10"/>
-      <c r="K117" s="6" t="s">
+      <c r="N118" s="10"/>
+      <c r="O118" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="L117" s="10" t="s">
+      <c r="P118" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D118" t="s">
+    <row r="119" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H119" t="s">
         <v>101</v>
       </c>
-      <c r="H118" s="10" t="s">
+      <c r="L119" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I118" s="11">
+      <c r="M119" s="11">
         <v>11.3</v>
       </c>
-      <c r="J118" s="10"/>
-      <c r="K118" s="6" t="s">
+      <c r="N119" s="10"/>
+      <c r="O119" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="L118" s="10" t="s">
+      <c r="P119" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D119" t="s">
+    <row r="120" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H120" t="s">
         <v>102</v>
       </c>
-      <c r="H119" s="10" t="s">
+      <c r="L120" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I119" s="11">
+      <c r="M120" s="11">
         <v>23.278130416666666</v>
       </c>
-      <c r="J119" s="10"/>
-      <c r="K119" s="6" t="s">
+      <c r="N120" s="10"/>
+      <c r="O120" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L119" s="10" t="s">
+      <c r="P120" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D120" t="s">
+    <row r="121" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H121" t="s">
         <v>71</v>
       </c>
-      <c r="H120" s="10" t="s">
+      <c r="L121" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I120" s="10">
+      <c r="M121" s="10">
         <v>13.15</v>
       </c>
-      <c r="J120" s="10"/>
-      <c r="K120" s="10" t="s">
+      <c r="N121" s="10"/>
+      <c r="O121" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="L120" s="10" t="s">
+      <c r="P121" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D121" t="s">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H122" t="s">
         <v>71</v>
       </c>
-      <c r="H121" s="10" t="s">
+      <c r="L122" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I121" s="10">
+      <c r="M122" s="10">
         <v>5.26</v>
       </c>
-      <c r="J121" s="10"/>
-      <c r="K121" s="10" t="s">
+      <c r="N122" s="10"/>
+      <c r="O122" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="L121" s="10" t="s">
+      <c r="P122" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
+    <row r="123" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
         <v>110</v>
       </c>
-      <c r="D122" t="s">
+      <c r="H123" t="s">
         <v>71</v>
       </c>
-      <c r="H122" s="10" t="s">
+      <c r="L123" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I122" s="12">
+      <c r="M123" s="12">
         <v>1.7546281240590185</v>
       </c>
-      <c r="J122" s="10"/>
-      <c r="K122" s="10" t="s">
+      <c r="N123" s="10"/>
+      <c r="O123" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="L122" s="4" t="s">
+      <c r="P123" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
+    <row r="124" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
         <v>113</v>
       </c>
-      <c r="D123" t="s">
+      <c r="H124" t="s">
         <v>71</v>
       </c>
-      <c r="H123" s="10" t="s">
+      <c r="L124" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I123" s="12">
+      <c r="M124" s="12">
         <v>5.1828516694033944</v>
       </c>
-      <c r="J123" s="10"/>
-      <c r="K123" s="6" t="s">
+      <c r="N124" s="10"/>
+      <c r="O124" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="L123" s="4" t="s">
+      <c r="P124" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
+    <row r="125" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
         <v>114</v>
       </c>
-      <c r="D124" t="s">
+      <c r="H125" t="s">
         <v>71</v>
       </c>
-      <c r="H124" s="10" t="s">
+      <c r="L125" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I124" s="13">
+      <c r="M125" s="13">
         <v>4.0531064740502947</v>
       </c>
-      <c r="K124" s="6" t="s">
+      <c r="O125" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="L124" s="4" t="s">
+      <c r="P125" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
+    <row r="126" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
         <v>118</v>
       </c>
-      <c r="D125" t="s">
+      <c r="H126" t="s">
         <v>71</v>
       </c>
-      <c r="H125" s="10" t="s">
+      <c r="L126" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I125" s="13">
+      <c r="M126" s="13">
         <v>4.3591310772039646</v>
       </c>
-      <c r="K125" s="6" t="s">
+      <c r="O126" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="L125" s="6" t="s">
+      <c r="P126" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H126" s="10"/>
-      <c r="I126" s="13"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
-    </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D127" t="s">
+    <row r="127" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L127" s="10"/>
+      <c r="M127" s="13"/>
+      <c r="O127" s="6"/>
+      <c r="P127" s="6"/>
+    </row>
+    <row r="128" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H128" t="s">
         <v>120</v>
       </c>
-      <c r="H127" s="10" t="s">
+      <c r="L128" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I127" s="13">
+      <c r="M128" s="13">
         <v>14.6</v>
       </c>
-      <c r="K127" s="6"/>
-      <c r="L127" s="4" t="s">
+      <c r="O128" s="6"/>
+      <c r="P128" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D128" t="s">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H129" t="s">
         <v>124</v>
       </c>
-      <c r="F128" t="s">
+      <c r="J129" t="s">
         <v>121</v>
       </c>
-      <c r="H128" s="10" t="s">
+      <c r="L129" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I128" s="13">
+      <c r="M129" s="13">
         <v>37.744765138888887</v>
       </c>
-      <c r="K128" s="6"/>
-      <c r="L128" s="6" t="s">
+      <c r="O129" s="6"/>
+      <c r="P129" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D129" t="s">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H130" t="s">
         <v>124</v>
       </c>
-      <c r="F129" t="s">
+      <c r="J130" t="s">
         <v>122</v>
       </c>
-      <c r="H129" s="10" t="s">
+      <c r="L130" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I129" s="13">
+      <c r="M130" s="13">
         <v>50.107162083333336</v>
       </c>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6" t="s">
+      <c r="O130" s="6"/>
+      <c r="P130" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D130" t="s">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H131" t="s">
         <v>124</v>
       </c>
-      <c r="F130" t="s">
+      <c r="J131" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="10" t="s">
+      <c r="L131" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I130" s="13">
+      <c r="M131" s="13">
         <v>36.955675972222224</v>
       </c>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6" t="s">
+      <c r="O131" s="6"/>
+      <c r="P131" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H131" s="10"/>
-      <c r="I131" s="13"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D132" t="s">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L132" s="10"/>
+      <c r="M132" s="13"/>
+      <c r="O132" s="6"/>
+      <c r="P132" s="6"/>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H133" t="s">
         <v>131</v>
       </c>
-      <c r="H132" s="10" t="s">
+      <c r="L133" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I132" s="13">
+      <c r="M133" s="13">
         <v>1.6176327916666666</v>
       </c>
-      <c r="K132" s="6" t="s">
+      <c r="O133" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="L132" s="4" t="s">
+      <c r="P133" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D133" t="s">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H134" t="s">
         <v>132</v>
       </c>
-      <c r="H133" s="10" t="s">
+      <c r="L134" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I133" s="13">
+      <c r="M134" s="13">
         <v>3.0774477499999997</v>
       </c>
-      <c r="K133" s="6" t="s">
+      <c r="O134" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="L133" s="4" t="s">
+      <c r="P134" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D134" t="s">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H135" t="s">
         <v>133</v>
       </c>
-      <c r="H134" s="10" t="s">
+      <c r="L135" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I134" s="13">
+      <c r="M135" s="13">
         <v>0.25</v>
       </c>
-      <c r="K134" s="6" t="s">
+      <c r="O135" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="L134" s="4" t="s">
+      <c r="P135" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="8"/>
-      <c r="I136" s="8"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="8"/>
-      <c r="L136" s="8"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H137" s="9" t="s">
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
+      <c r="N137" s="8"/>
+      <c r="O137" s="8"/>
+      <c r="P137" s="8"/>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L138" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I137" s="9">
+      <c r="M138" s="9">
         <v>0</v>
       </c>
-      <c r="K137" s="9" t="s">
+      <c r="O138" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H138" t="s">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L139" t="s">
         <v>49</v>
       </c>
-      <c r="I138" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="8"/>
-      <c r="I140" s="8"/>
-      <c r="J140" s="8"/>
-      <c r="K140" s="8"/>
-      <c r="L140" s="8"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H141" s="9" t="s">
+      <c r="M139" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
+      <c r="K141" s="1"/>
+      <c r="L141" s="8"/>
+      <c r="M141" s="8"/>
+      <c r="N141" s="8"/>
+      <c r="O141" s="8"/>
+      <c r="P141" s="8"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L142" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="M142" s="9">
+        <v>0</v>
+      </c>
+      <c r="N142" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="I141" s="9">
+      <c r="O142" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>160</v>
+      </c>
+      <c r="L143" t="s">
+        <v>167</v>
+      </c>
+      <c r="M143">
+        <v>302</v>
+      </c>
+      <c r="N143" t="s">
+        <v>168</v>
+      </c>
+      <c r="O143" t="s">
+        <v>169</v>
+      </c>
+      <c r="P143" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>161</v>
+      </c>
+      <c r="L144" t="s">
+        <v>167</v>
+      </c>
+      <c r="M144">
+        <v>197</v>
+      </c>
+      <c r="N144" t="s">
+        <v>168</v>
+      </c>
+      <c r="O144" t="s">
+        <v>170</v>
+      </c>
+      <c r="P144" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>162</v>
+      </c>
+      <c r="L145" t="s">
+        <v>167</v>
+      </c>
+      <c r="M145">
+        <v>216</v>
+      </c>
+      <c r="N145" t="s">
+        <v>168</v>
+      </c>
+      <c r="O145" t="s">
+        <v>171</v>
+      </c>
+      <c r="P145" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>163</v>
+      </c>
+      <c r="L146" t="s">
+        <v>167</v>
+      </c>
+      <c r="M146">
+        <v>216</v>
+      </c>
+      <c r="N146" t="s">
+        <v>168</v>
+      </c>
+      <c r="O146" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>164</v>
+      </c>
+      <c r="L147" t="s">
+        <v>167</v>
+      </c>
+      <c r="M147">
+        <v>216</v>
+      </c>
+      <c r="N147" t="s">
+        <v>168</v>
+      </c>
+      <c r="O147" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>165</v>
+      </c>
+      <c r="L148" t="s">
+        <v>167</v>
+      </c>
+      <c r="M148">
+        <v>216</v>
+      </c>
+      <c r="N148" t="s">
+        <v>168</v>
+      </c>
+      <c r="O148" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>166</v>
+      </c>
+      <c r="L149" t="s">
+        <v>167</v>
+      </c>
+      <c r="M149">
+        <v>216</v>
+      </c>
+      <c r="N149" t="s">
+        <v>168</v>
+      </c>
+      <c r="O149" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+      <c r="L151" s="8"/>
+      <c r="M151" s="8"/>
+      <c r="N151" s="8"/>
+      <c r="O151" s="8"/>
+      <c r="P151" s="8"/>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L152" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="M152" s="9">
         <v>0</v>
       </c>
-      <c r="J141" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="K141" s="9" t="s">
+      <c r="N152" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="O152" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
-        <v>161</v>
-      </c>
-      <c r="H142" t="s">
-        <v>168</v>
-      </c>
-      <c r="I142">
-        <v>302</v>
-      </c>
-      <c r="J142" t="s">
-        <v>169</v>
-      </c>
-      <c r="K142" t="s">
-        <v>170</v>
-      </c>
-      <c r="L142" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
-        <v>162</v>
-      </c>
-      <c r="H143" t="s">
-        <v>168</v>
-      </c>
-      <c r="I143">
-        <v>197</v>
-      </c>
-      <c r="J143" t="s">
-        <v>169</v>
-      </c>
-      <c r="K143" t="s">
-        <v>171</v>
-      </c>
-      <c r="L143" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
-        <v>163</v>
-      </c>
-      <c r="H144" t="s">
-        <v>168</v>
-      </c>
-      <c r="I144">
-        <v>216</v>
-      </c>
-      <c r="J144" t="s">
-        <v>169</v>
-      </c>
-      <c r="K144" t="s">
-        <v>172</v>
-      </c>
-      <c r="L144" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B145" t="s">
-        <v>164</v>
-      </c>
-      <c r="H145" t="s">
-        <v>168</v>
-      </c>
-      <c r="I145">
-        <v>216</v>
-      </c>
-      <c r="J145" t="s">
-        <v>169</v>
-      </c>
-      <c r="K145" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B146" t="s">
-        <v>165</v>
-      </c>
-      <c r="H146" t="s">
-        <v>168</v>
-      </c>
-      <c r="I146">
-        <v>216</v>
-      </c>
-      <c r="J146" t="s">
-        <v>169</v>
-      </c>
-      <c r="K146" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B147" t="s">
-        <v>166</v>
-      </c>
-      <c r="H147" t="s">
-        <v>168</v>
-      </c>
-      <c r="I147">
-        <v>216</v>
-      </c>
-      <c r="J147" t="s">
-        <v>169</v>
-      </c>
-      <c r="K147" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>167</v>
-      </c>
-      <c r="H148" t="s">
-        <v>168</v>
-      </c>
-      <c r="I148">
-        <v>216</v>
-      </c>
-      <c r="J148" t="s">
-        <v>169</v>
-      </c>
-      <c r="K148" t="s">
-        <v>172</v>
-      </c>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L153" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M153" s="9">
+        <v>0</v>
+      </c>
+      <c r="N153" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O153" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>203</v>
+      </c>
+      <c r="C155" t="s">
+        <v>201</v>
+      </c>
+      <c r="D155" t="s">
+        <v>211</v>
+      </c>
+      <c r="E155" t="s">
+        <v>212</v>
+      </c>
+      <c r="F155" t="s">
+        <v>239</v>
+      </c>
+      <c r="L155" t="s">
+        <v>237</v>
+      </c>
+      <c r="M155" s="25">
+        <f>'energy stables'!E27</f>
+        <v>3.5302245250431775E-2</v>
+      </c>
+      <c r="N155" t="s">
+        <v>206</v>
+      </c>
+      <c r="O155" t="s">
+        <v>221</v>
+      </c>
+      <c r="P155" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>207</v>
+      </c>
+      <c r="C156" t="s">
+        <v>201</v>
+      </c>
+      <c r="D156" t="s">
+        <v>211</v>
+      </c>
+      <c r="E156" t="s">
+        <v>212</v>
+      </c>
+      <c r="L156" t="s">
+        <v>235</v>
+      </c>
+      <c r="M156" s="24">
+        <f>'energy stables'!D29</f>
+        <v>308.33833333333342</v>
+      </c>
+      <c r="N156" t="s">
+        <v>208</v>
+      </c>
+      <c r="O156" t="s">
+        <v>244</v>
+      </c>
+      <c r="P156" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>205</v>
+      </c>
+      <c r="C157" t="s">
+        <v>201</v>
+      </c>
+      <c r="D157" t="s">
+        <v>211</v>
+      </c>
+      <c r="E157" t="s">
+        <v>212</v>
+      </c>
+      <c r="F157" t="s">
+        <v>239</v>
+      </c>
+      <c r="L157" t="s">
+        <v>237</v>
+      </c>
+      <c r="M157" s="25">
+        <f>'energy stables'!E30</f>
+        <v>4.1036269430051814E-2</v>
+      </c>
+      <c r="N157" t="s">
+        <v>206</v>
+      </c>
+      <c r="P157" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>203</v>
+      </c>
+      <c r="C159" t="s">
+        <v>201</v>
+      </c>
+      <c r="L159" t="s">
+        <v>235</v>
+      </c>
+      <c r="M159" s="24">
+        <f>'energy stables'!D32</f>
+        <v>170.33333333333331</v>
+      </c>
+      <c r="N159" t="s">
+        <v>208</v>
+      </c>
+      <c r="O159" t="s">
+        <v>221</v>
+      </c>
+      <c r="P159" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>207</v>
+      </c>
+      <c r="C160" t="s">
+        <v>201</v>
+      </c>
+      <c r="L160" t="s">
+        <v>235</v>
+      </c>
+      <c r="M160" s="24">
+        <f>'energy stables'!D34</f>
+        <v>332.32333333333338</v>
+      </c>
+      <c r="N160" t="s">
+        <v>208</v>
+      </c>
+      <c r="O160" t="s">
+        <v>244</v>
+      </c>
+      <c r="P160" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="161" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M161" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3557,7 +4124,598 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
+  <dimension ref="B2:J35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="27"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" s="31">
+        <v>150</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="4">
+        <v>220</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="31">
+        <v>150</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="4">
+        <v>220</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="32"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" s="31">
+        <v>10500</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="4">
+        <v>8800</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="32"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="31"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="32"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="31">
+        <v>652</v>
+      </c>
+      <c r="E14" s="33">
+        <f>D14*(2/3)</f>
+        <v>434.66666666666663</v>
+      </c>
+      <c r="F14" s="34">
+        <f>D14*(1/3)</f>
+        <v>217.33333333333331</v>
+      </c>
+      <c r="G14" s="4">
+        <v>370</v>
+      </c>
+      <c r="H14" s="33">
+        <f>G14*(2/3)</f>
+        <v>246.66666666666666</v>
+      </c>
+      <c r="I14" s="34">
+        <f>G14*(1/3)</f>
+        <v>123.33333333333333</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="31">
+        <v>3</v>
+      </c>
+      <c r="E15" s="33">
+        <f>(E$21-E$14-E$16-E$18) * (D15/SUM(D$15,D$17,D$19))</f>
+        <v>2.1908735632183913</v>
+      </c>
+      <c r="F15" s="34">
+        <f>(F$21-F$14-F$16-F$18) * (D15/SUM(D$15,D$17,D$19))</f>
+        <v>0.80912643678160945</v>
+      </c>
+      <c r="G15" s="4">
+        <v>74</v>
+      </c>
+      <c r="H15" s="33">
+        <f>(H$21-H$14-H$16-H$18) * (G15/SUM(G$15,G$17,G$19))</f>
+        <v>42.039127163280675</v>
+      </c>
+      <c r="I15" s="34">
+        <f>(I$21-I$14-I$16-I$18) * (G15/SUM(G$15,G$17,G$19))</f>
+        <v>31.960872836719343</v>
+      </c>
+      <c r="J15" s="26"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="31">
+        <v>40</v>
+      </c>
+      <c r="E16" s="33">
+        <f>D16*(2/3)</f>
+        <v>26.666666666666664</v>
+      </c>
+      <c r="F16" s="34">
+        <f>D16*(1/3)</f>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="G16" s="4">
+        <v>31</v>
+      </c>
+      <c r="H16" s="33">
+        <f>G16*(2/3)</f>
+        <v>20.666666666666664</v>
+      </c>
+      <c r="I16" s="34">
+        <f>G16*(1/3)</f>
+        <v>10.333333333333332</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="31">
+        <v>216</v>
+      </c>
+      <c r="E17" s="33">
+        <f>(E$21-E$14-E$16-E$18) * (D17/SUM(D$15,D$17,D$19))</f>
+        <v>157.74289655172416</v>
+      </c>
+      <c r="F17" s="34">
+        <f>(F$21-F$14-F$16-F$18) * (D17/SUM(D$15,D$17,D$19))</f>
+        <v>58.257103448275878</v>
+      </c>
+      <c r="G17" s="4">
+        <v>224</v>
+      </c>
+      <c r="H17" s="33">
+        <f>(H$21-H$14-H$16-H$18) * (G17/SUM(G$15,G$17,G$19))</f>
+        <v>127.25357411587665</v>
+      </c>
+      <c r="I17" s="34">
+        <f>(I$21-I$14-I$16-I$18) * (G17/SUM(G$15,G$17,G$19))</f>
+        <v>96.746425884123411</v>
+      </c>
+      <c r="J17" s="26"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="31">
+        <v>386</v>
+      </c>
+      <c r="E18" s="33">
+        <f>D18</f>
+        <v>386</v>
+      </c>
+      <c r="F18" s="34">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>406</v>
+      </c>
+      <c r="H18" s="33">
+        <f>G18</f>
+        <v>406</v>
+      </c>
+      <c r="I18" s="34">
+        <v>0</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" s="31">
+        <v>216</v>
+      </c>
+      <c r="E19" s="33">
+        <f>(E$21-E$14-E$16-E$18) * (D19/SUM(D$15,D$17,D$19))</f>
+        <v>157.74289655172416</v>
+      </c>
+      <c r="F19" s="34">
+        <f>(F$21-F$14-F$16-F$18) * (D19/SUM(D$15,D$17,D$19))</f>
+        <v>58.257103448275878</v>
+      </c>
+      <c r="G19" s="4">
+        <v>145</v>
+      </c>
+      <c r="H19" s="33">
+        <f>(H$21-H$14-H$16-H$18) * (G19/SUM(G$15,G$17,G$19))</f>
+        <v>82.373965387509429</v>
+      </c>
+      <c r="I19" s="34">
+        <f>(I$21-I$14-I$16-I$18) * (G19/SUM(G$15,G$17,G$19))</f>
+        <v>62.626034612490599</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="31"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" s="36">
+        <f>SUM(D14:D19)</f>
+        <v>1513</v>
+      </c>
+      <c r="E21" s="38">
+        <f t="shared" ref="E21" si="0">D21*(1-D$24/100)</f>
+        <v>1165.01</v>
+      </c>
+      <c r="F21" s="39">
+        <f>D21*(D$24/100)</f>
+        <v>347.99</v>
+      </c>
+      <c r="G21" s="37">
+        <f>SUM(G14:G19)</f>
+        <v>1250</v>
+      </c>
+      <c r="H21" s="38">
+        <f t="shared" ref="H21" si="1">G21*(1-G$24/100)</f>
+        <v>925</v>
+      </c>
+      <c r="I21" s="39">
+        <f>G21*(G$24/100)</f>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" s="31">
+        <v>868</v>
+      </c>
+      <c r="E22" s="33">
+        <f>SUM(E15:E19)</f>
+        <v>730.34333333333336</v>
+      </c>
+      <c r="F22" s="34">
+        <f>SUM(F15:F19)</f>
+        <v>130.65666666666669</v>
+      </c>
+      <c r="G22" s="4">
+        <v>994</v>
+      </c>
+      <c r="H22" s="33">
+        <f>SUM(H15:H19)</f>
+        <v>678.33333333333337</v>
+      </c>
+      <c r="I22" s="34">
+        <f>SUM(I15:I19)</f>
+        <v>201.66666666666669</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="31"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="48">
+        <f t="shared" ref="D23:I23" si="2">D22/D21</f>
+        <v>0.57369464639788503</v>
+      </c>
+      <c r="E23" s="40">
+        <f t="shared" si="2"/>
+        <v>0.62689876767867514</v>
+      </c>
+      <c r="F23" s="41">
+        <f t="shared" si="2"/>
+        <v>0.37546098067952149</v>
+      </c>
+      <c r="G23" s="40">
+        <f t="shared" si="2"/>
+        <v>0.79520000000000002</v>
+      </c>
+      <c r="H23" s="40">
+        <f t="shared" si="2"/>
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="I23" s="41">
+        <f t="shared" si="2"/>
+        <v>0.62051282051282053</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="42">
+        <v>23</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="14">
+        <v>26</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="43"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="27"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="44">
+        <f>(E14+H14)/(D12+G12)</f>
+        <v>3.5302245250431775E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D29" s="35">
+        <f>SUM(E15:E17,E19,H15:H17,H19)/2</f>
+        <v>308.33833333333342</v>
+      </c>
+      <c r="E29" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="44">
+        <f>(E18+H18)/(D12+G12)</f>
+        <v>4.1036269430051814E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="31"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="32"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="35">
+        <f>SUM(F14,I14)/2</f>
+        <v>170.33333333333331</v>
+      </c>
+      <c r="E32" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D34" s="35">
+        <f>SUM(F15:F17,F19,I15:I17,I19)</f>
+        <v>332.32333333333338</v>
+      </c>
+      <c r="E34" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="43">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -3610,6 +4768,11 @@
         <v>147</v>
       </c>
     </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
+++ b/data/prod_parameters/MachineryAndEnergyMgmt.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18240" windowHeight="10650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="10650"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
     <sheet name="energy stables" sheetId="3" r:id="rId2"/>
-    <sheet name="references" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
+    <sheet name="references" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,8 +22,462 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="M41" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+FTS avd 36W/box, Sin o betäckning 25W/djurplats</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N41" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Grisn. avd. 36 W/box, Betäckn. avd 17 W/djurplats, Sinavdelning 10 W/djurplats.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O41" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+18 W/box</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P41" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Grisn.avd 25,2W7box, Tillväxtavd. 28,8 W/box. Sin- och bet.- avdn. 11,8 W/djurplats,
+slaktsvinsstall 2,2 W/djurplats.* SIP= sugga i produktion</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M42" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+olja</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N42" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+värmepump</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O42" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+olja (före insättning)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M52" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Drankpump</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N52" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Kvarn</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+FTS avd 36W/box, Sin o betäckning 25W/djurplats</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Grisn. avd. 36 W/box, Betäckn. avd 17 W/djurplats, Sinavdelning 10 W/djurplats.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+18 W/box</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Grisn.avd 25,2W7box, Tillväxtavd. 28,8 W/box. Sin- och bet.- avdn. 11,8 W/djurplats,
+slaktsvinsstall 2,2 W/djurplats.* SIP= sugga i produktion</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+olja</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+värmepump</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+olja (före insättning)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Drankpump</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G17" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Kvarn</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="332">
   <si>
     <t>f_crop</t>
   </si>
@@ -752,9 +1208,6 @@
     <t>stable misc</t>
   </si>
   <si>
-    <t>kWh/head</t>
-  </si>
-  <si>
     <t>f_breed</t>
   </si>
   <si>
@@ -824,12 +1277,6 @@
     <t>recr.</t>
   </si>
   <si>
-    <t>per head</t>
-  </si>
-  <si>
-    <t>per kg milk</t>
-  </si>
-  <si>
     <t>&lt;--- Assumes double feed consuption for dairy cows compared to recruitment</t>
   </si>
   <si>
@@ -851,57 +1298,359 @@
     <t>&lt;--- Milking only dairy cows</t>
   </si>
   <si>
+    <t>Hörndahl, Torsten &amp; Neuman, Lars. (2012). Energiförbrukning I jordbrukets driftsbyggnader - En kartläggning av 16 gårdar 2005-2006 kompletterat med mätningar på två gårdar 2010-2012. Sveriges lantbruksuniversitet Fakulteten för landskapsplanering, trädgårds- och jordbruksvetenskap. Rapport 2012:19</t>
+  </si>
+  <si>
+    <t>Hörndahl &amp; Neuman (2012)</t>
+  </si>
+  <si>
+    <t>manure, lighting, ventilation, etc.</t>
+  </si>
+  <si>
+    <t>poultry</t>
+  </si>
+  <si>
+    <t>broiler</t>
+  </si>
+  <si>
+    <t>feeding, manure</t>
+  </si>
+  <si>
+    <t>lighting, ventilation</t>
+  </si>
+  <si>
+    <r>
+      <t>feeding |</t>
+    </r>
     <r>
       <rPr>
-        <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Hörndahl, Torsten &amp; Neuman, Lars</t>
+      <t xml:space="preserve"> based on energy use for dairy recruitement animals</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">manure, lighting, ventilation, etc. | </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">. (2012). </t>
+      <t>based on energy use for dairy recruitement animals</t>
+    </r>
+  </si>
+  <si>
+    <t>broilers</t>
+  </si>
+  <si>
+    <t>pigs</t>
+  </si>
+  <si>
+    <t>Pigs</t>
+  </si>
+  <si>
+    <t>Baky, A., Sundberg, M., Brown, N. (2010). Kartläggning av jordbrukets energianvändning - Ett projekt utfört på uppdrag av Jordbruksverket. JTI Rapport</t>
+  </si>
+  <si>
+    <t>Fördelning energislag, kWh</t>
+  </si>
+  <si>
+    <t>E01</t>
+  </si>
+  <si>
+    <t>Per smågris</t>
+  </si>
+  <si>
+    <t>Per slaktgris</t>
+  </si>
+  <si>
+    <t>Total energi</t>
+  </si>
+  <si>
+    <t>El</t>
+  </si>
+  <si>
+    <t>Biobränsle</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Landquist et al (2020)</t>
+  </si>
+  <si>
+    <t>Beskrivning</t>
+  </si>
+  <si>
+    <t>Uppvärmning värmkälla</t>
+  </si>
+  <si>
+    <t>Ej spec värmepump</t>
+  </si>
+  <si>
+    <t>Övrigt</t>
+  </si>
+  <si>
+    <t>Utfodring</t>
+  </si>
+  <si>
+    <t>Ventilation</t>
+  </si>
+  <si>
+    <t>9,6</t>
+  </si>
+  <si>
+    <t>Ej spec</t>
+  </si>
+  <si>
+    <t>Utgödsling</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>43,2</t>
+  </si>
+  <si>
+    <t>992
+olja</t>
+  </si>
+  <si>
+    <t>93
+värmepump</t>
+  </si>
+  <si>
+    <t>4,2
+olja (före insättning)</t>
+  </si>
+  <si>
+    <t>Vatten</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ingår i
+</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
       </rPr>
-      <t>Energiförbrukning I jordbrukets driftsbyggnader - En kartläggning av 16 gårdar 2005-2006 kompletterat med mätningar på två gårdar 2010-2012</t>
+      <t>Övrigt</t>
+    </r>
+  </si>
+  <si>
+    <t>Ingår ej</t>
+  </si>
+  <si>
+    <t>Ingår</t>
+  </si>
+  <si>
+    <t>Tvätt</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>Rekrytering, totalt</t>
+  </si>
+  <si>
+    <t>Personal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ingår i </t>
     </r>
     <r>
       <rPr>
+        <i/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
       </rPr>
-      <t>. Sveriges lantbruksuniversitet Fakulteten för landskapsplanering, trädgårds- och jordbruksvetenskap. Rapport 2012:19</t>
+      <t>Övrigt</t>
     </r>
   </si>
   <si>
-    <t>Hörndahl, Torsten &amp; Neuman, Lars. (2012). Energiförbrukning I jordbrukets driftsbyggnader - En kartläggning av 16 gårdar 2005-2006 kompletterat med mätningar på två gårdar 2010-2012. Sveriges lantbruksuniversitet Fakulteten för landskapsplanering, trädgårds- och jordbruksvetenskap. Rapport 2012:19</t>
-  </si>
-  <si>
-    <t>Hörndahl &amp; Neuman (2012)</t>
-  </si>
-  <si>
-    <t>manure, lighting, ventilation, etc.</t>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>Summa</t>
+  </si>
+  <si>
+    <t>19,7</t>
+  </si>
+  <si>
+    <t>Därav el</t>
+  </si>
+  <si>
+    <t>15,5</t>
+  </si>
+  <si>
+    <t>Övrig utrustning                  23
+Drankpump</t>
+  </si>
+  <si>
+    <t>38
+Kvarn</t>
+  </si>
+  <si>
+    <t>-                                  Kvarn ingår i
+utfodringen</t>
+  </si>
+  <si>
+    <t>Betäcknings avd</t>
+  </si>
+  <si>
+    <t>Isolerad</t>
+  </si>
+  <si>
+    <t>Sin avd Slaktgris
+Byggår</t>
+  </si>
+  <si>
+    <t>Isolerad Isolerad
+1998</t>
+  </si>
+  <si>
+    <t>Oisolerad
+1999</t>
+  </si>
+  <si>
+    <t>-
+Isolerad 1998</t>
+  </si>
+  <si>
+    <t>Isolerad Isolerad
+2008</t>
+  </si>
+  <si>
+    <t>Belysning</t>
+  </si>
+  <si>
+    <t>2441)</t>
+  </si>
+  <si>
+    <t>782)</t>
+  </si>
+  <si>
+    <t>1,83)</t>
+  </si>
+  <si>
+    <t>3404)</t>
+  </si>
+  <si>
+    <t>Övrig utrustning</t>
+  </si>
+  <si>
+    <t>Gård</t>
+  </si>
+  <si>
+    <t>Hel intergrerad
+FTS-system
+96 SIP*
+kWh/SIP*, år</t>
+  </si>
+  <si>
+    <t>Enhetsbox
+480 SIP*
+kWh/SIP*, år</t>
+  </si>
+  <si>
+    <t>Slaktgris
+1160 platser
+kWh/djurpl, omg</t>
+  </si>
+  <si>
+    <t>Hel integrerad
+Tillväxtboxsyst.
+254 SIP*
+kWh/SIP*, år</t>
+  </si>
+  <si>
+    <t>Gård F</t>
+  </si>
+  <si>
+    <t>Gård G</t>
+  </si>
+  <si>
+    <t>Gård H</t>
+  </si>
+  <si>
+    <t>Gård Y</t>
+  </si>
+  <si>
+    <t>Kvarn ingår i
+utfodringen</t>
+  </si>
+  <si>
+    <t>Sin avd</t>
+  </si>
+  <si>
+    <t>Slaktgris</t>
+  </si>
+  <si>
+    <t>Byggår</t>
+  </si>
+  <si>
+    <t>Oisolerad</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Kvarn ingår i utfodringen</t>
+  </si>
+  <si>
+    <t>Därav ej el</t>
+  </si>
+  <si>
+    <t>kWh/head/year</t>
+  </si>
+  <si>
+    <t>Per SIP</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>piglets</t>
+  </si>
+  <si>
+    <t>Energy source</t>
+  </si>
+  <si>
+    <t>Used values</t>
+  </si>
+  <si>
+    <t>growing pigs</t>
+  </si>
+  <si>
+    <t>kWh per</t>
+  </si>
+  <si>
+    <t>ins. animal</t>
+  </si>
+  <si>
+    <t>kWh/inserted head</t>
+  </si>
+  <si>
+    <t>stable_energy_use_per_inserted_head</t>
   </si>
 </sst>
 </file>
@@ -910,9 +1659,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1000,14 +1749,6 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1029,8 +1770,76 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1049,8 +1858,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1177,12 +1992,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1208,35 +2086,78 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1518,14 +2439,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T161"/>
+  <dimension ref="A1:T187"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="15" max="15" width="31.7109375" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.7109375" customWidth="1"/>
     <col min="16" max="16" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1540,13 +2461,13 @@
         <v>200</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>210</v>
-      </c>
       <c r="F1" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>148</v>
@@ -1678,6 +2599,9 @@
       <c r="A9" t="s">
         <v>203</v>
       </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
       <c r="G9" s="4" t="s">
         <v>26</v>
       </c>
@@ -1695,6 +2619,9 @@
       <c r="A10" t="s">
         <v>204</v>
       </c>
+      <c r="C10" t="s">
+        <v>201</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="L10" s="6"/>
       <c r="M10" s="10"/>
@@ -1703,6 +2630,9 @@
       <c r="A11" t="s">
         <v>207</v>
       </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
       <c r="G11" s="6" t="s">
         <v>150</v>
       </c>
@@ -1720,6 +2650,9 @@
       <c r="A12" t="s">
         <v>205</v>
       </c>
+      <c r="C12" t="s">
+        <v>201</v>
+      </c>
       <c r="G12" s="6" t="s">
         <v>150</v>
       </c>
@@ -1736,1429 +2669,1550 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G13" s="6"/>
       <c r="L13" s="6"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>153</v>
+        <v>203</v>
+      </c>
+      <c r="C14" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M14" s="11">
-        <v>6.4777062142923141</v>
+      <c r="M14" s="10">
+        <v>100</v>
       </c>
       <c r="N14" t="s">
         <v>128</v>
       </c>
-      <c r="P14" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>204</v>
+      </c>
+      <c r="C15" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" t="s">
+        <v>242</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M15" s="11">
-        <v>8.7567853491111922</v>
+      <c r="M15" s="10">
+        <v>100</v>
       </c>
       <c r="N15" t="s">
         <v>128</v>
       </c>
-      <c r="O15" t="s">
-        <v>175</v>
-      </c>
-      <c r="P15" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>207</v>
+      </c>
+      <c r="C16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" t="s">
+        <v>242</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M16" s="18">
-        <v>59.671114354829328</v>
+      <c r="M16" s="10">
+        <v>100</v>
       </c>
       <c r="N16" t="s">
         <v>128</v>
       </c>
-      <c r="O16" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="P16" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="M17" s="18">
-        <v>16.802918820320372</v>
-      </c>
-      <c r="N17" t="s">
-        <v>128</v>
-      </c>
+      <c r="G17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="10"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>157</v>
+        <v>203</v>
+      </c>
+      <c r="C18" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" t="s">
+        <v>324</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M18" s="11">
-        <v>7.4851294970113242</v>
+      <c r="M18" s="10">
+        <v>100</v>
       </c>
       <c r="N18" t="s">
         <v>128</v>
       </c>
+      <c r="P18" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>204</v>
+      </c>
+      <c r="C19" t="s">
+        <v>248</v>
+      </c>
+      <c r="E19" t="s">
+        <v>324</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M19" s="11">
-        <v>0.80634576443547301</v>
+      <c r="M19">
+        <v>4</v>
       </c>
       <c r="N19" t="s">
         <v>128</v>
       </c>
+      <c r="P19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M20">
+        <v>76</v>
+      </c>
+      <c r="N20" t="s">
+        <v>128</v>
+      </c>
+      <c r="P20" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J21" t="s">
-        <v>121</v>
-      </c>
-      <c r="L21" t="s">
-        <v>130</v>
-      </c>
-      <c r="M21" s="15">
-        <v>80</v>
+      <c r="A21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E21" t="s">
+        <v>324</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M21">
+        <v>20</v>
       </c>
       <c r="N21" t="s">
         <v>128</v>
       </c>
+      <c r="P21" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J22" t="s">
-        <v>122</v>
-      </c>
-      <c r="L22" t="s">
-        <v>130</v>
-      </c>
-      <c r="M22" s="15">
-        <v>10</v>
+      <c r="A22" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" t="s">
+        <v>324</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M22" s="10">
+        <v>100</v>
       </c>
       <c r="N22" t="s">
         <v>128</v>
       </c>
+      <c r="P22" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J23" t="s">
-        <v>123</v>
-      </c>
-      <c r="L23" t="s">
-        <v>130</v>
-      </c>
-      <c r="M23" s="15">
-        <v>10</v>
+      <c r="A23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" t="s">
+        <v>248</v>
+      </c>
+      <c r="E23" t="s">
+        <v>327</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="10">
+        <v>100</v>
       </c>
       <c r="N23" t="s">
         <v>128</v>
       </c>
+      <c r="P23" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" t="s">
+        <v>327</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24">
+        <v>20</v>
+      </c>
+      <c r="N24" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" t="s">
+        <v>248</v>
+      </c>
+      <c r="E25" t="s">
+        <v>327</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M25">
+        <v>60</v>
+      </c>
+      <c r="N25" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E26" t="s">
+        <v>327</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M26">
+        <v>20.000000000000018</v>
+      </c>
+      <c r="N26" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" t="s">
+        <v>248</v>
+      </c>
+      <c r="E27" t="s">
+        <v>327</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M27" s="10">
+        <v>100</v>
+      </c>
+      <c r="N27" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="15"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M29" s="11">
+        <v>6.4777062142923141</v>
+      </c>
+      <c r="N29" t="s">
+        <v>128</v>
+      </c>
+      <c r="P29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>158</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M30" s="11">
+        <v>8.7567853491111922</v>
+      </c>
+      <c r="N30" t="s">
+        <v>128</v>
+      </c>
+      <c r="O30" t="s">
+        <v>175</v>
+      </c>
+      <c r="P30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M31" s="18">
+        <v>59.671114354829328</v>
+      </c>
+      <c r="N31" t="s">
+        <v>128</v>
+      </c>
+      <c r="O31" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>158</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M32" s="18">
+        <v>16.802918820320372</v>
+      </c>
+      <c r="N32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M33" s="11">
+        <v>7.4851294970113242</v>
+      </c>
+      <c r="N33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M34" s="11">
+        <v>0.80634576443547301</v>
+      </c>
+      <c r="N34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J36" t="s">
+        <v>121</v>
+      </c>
+      <c r="L36" t="s">
+        <v>130</v>
+      </c>
+      <c r="M36" s="15">
+        <v>80</v>
+      </c>
+      <c r="N36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L37" t="s">
+        <v>130</v>
+      </c>
+      <c r="M37" s="15">
+        <v>10</v>
+      </c>
+      <c r="N37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J38" t="s">
+        <v>123</v>
+      </c>
+      <c r="L38" t="s">
+        <v>130</v>
+      </c>
+      <c r="M38" s="15">
+        <v>10</v>
+      </c>
+      <c r="N38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G25" s="4"/>
-      <c r="L25" s="9" t="s">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G40" s="4"/>
+      <c r="L40" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M40" s="23">
         <v>0</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9" t="s">
+      <c r="N40" s="9"/>
+      <c r="O40" s="9" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G26" s="4"/>
-      <c r="M26" s="18"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G27" s="4" t="s">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G41" s="4"/>
+      <c r="M41" s="18"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G42" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K42" t="s">
         <v>183</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L42" t="s">
         <v>182</v>
       </c>
-      <c r="M27" s="18">
+      <c r="M42" s="18">
         <f>74100</f>
         <v>74100</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N42" t="s">
         <v>192</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O42" t="s">
         <v>186</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P42" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G28" s="4" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G43" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K43" t="s">
         <v>190</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L43" t="s">
         <v>182</v>
       </c>
-      <c r="M28" s="11">
+      <c r="M43" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="N28" t="s">
+      <c r="N43" t="s">
         <v>192</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P43" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G29" s="4" t="s">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G44" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K44" t="s">
         <v>184</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L44" t="s">
         <v>182</v>
       </c>
-      <c r="M29" s="11">
+      <c r="M44" s="11">
         <f>3.9</f>
         <v>3.9</v>
       </c>
-      <c r="N29" t="s">
+      <c r="N44" t="s">
         <v>192</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P44" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G30" s="4" t="s">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G45" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K45" t="s">
         <v>183</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L45" t="s">
         <v>182</v>
       </c>
-      <c r="M30" s="18">
+      <c r="M45" s="18">
         <v>0</v>
       </c>
-      <c r="N30" t="s">
+      <c r="N45" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G31" s="4" t="s">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G46" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K46" t="s">
         <v>191</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L46" t="s">
         <v>182</v>
       </c>
-      <c r="M31" s="22">
-        <f t="shared" ref="M31:M32" si="0">M28</f>
+      <c r="M46" s="22">
+        <f t="shared" ref="M46:M47" si="0">M43</f>
         <v>3.9</v>
       </c>
-      <c r="N31" t="s">
+      <c r="N46" t="s">
         <v>192</v>
       </c>
-      <c r="O31" t="s">
+      <c r="O46" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G32" s="4" t="s">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G47" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K47" t="s">
         <v>184</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L47" t="s">
         <v>182</v>
       </c>
-      <c r="M32" s="22">
+      <c r="M47" s="22">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N47" t="s">
         <v>192</v>
       </c>
-      <c r="O32" t="s">
+      <c r="O47" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G33" s="6" t="s">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G48" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K48" t="s">
         <v>183</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L48" t="s">
         <v>182</v>
       </c>
-      <c r="M33" s="18">
+      <c r="M48" s="18">
         <v>73300</v>
       </c>
-      <c r="N33" t="s">
+      <c r="N48" t="s">
         <v>192</v>
       </c>
-      <c r="O33" t="s">
+      <c r="O48" t="s">
         <v>195</v>
       </c>
-      <c r="P33" t="s">
+      <c r="P48" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G34" s="6" t="s">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G49" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K49" t="s">
         <v>190</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L49" t="s">
         <v>182</v>
       </c>
-      <c r="M34">
+      <c r="M49">
         <v>10</v>
       </c>
-      <c r="N34" t="s">
+      <c r="N49" t="s">
         <v>192</v>
       </c>
-      <c r="P34" t="s">
+      <c r="P49" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G35" s="6" t="s">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G50" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K50" t="s">
         <v>184</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L50" t="s">
         <v>182</v>
       </c>
-      <c r="M35">
+      <c r="M50">
         <v>0.6</v>
       </c>
-      <c r="N35" t="s">
+      <c r="N50" t="s">
         <v>192</v>
       </c>
-      <c r="P35" t="s">
+      <c r="P50" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G36" s="6" t="s">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G51" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K51" t="s">
         <v>183</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L51" t="s">
         <v>182</v>
       </c>
-      <c r="M36" s="18">
+      <c r="M51" s="18">
         <v>56100</v>
       </c>
-      <c r="N36" t="s">
+      <c r="N51" t="s">
         <v>192</v>
       </c>
-      <c r="O36" t="s">
+      <c r="O51" t="s">
         <v>194</v>
       </c>
-      <c r="P36" t="s">
+      <c r="P51" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G37" s="6" t="s">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G52" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K52" t="s">
         <v>190</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L52" t="s">
         <v>182</v>
       </c>
-      <c r="M37">
+      <c r="M52">
         <v>5</v>
       </c>
-      <c r="N37" t="s">
+      <c r="N52" t="s">
         <v>192</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P52" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G38" s="6" t="s">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G53" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K53" t="s">
         <v>184</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L53" t="s">
         <v>182</v>
       </c>
-      <c r="M38">
+      <c r="M53">
         <v>0.1</v>
       </c>
-      <c r="N38" t="s">
+      <c r="N53" t="s">
         <v>192</v>
       </c>
-      <c r="P38" t="s">
+      <c r="P53" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G39" s="6" t="s">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G54" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K54" t="s">
         <v>183</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L54" t="s">
         <v>182</v>
       </c>
-      <c r="M39" s="18">
+      <c r="M54" s="18">
         <v>0</v>
       </c>
-      <c r="N39" t="s">
+      <c r="N54" t="s">
         <v>192</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O54" t="s">
         <v>193</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P54" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G40" s="6" t="s">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G55" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K55" t="s">
         <v>191</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L55" t="s">
         <v>182</v>
       </c>
-      <c r="M40" s="18">
+      <c r="M55" s="18">
         <v>300</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N55" t="s">
         <v>192</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P55" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G41" s="6" t="s">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G56" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K56" t="s">
         <v>184</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L56" t="s">
         <v>182</v>
       </c>
-      <c r="M41" s="18">
+      <c r="M56" s="18">
         <v>4</v>
       </c>
-      <c r="N41" t="s">
+      <c r="N56" t="s">
         <v>192</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P56" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G42" s="6" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G57" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L57" t="s">
         <v>182</v>
       </c>
-      <c r="M42" s="18">
+      <c r="M57" s="18">
         <v>0</v>
       </c>
-      <c r="N42" t="s">
+      <c r="N57" t="s">
         <v>192</v>
       </c>
-      <c r="O42" s="15"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G43" s="6" t="s">
+      <c r="O57" s="15"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G58" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L58" t="s">
         <v>182</v>
       </c>
-      <c r="M43" s="18">
+      <c r="M58" s="18">
         <v>0</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N58" t="s">
         <v>192</v>
       </c>
-      <c r="O43" s="15"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G44" s="4" t="s">
+      <c r="O58" s="15"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G59" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L59" t="s">
         <v>182</v>
       </c>
-      <c r="M44" s="18">
+      <c r="M59" s="18">
         <v>0</v>
       </c>
-      <c r="N44" t="s">
+      <c r="N59" t="s">
         <v>192</v>
       </c>
-      <c r="O44" s="15" t="s">
+      <c r="O59" s="15" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G45" s="6" t="s">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G60" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L60" t="s">
         <v>182</v>
       </c>
-      <c r="M45" s="18">
+      <c r="M60" s="18">
         <v>0</v>
       </c>
-      <c r="N45" t="s">
+      <c r="N60" t="s">
         <v>192</v>
       </c>
-      <c r="O45" s="15"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G46" s="6"/>
-      <c r="M46" s="18"/>
-      <c r="O46" s="15"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="O60" s="15"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G61" s="6"/>
+      <c r="M61" s="18"/>
+      <c r="O61" s="15"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4" t="s">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M49">
+      <c r="M64">
         <v>10800</v>
       </c>
-      <c r="N49" t="s">
+      <c r="N64" t="s">
         <v>11</v>
       </c>
-      <c r="O49" s="4" t="s">
+      <c r="O64" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4" t="s">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M50">
+      <c r="M65">
         <v>5</v>
       </c>
-      <c r="N50" t="s">
+      <c r="N65" t="s">
         <v>13</v>
       </c>
-      <c r="O50" s="4" t="s">
+      <c r="O65" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="6" t="s">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="M51">
+      <c r="M66">
         <v>2</v>
       </c>
-      <c r="N51" t="s">
+      <c r="N66" t="s">
         <v>126</v>
       </c>
-      <c r="O51" s="7"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4" t="s">
+      <c r="O66" s="7"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M52">
+      <c r="M67">
         <v>0.2</v>
       </c>
-      <c r="N52" t="s">
+      <c r="N67" t="s">
         <v>15</v>
       </c>
-      <c r="O52" s="4" t="s">
+      <c r="O67" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4" t="s">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M53">
+      <c r="M68">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="N53" t="s">
+      <c r="N68" t="s">
         <v>17</v>
       </c>
-      <c r="O53" s="5" t="s">
+      <c r="O68" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="6" t="s">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M54">
+      <c r="M69">
         <v>250</v>
       </c>
-      <c r="N54" t="s">
+      <c r="N69" t="s">
         <v>19</v>
       </c>
-      <c r="O54" s="5" t="s">
+      <c r="O69" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="20" t="s">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M55" s="9">
+      <c r="M70" s="9">
         <v>1</v>
       </c>
-      <c r="N55" s="9"/>
-      <c r="O55" s="21" t="s">
+      <c r="N70" s="9"/>
+      <c r="O70" s="21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4" t="s">
+    <row r="71" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="6" t="s">
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M56">
+      <c r="M71">
         <v>0.26</v>
       </c>
-      <c r="O56" s="5" t="s">
+      <c r="O71" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4" t="s">
+    <row r="72" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="6" t="s">
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M57">
+      <c r="M72">
         <v>0.26</v>
       </c>
-      <c r="O57" s="5" t="s">
+      <c r="O72" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4" t="s">
+    <row r="73" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="6" t="s">
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M58">
+      <c r="M73">
         <v>0.45</v>
       </c>
-      <c r="O58" s="5" t="s">
+      <c r="O73" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="6" t="s">
+    <row r="74" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6" t="s">
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M59">
+      <c r="M74">
         <v>0.76</v>
       </c>
-      <c r="O59" s="5" t="s">
+      <c r="O74" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="6" t="s">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M60">
+      <c r="M75">
         <v>4</v>
       </c>
-      <c r="N60" t="s">
+      <c r="N75" t="s">
         <v>21</v>
       </c>
-      <c r="O60" s="7" t="s">
+      <c r="O75" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L63" t="s">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L78" t="s">
         <v>127</v>
       </c>
-      <c r="M63">
+      <c r="M78">
         <v>4</v>
       </c>
-      <c r="N63" t="s">
+      <c r="N78" t="s">
         <v>29</v>
       </c>
-      <c r="O63" t="s">
+      <c r="O78" t="s">
         <v>28</v>
       </c>
-      <c r="T63" s="6"/>
-    </row>
-    <row r="64" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L64" t="s">
+      <c r="T78" s="6"/>
+    </row>
+    <row r="79" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L79" t="s">
         <v>45</v>
       </c>
-      <c r="M64">
+      <c r="M79">
         <v>0.9</v>
       </c>
-      <c r="O64" t="s">
+      <c r="O79" t="s">
         <v>30</v>
       </c>
-      <c r="T64" s="6"/>
-    </row>
-    <row r="65" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L65" t="s">
+      <c r="T79" s="6"/>
+    </row>
+    <row r="80" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L80" t="s">
         <v>38</v>
       </c>
-      <c r="M65">
+      <c r="M80">
         <v>1.2250000000000001</v>
       </c>
-      <c r="N65" t="s">
+      <c r="N80" t="s">
         <v>32</v>
       </c>
-      <c r="O65" t="s">
+      <c r="O80" t="s">
         <v>31</v>
       </c>
-      <c r="T65" s="6"/>
-    </row>
-    <row r="66" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L66" t="s">
+      <c r="T80" s="6"/>
+    </row>
+    <row r="81" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L81" t="s">
         <v>39</v>
       </c>
-      <c r="M66">
+      <c r="M81">
         <v>0.1</v>
       </c>
-      <c r="O66" t="s">
+      <c r="O81" t="s">
         <v>33</v>
       </c>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L67" t="s">
+      <c r="T81" s="6"/>
+    </row>
+    <row r="82" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L82" t="s">
         <v>40</v>
       </c>
-      <c r="M67">
+      <c r="M82">
         <v>0.01</v>
       </c>
-      <c r="O67" t="s">
+      <c r="O82" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L68" t="s">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L83" t="s">
         <v>41</v>
       </c>
-      <c r="M68">
+      <c r="M83">
         <v>0.2</v>
       </c>
-      <c r="O68" t="s">
+      <c r="O83" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L69" t="s">
+    <row r="84" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L84" t="s">
         <v>42</v>
       </c>
-      <c r="M69">
+      <c r="M84">
         <v>0.8</v>
       </c>
-      <c r="O69" t="s">
+      <c r="O84" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="L70" t="s">
+    <row r="85" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="L85" t="s">
         <v>43</v>
       </c>
-      <c r="M70">
+      <c r="M85">
         <v>55</v>
       </c>
-      <c r="O70" t="s">
+      <c r="O85" t="s">
         <v>37</v>
       </c>
-      <c r="S70" s="4"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="S85" s="4"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-      <c r="P72" s="8"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L73" s="9" t="s">
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+      <c r="N87" s="8"/>
+      <c r="O87" s="8"/>
+      <c r="P87" s="8"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L88" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M73" s="9">
+      <c r="M88" s="9">
         <v>0</v>
       </c>
-      <c r="N73" s="9" t="s">
+      <c r="N88" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O73" s="9"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L74" s="9" t="s">
+      <c r="O88" s="9"/>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L89" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="M74" s="9">
+      <c r="M89" s="9">
         <v>0</v>
       </c>
-      <c r="N74" s="9" t="s">
+      <c r="N89" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O74" s="9"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L75" s="9" t="s">
+      <c r="O89" s="9"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L90" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="M75" s="9">
+      <c r="M90" s="9">
         <v>0</v>
       </c>
-      <c r="N75" s="9" t="s">
+      <c r="N90" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O75" s="9"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L76" s="9" t="s">
+      <c r="O90" s="9"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L91" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M76" s="9">
+      <c r="M91" s="9">
         <v>0</v>
       </c>
-      <c r="N76" s="9" t="s">
+      <c r="N91" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="O76" s="9"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L77" s="9" t="s">
+      <c r="O91" s="9"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L92" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="M77" s="9">
+      <c r="M92" s="9">
         <v>0</v>
       </c>
-      <c r="N77" s="9" t="s">
+      <c r="N92" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O77" s="9"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L78" s="9" t="s">
+      <c r="O92" s="9"/>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L93" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="M78" s="9">
+      <c r="M93" s="9">
         <v>1</v>
       </c>
-      <c r="N78" s="9" t="s">
+      <c r="N93" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O78" s="9" t="s">
+      <c r="O93" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L79" s="9" t="s">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L94" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M79" s="9">
+      <c r="M94" s="9">
         <v>0</v>
       </c>
-      <c r="N79" s="9" t="s">
+      <c r="N94" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O79" s="9"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L80" s="9" t="s">
+      <c r="O94" s="9"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L95" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M80" s="9">
+      <c r="M95" s="9">
         <v>0</v>
       </c>
-      <c r="N80" s="9" t="s">
+      <c r="N95" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="O80" s="9"/>
-    </row>
-    <row r="81" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L81" s="9" t="s">
+      <c r="O95" s="9"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L96" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="M81" s="9">
+      <c r="M96" s="9">
         <v>0</v>
       </c>
-      <c r="N81" s="9" t="s">
+      <c r="N96" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="O81" s="9"/>
-    </row>
-    <row r="82" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L82" s="9" t="s">
+      <c r="O96" s="9"/>
+    </row>
+    <row r="97" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L97" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M82" s="9">
+      <c r="M97" s="9">
         <v>0</v>
       </c>
-      <c r="N82" s="9" t="s">
+      <c r="N97" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="O82" s="9"/>
-    </row>
-    <row r="83" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L83" s="9"/>
-      <c r="M83" s="9"/>
-      <c r="N83" s="9"/>
-      <c r="O83" s="9"/>
-    </row>
-    <row r="84" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H84" t="s">
+      <c r="O97" s="9"/>
+    </row>
+    <row r="98" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+      <c r="N98" s="9"/>
+      <c r="O98" s="9"/>
+    </row>
+    <row r="99" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H99" t="s">
         <v>60</v>
       </c>
-      <c r="L84" s="10" t="s">
+      <c r="L99" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="M84" s="10">
+      <c r="M99" s="10">
         <v>364</v>
       </c>
-      <c r="N84" s="10"/>
-      <c r="O84" s="10" t="s">
+      <c r="N99" s="10"/>
+      <c r="O99" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="P84" s="10"/>
-    </row>
-    <row r="85" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H85" t="s">
-        <v>60</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="M85" s="10">
-        <v>18.8</v>
-      </c>
-      <c r="N85" s="10"/>
-      <c r="O85" s="10"/>
-      <c r="P85" s="10"/>
-    </row>
-    <row r="86" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H86" t="s">
-        <v>60</v>
-      </c>
-      <c r="L86" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="M86" s="10">
-        <v>0</v>
-      </c>
-      <c r="N86" s="10"/>
-      <c r="O86" s="10"/>
-      <c r="P86" s="10"/>
-    </row>
-    <row r="87" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H87" t="s">
-        <v>60</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M87" s="10">
-        <v>10</v>
-      </c>
-      <c r="N87" s="10"/>
-      <c r="O87" s="10"/>
-      <c r="P87" s="10"/>
-    </row>
-    <row r="88" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H88" t="s">
-        <v>60</v>
-      </c>
-      <c r="I88" t="s">
-        <v>74</v>
-      </c>
-      <c r="L88" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M88" s="12">
-        <v>1</v>
-      </c>
-      <c r="N88" s="10"/>
-      <c r="O88" s="10"/>
-      <c r="P88" s="10"/>
-    </row>
-    <row r="89" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H89" t="s">
-        <v>60</v>
-      </c>
-      <c r="I89" t="s">
-        <v>73</v>
-      </c>
-      <c r="L89" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M89" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="N89" s="10"/>
-      <c r="O89" s="10"/>
-      <c r="P89" s="10"/>
-    </row>
-    <row r="90" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H90" t="s">
-        <v>60</v>
-      </c>
-      <c r="I90" t="s">
-        <v>72</v>
-      </c>
-      <c r="L90" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M90" s="10">
-        <v>0.78</v>
-      </c>
-      <c r="N90" s="10"/>
-      <c r="O90" s="10"/>
-      <c r="P90" s="10"/>
-    </row>
-    <row r="91" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
-      <c r="N91" s="10"/>
-      <c r="O91" s="10"/>
-      <c r="P91" s="10"/>
-    </row>
-    <row r="92" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H92" t="s">
-        <v>63</v>
-      </c>
-      <c r="L92" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="M92" s="10">
-        <v>652</v>
-      </c>
-      <c r="N92" s="10"/>
-      <c r="O92" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="P92" s="10"/>
-    </row>
-    <row r="93" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H93" t="s">
-        <v>63</v>
-      </c>
-      <c r="L93" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="M93" s="10">
-        <v>0</v>
-      </c>
-      <c r="N93" s="10"/>
-      <c r="O93" s="10"/>
-      <c r="P93" s="10"/>
-    </row>
-    <row r="94" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H94" t="s">
-        <v>63</v>
-      </c>
-      <c r="L94" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="M94" s="10">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="N94" s="10"/>
-      <c r="O94" s="10"/>
-      <c r="P94" s="10"/>
-    </row>
-    <row r="95" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H95" t="s">
-        <v>63</v>
-      </c>
-      <c r="L95" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M95" s="10">
-        <v>20</v>
-      </c>
-      <c r="N95" s="10"/>
-      <c r="O95" s="10"/>
-      <c r="P95" s="10"/>
-    </row>
-    <row r="96" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H96" t="s">
-        <v>63</v>
-      </c>
-      <c r="I96" t="s">
-        <v>74</v>
-      </c>
-      <c r="L96" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M96" s="12">
-        <v>1</v>
-      </c>
-      <c r="N96" s="10"/>
-      <c r="O96" s="10"/>
-      <c r="P96" s="10"/>
-    </row>
-    <row r="97" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H97" t="s">
-        <v>63</v>
-      </c>
-      <c r="I97" t="s">
-        <v>73</v>
-      </c>
-      <c r="L97" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M97" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="N97" s="10"/>
-      <c r="O97" s="10"/>
-      <c r="P97" s="10"/>
-    </row>
-    <row r="98" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H98" t="s">
-        <v>63</v>
-      </c>
-      <c r="I98" t="s">
-        <v>72</v>
-      </c>
-      <c r="L98" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M98" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="N98" s="10"/>
-      <c r="O98" s="10"/>
-      <c r="P98" s="10"/>
-    </row>
-    <row r="99" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L99" s="10"/>
-      <c r="M99" s="10"/>
-      <c r="N99" s="10"/>
-      <c r="O99" s="10"/>
       <c r="P99" s="10"/>
     </row>
     <row r="100" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H100" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L100" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M100" s="10">
-        <v>46</v>
+        <v>18.8</v>
       </c>
       <c r="N100" s="10"/>
-      <c r="O100" s="10" t="s">
-        <v>83</v>
-      </c>
+      <c r="O100" s="10"/>
       <c r="P100" s="10"/>
     </row>
     <row r="101" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H101" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L101" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M101" s="10">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N101" s="10"/>
       <c r="O101" s="10"/>
@@ -3166,13 +4220,13 @@
     </row>
     <row r="102" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H102" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L102" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M102" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N102" s="10"/>
       <c r="O102" s="10"/>
@@ -3180,13 +4234,16 @@
     </row>
     <row r="103" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H103" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="I103" t="s">
+        <v>74</v>
       </c>
       <c r="L103" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M103" s="10">
-        <v>5</v>
+        <v>79</v>
+      </c>
+      <c r="M103" s="12">
+        <v>1</v>
       </c>
       <c r="N103" s="10"/>
       <c r="O103" s="10"/>
@@ -3194,16 +4251,16 @@
     </row>
     <row r="104" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H104" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I104" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L104" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M104" s="12">
-        <v>1</v>
+      <c r="M104" s="10">
+        <v>0.88</v>
       </c>
       <c r="N104" s="10"/>
       <c r="O104" s="10"/>
@@ -3211,910 +4268,1370 @@
     </row>
     <row r="105" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H105" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I105" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L105" s="10" t="s">
         <v>79</v>
       </c>
       <c r="M105" s="10">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="N105" s="10"/>
       <c r="O105" s="10"/>
       <c r="P105" s="10"/>
     </row>
     <row r="106" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="H106" t="s">
-        <v>62</v>
-      </c>
-      <c r="I106" t="s">
-        <v>72</v>
-      </c>
-      <c r="L106" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M106" s="10">
-        <v>0.65</v>
-      </c>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
       <c r="N106" s="10"/>
       <c r="O106" s="10"/>
       <c r="P106" s="10"/>
     </row>
     <row r="107" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
+      <c r="H107" t="s">
+        <v>63</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M107" s="10">
+        <v>652</v>
+      </c>
       <c r="N107" s="10"/>
-      <c r="O107" s="10"/>
+      <c r="O107" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="P107" s="10"/>
     </row>
     <row r="108" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H108" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L108" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M108" s="12">
-        <v>5.0999999999999996</v>
+        <v>77</v>
+      </c>
+      <c r="M108" s="10">
+        <v>0</v>
       </c>
       <c r="N108" s="10"/>
-      <c r="O108" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="P108" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="O108" s="10"/>
+      <c r="P108" s="10"/>
     </row>
     <row r="109" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H109" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L109" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M109" s="12">
-        <v>7.1</v>
+        <v>78</v>
+      </c>
+      <c r="M109" s="10">
+        <v>5.0999999999999996</v>
       </c>
       <c r="N109" s="10"/>
-      <c r="O109" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P109" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="O109" s="10"/>
+      <c r="P109" s="10"/>
     </row>
     <row r="110" spans="8:16" x14ac:dyDescent="0.25">
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
+      <c r="H110" t="s">
+        <v>63</v>
+      </c>
+      <c r="L110" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="M110" s="10">
+        <v>20</v>
+      </c>
       <c r="N110" s="10"/>
       <c r="O110" s="10"/>
       <c r="P110" s="10"/>
     </row>
     <row r="111" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H111" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="I111" t="s">
+        <v>74</v>
       </c>
       <c r="L111" s="10" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M111" s="12">
-        <v>3.7353333333333332</v>
+        <v>1</v>
       </c>
       <c r="N111" s="10"/>
-      <c r="O111" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="O111" s="10"/>
+      <c r="P111" s="10"/>
     </row>
     <row r="112" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H112" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="I112" t="s">
+        <v>73</v>
       </c>
       <c r="L112" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M112" s="11">
-        <v>17.096931944444446</v>
+        <v>79</v>
+      </c>
+      <c r="M112" s="12">
+        <v>0.7</v>
       </c>
       <c r="N112" s="10"/>
-      <c r="O112" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="P112" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O112" s="10"/>
+      <c r="P112" s="10"/>
+    </row>
+    <row r="113" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H113" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="I113" t="s">
+        <v>72</v>
       </c>
       <c r="L113" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M113" s="12">
-        <v>1.2451111111111113</v>
+        <v>79</v>
+      </c>
+      <c r="M113" s="10">
+        <v>0.45</v>
       </c>
       <c r="N113" s="10"/>
-      <c r="O113" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="P113" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H114" t="s">
-        <v>68</v>
-      </c>
-      <c r="L114" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M114" s="12">
-        <v>3.1127777777777781</v>
-      </c>
+      <c r="O113" s="10"/>
+      <c r="P113" s="10"/>
+    </row>
+    <row r="114" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L114" s="10"/>
+      <c r="M114" s="10"/>
       <c r="N114" s="10"/>
-      <c r="O114" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P114" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O114" s="10"/>
+      <c r="P114" s="10"/>
+    </row>
+    <row r="115" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H115" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="L115" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M115" s="12">
-        <v>4.6691666666666665</v>
+        <v>76</v>
+      </c>
+      <c r="M115" s="10">
+        <v>46</v>
       </c>
       <c r="N115" s="10"/>
-      <c r="O115" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P115" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O115" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P115" s="10"/>
+    </row>
+    <row r="116" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H116" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L116" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M116" s="12">
-        <v>3.1127777777777781</v>
+        <v>77</v>
+      </c>
+      <c r="M116" s="10">
+        <v>2.8</v>
       </c>
       <c r="N116" s="10"/>
-      <c r="O116" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O116" s="10"/>
+      <c r="P116" s="10"/>
+    </row>
+    <row r="117" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H117" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L117" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M117" s="11">
-        <v>11.828555555555555</v>
+        <v>78</v>
+      </c>
+      <c r="M117" s="10">
+        <v>0</v>
       </c>
       <c r="N117" s="10"/>
-      <c r="O117" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="P117" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="118" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O117" s="10"/>
+      <c r="P117" s="10"/>
+    </row>
+    <row r="118" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H118" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="L118" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M118" s="11">
-        <v>26.302972222222223</v>
+        <v>75</v>
+      </c>
+      <c r="M118" s="10">
+        <v>5</v>
       </c>
       <c r="N118" s="10"/>
-      <c r="O118" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="P118" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O118" s="10"/>
+      <c r="P118" s="10"/>
+    </row>
+    <row r="119" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H119" t="s">
-        <v>101</v>
+        <v>62</v>
+      </c>
+      <c r="I119" t="s">
+        <v>74</v>
       </c>
       <c r="L119" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M119" s="11">
-        <v>11.3</v>
+        <v>79</v>
+      </c>
+      <c r="M119" s="12">
+        <v>1</v>
       </c>
       <c r="N119" s="10"/>
-      <c r="O119" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P119" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="120" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O119" s="10"/>
+      <c r="P119" s="10"/>
+    </row>
+    <row r="120" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H120" t="s">
-        <v>102</v>
+        <v>62</v>
+      </c>
+      <c r="I120" t="s">
+        <v>73</v>
       </c>
       <c r="L120" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M120" s="11">
-        <v>23.278130416666666</v>
+        <v>79</v>
+      </c>
+      <c r="M120" s="10">
+        <v>0.85</v>
       </c>
       <c r="N120" s="10"/>
-      <c r="O120" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="P120" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O120" s="10"/>
+      <c r="P120" s="10"/>
+    </row>
+    <row r="121" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H121" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="I121" t="s">
+        <v>72</v>
       </c>
       <c r="L121" s="10" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M121" s="10">
-        <v>13.15</v>
+        <v>0.65</v>
       </c>
       <c r="N121" s="10"/>
-      <c r="O121" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="P121" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H122" t="s">
-        <v>71</v>
-      </c>
-      <c r="L122" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M122" s="10">
-        <v>5.26</v>
-      </c>
+      <c r="O121" s="10"/>
+      <c r="P121" s="10"/>
+    </row>
+    <row r="122" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L122" s="10"/>
+      <c r="M122" s="10"/>
       <c r="N122" s="10"/>
-      <c r="O122" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="P122" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
-        <v>110</v>
-      </c>
+      <c r="O122" s="10"/>
+      <c r="P122" s="10"/>
+    </row>
+    <row r="123" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H123" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L123" s="10" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="M123" s="12">
-        <v>1.7546281240590185</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="N123" s="10"/>
-      <c r="O123" s="10" t="s">
-        <v>111</v>
+      <c r="O123" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
-        <v>113</v>
-      </c>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="124" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H124" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L124" s="10" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="M124" s="12">
-        <v>5.1828516694033944</v>
+        <v>7.1</v>
       </c>
       <c r="N124" s="10"/>
       <c r="O124" s="6" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
-        <v>114</v>
-      </c>
-      <c r="H125" t="s">
-        <v>71</v>
-      </c>
-      <c r="L125" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M125" s="13">
-        <v>4.0531064740502947</v>
-      </c>
-      <c r="O125" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="P125" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="126" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
-        <v>118</v>
-      </c>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="125" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="L125" s="10"/>
+      <c r="M125" s="10"/>
+      <c r="N125" s="10"/>
+      <c r="O125" s="10"/>
+      <c r="P125" s="10"/>
+    </row>
+    <row r="126" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H126" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L126" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M126" s="13">
-        <v>4.3591310772039646</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>117</v>
+        <v>54</v>
+      </c>
+      <c r="M126" s="12">
+        <v>3.7353333333333332</v>
+      </c>
+      <c r="N126" s="10"/>
+      <c r="O126" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="L127" s="10"/>
-      <c r="M127" s="13"/>
-      <c r="O127" s="6"/>
-      <c r="P127" s="6"/>
-    </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="127" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H127" t="s">
+        <v>64</v>
+      </c>
+      <c r="L127" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M127" s="11">
+        <v>17.096931944444446</v>
+      </c>
+      <c r="N127" s="10"/>
+      <c r="O127" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P127" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="128" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H128" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="L128" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M128" s="13">
-        <v>14.6</v>
-      </c>
-      <c r="O128" s="6"/>
-      <c r="P128" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M128" s="12">
+        <v>1.2451111111111113</v>
+      </c>
+      <c r="N128" s="10"/>
+      <c r="O128" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P128" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="129" spans="2:16" x14ac:dyDescent="0.25">
       <c r="H129" t="s">
-        <v>124</v>
-      </c>
-      <c r="J129" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="L129" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M129" s="13">
-        <v>37.744765138888887</v>
-      </c>
-      <c r="O129" s="6"/>
-      <c r="P129" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M129" s="12">
+        <v>3.1127777777777781</v>
+      </c>
+      <c r="N129" s="10"/>
+      <c r="O129" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P129" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="130" spans="2:16" x14ac:dyDescent="0.25">
       <c r="H130" t="s">
-        <v>124</v>
-      </c>
-      <c r="J130" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="L130" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M130" s="13">
-        <v>50.107162083333336</v>
-      </c>
-      <c r="O130" s="6"/>
-      <c r="P130" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M130" s="12">
+        <v>4.6691666666666665</v>
+      </c>
+      <c r="N130" s="10"/>
+      <c r="O130" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P130" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="131" spans="2:16" x14ac:dyDescent="0.25">
       <c r="H131" t="s">
-        <v>124</v>
-      </c>
-      <c r="J131" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="L131" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M131" s="13">
+      <c r="M131" s="12">
+        <v>3.1127777777777781</v>
+      </c>
+      <c r="N131" s="10"/>
+      <c r="O131" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="P131" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="132" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H132" t="s">
+        <v>70</v>
+      </c>
+      <c r="L132" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M132" s="11">
+        <v>11.828555555555555</v>
+      </c>
+      <c r="N132" s="10"/>
+      <c r="O132" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P132" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="133" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H133" t="s">
+        <v>100</v>
+      </c>
+      <c r="L133" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M133" s="11">
+        <v>26.302972222222223</v>
+      </c>
+      <c r="N133" s="10"/>
+      <c r="O133" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P133" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="134" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H134" t="s">
+        <v>101</v>
+      </c>
+      <c r="L134" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M134" s="11">
+        <v>11.3</v>
+      </c>
+      <c r="N134" s="10"/>
+      <c r="O134" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P134" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="135" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H135" t="s">
+        <v>102</v>
+      </c>
+      <c r="L135" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M135" s="11">
+        <v>23.278130416666666</v>
+      </c>
+      <c r="N135" s="10"/>
+      <c r="O135" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P135" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="136" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H136" t="s">
+        <v>71</v>
+      </c>
+      <c r="L136" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M136" s="10">
+        <v>13.15</v>
+      </c>
+      <c r="N136" s="10"/>
+      <c r="O136" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="P136" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="137" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H137" t="s">
+        <v>71</v>
+      </c>
+      <c r="L137" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M137" s="10">
+        <v>5.26</v>
+      </c>
+      <c r="N137" s="10"/>
+      <c r="O137" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="P137" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="138" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>110</v>
+      </c>
+      <c r="H138" t="s">
+        <v>71</v>
+      </c>
+      <c r="L138" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M138" s="12">
+        <v>1.7546281240590185</v>
+      </c>
+      <c r="N138" s="10"/>
+      <c r="O138" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="P138" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="139" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>113</v>
+      </c>
+      <c r="H139" t="s">
+        <v>71</v>
+      </c>
+      <c r="L139" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M139" s="12">
+        <v>5.1828516694033944</v>
+      </c>
+      <c r="N139" s="10"/>
+      <c r="O139" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P139" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="140" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>114</v>
+      </c>
+      <c r="H140" t="s">
+        <v>71</v>
+      </c>
+      <c r="L140" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M140" s="13">
+        <v>4.0531064740502947</v>
+      </c>
+      <c r="O140" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="P140" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="141" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>118</v>
+      </c>
+      <c r="H141" t="s">
+        <v>71</v>
+      </c>
+      <c r="L141" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M141" s="13">
+        <v>4.3591310772039646</v>
+      </c>
+      <c r="O141" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P141" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="142" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L142" s="10"/>
+      <c r="M142" s="13"/>
+      <c r="O142" s="6"/>
+      <c r="P142" s="6"/>
+    </row>
+    <row r="143" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H143" t="s">
+        <v>120</v>
+      </c>
+      <c r="L143" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M143" s="13">
+        <v>14.6</v>
+      </c>
+      <c r="O143" s="6"/>
+      <c r="P143" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="144" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H144" t="s">
+        <v>124</v>
+      </c>
+      <c r="J144" t="s">
+        <v>121</v>
+      </c>
+      <c r="L144" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M144" s="13">
+        <v>37.744765138888887</v>
+      </c>
+      <c r="O144" s="6"/>
+      <c r="P144" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H145" t="s">
+        <v>124</v>
+      </c>
+      <c r="J145" t="s">
+        <v>122</v>
+      </c>
+      <c r="L145" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M145" s="13">
+        <v>50.107162083333336</v>
+      </c>
+      <c r="O145" s="6"/>
+      <c r="P145" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H146" t="s">
+        <v>124</v>
+      </c>
+      <c r="J146" t="s">
+        <v>123</v>
+      </c>
+      <c r="L146" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M146" s="13">
         <v>36.955675972222224</v>
       </c>
-      <c r="O131" s="6"/>
-      <c r="P131" s="6" t="s">
+      <c r="O146" s="6"/>
+      <c r="P146" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L132" s="10"/>
-      <c r="M132" s="13"/>
-      <c r="O132" s="6"/>
-      <c r="P132" s="6"/>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H133" t="s">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L147" s="10"/>
+      <c r="M147" s="13"/>
+      <c r="O147" s="6"/>
+      <c r="P147" s="6"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H148" t="s">
         <v>131</v>
       </c>
-      <c r="L133" s="10" t="s">
+      <c r="L148" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="M133" s="13">
+      <c r="M148" s="13">
         <v>1.6176327916666666</v>
       </c>
-      <c r="O133" s="6" t="s">
+      <c r="O148" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="P133" s="4" t="s">
+      <c r="P148" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H134" t="s">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H149" t="s">
         <v>132</v>
       </c>
-      <c r="L134" s="10" t="s">
+      <c r="L149" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="M134" s="13">
+      <c r="M149" s="13">
         <v>3.0774477499999997</v>
       </c>
-      <c r="O134" s="6" t="s">
+      <c r="O149" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="P134" s="4" t="s">
+      <c r="P149" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H135" t="s">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H150" t="s">
         <v>133</v>
       </c>
-      <c r="L135" s="10" t="s">
+      <c r="L150" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="M135" s="13">
+      <c r="M150" s="13">
         <v>0.25</v>
       </c>
-      <c r="O135" s="6" t="s">
+      <c r="O150" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="P135" s="4" t="s">
+      <c r="P150" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-      <c r="L137" s="8"/>
-      <c r="M137" s="8"/>
-      <c r="N137" s="8"/>
-      <c r="O137" s="8"/>
-      <c r="P137" s="8"/>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L138" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M138" s="9">
-        <v>0</v>
-      </c>
-      <c r="O138" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L139" t="s">
-        <v>49</v>
-      </c>
-      <c r="M139" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1"/>
-      <c r="K141" s="1"/>
-      <c r="L141" s="8"/>
-      <c r="M141" s="8"/>
-      <c r="N141" s="8"/>
-      <c r="O141" s="8"/>
-      <c r="P141" s="8"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L142" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="M142" s="9">
-        <v>0</v>
-      </c>
-      <c r="N142" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="O142" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
-        <v>160</v>
-      </c>
-      <c r="L143" t="s">
-        <v>167</v>
-      </c>
-      <c r="M143">
-        <v>302</v>
-      </c>
-      <c r="N143" t="s">
-        <v>168</v>
-      </c>
-      <c r="O143" t="s">
-        <v>169</v>
-      </c>
-      <c r="P143" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
-        <v>161</v>
-      </c>
-      <c r="L144" t="s">
-        <v>167</v>
-      </c>
-      <c r="M144">
-        <v>197</v>
-      </c>
-      <c r="N144" t="s">
-        <v>168</v>
-      </c>
-      <c r="O144" t="s">
-        <v>170</v>
-      </c>
-      <c r="P144" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B145" t="s">
-        <v>162</v>
-      </c>
-      <c r="L145" t="s">
-        <v>167</v>
-      </c>
-      <c r="M145">
-        <v>216</v>
-      </c>
-      <c r="N145" t="s">
-        <v>168</v>
-      </c>
-      <c r="O145" t="s">
-        <v>171</v>
-      </c>
-      <c r="P145" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B146" t="s">
-        <v>163</v>
-      </c>
-      <c r="L146" t="s">
-        <v>167</v>
-      </c>
-      <c r="M146">
-        <v>216</v>
-      </c>
-      <c r="N146" t="s">
-        <v>168</v>
-      </c>
-      <c r="O146" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B147" t="s">
-        <v>164</v>
-      </c>
-      <c r="L147" t="s">
-        <v>167</v>
-      </c>
-      <c r="M147">
-        <v>216</v>
-      </c>
-      <c r="N147" t="s">
-        <v>168</v>
-      </c>
-      <c r="O147" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>165</v>
-      </c>
-      <c r="L148" t="s">
-        <v>167</v>
-      </c>
-      <c r="M148">
-        <v>216</v>
-      </c>
-      <c r="N148" t="s">
-        <v>168</v>
-      </c>
-      <c r="O148" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B149" t="s">
-        <v>166</v>
-      </c>
-      <c r="L149" t="s">
-        <v>167</v>
-      </c>
-      <c r="M149">
-        <v>216</v>
-      </c>
-      <c r="N149" t="s">
-        <v>168</v>
-      </c>
-      <c r="O149" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
-      <c r="E151" s="1"/>
-      <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="1"/>
-      <c r="K151" s="1"/>
-      <c r="L151" s="8"/>
-      <c r="M151" s="8"/>
-      <c r="N151" s="8"/>
-      <c r="O151" s="8"/>
-      <c r="P151" s="8"/>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L152" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="M152" s="9">
-        <v>0</v>
-      </c>
-      <c r="N152" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="O152" s="9" t="s">
-        <v>53</v>
-      </c>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="8"/>
+      <c r="M152" s="8"/>
+      <c r="N152" s="8"/>
+      <c r="O152" s="8"/>
+      <c r="P152" s="8"/>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L153" s="9" t="s">
-        <v>237</v>
+        <v>49</v>
       </c>
       <c r="M153" s="9">
         <v>0</v>
       </c>
-      <c r="N153" s="9" t="s">
-        <v>238</v>
-      </c>
       <c r="O153" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L154" t="s">
+        <v>49</v>
+      </c>
+      <c r="M154" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="K156" s="1"/>
+      <c r="L156" s="8"/>
+      <c r="M156" s="8"/>
+      <c r="N156" s="8"/>
+      <c r="O156" s="8"/>
+      <c r="P156" s="8"/>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L157" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="M157" s="9">
+        <v>0</v>
+      </c>
+      <c r="N157" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="O157" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>160</v>
+      </c>
+      <c r="L158" t="s">
+        <v>167</v>
+      </c>
+      <c r="M158">
+        <v>302</v>
+      </c>
+      <c r="N158" t="s">
+        <v>168</v>
+      </c>
+      <c r="O158" t="s">
+        <v>169</v>
+      </c>
+      <c r="P158" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>161</v>
+      </c>
+      <c r="L159" t="s">
+        <v>167</v>
+      </c>
+      <c r="M159">
+        <v>197</v>
+      </c>
+      <c r="N159" t="s">
+        <v>168</v>
+      </c>
+      <c r="O159" t="s">
+        <v>170</v>
+      </c>
+      <c r="P159" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>162</v>
+      </c>
+      <c r="L160" t="s">
+        <v>167</v>
+      </c>
+      <c r="M160">
+        <v>216</v>
+      </c>
+      <c r="N160" t="s">
+        <v>168</v>
+      </c>
+      <c r="O160" t="s">
+        <v>171</v>
+      </c>
+      <c r="P160" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>163</v>
+      </c>
+      <c r="L161" t="s">
+        <v>167</v>
+      </c>
+      <c r="M161">
+        <v>216</v>
+      </c>
+      <c r="N161" t="s">
+        <v>168</v>
+      </c>
+      <c r="O161" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>164</v>
+      </c>
+      <c r="L162" t="s">
+        <v>167</v>
+      </c>
+      <c r="M162">
+        <v>216</v>
+      </c>
+      <c r="N162" t="s">
+        <v>168</v>
+      </c>
+      <c r="O162" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>165</v>
+      </c>
+      <c r="L163" t="s">
+        <v>167</v>
+      </c>
+      <c r="M163">
+        <v>216</v>
+      </c>
+      <c r="N163" t="s">
+        <v>168</v>
+      </c>
+      <c r="O163" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>166</v>
+      </c>
+      <c r="L164" t="s">
+        <v>167</v>
+      </c>
+      <c r="M164">
+        <v>216</v>
+      </c>
+      <c r="N164" t="s">
+        <v>168</v>
+      </c>
+      <c r="O164" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+      <c r="L166" s="8"/>
+      <c r="M166" s="8"/>
+      <c r="N166" s="8"/>
+      <c r="O166" s="8"/>
+      <c r="P166" s="8"/>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L167" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="M167" s="9">
+        <v>0</v>
+      </c>
+      <c r="N167" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="O167" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L168" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="M168" s="9">
+        <v>0</v>
+      </c>
+      <c r="N168" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="O168" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L169" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="M169" s="9">
+        <v>0</v>
+      </c>
+      <c r="N169" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="O169" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>203</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C171" t="s">
         <v>201</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D171" t="s">
+        <v>210</v>
+      </c>
+      <c r="E171" t="s">
         <v>211</v>
       </c>
-      <c r="E155" t="s">
-        <v>212</v>
-      </c>
-      <c r="F155" t="s">
+      <c r="F171" t="s">
+        <v>236</v>
+      </c>
+      <c r="L171" t="s">
+        <v>234</v>
+      </c>
+      <c r="M171" s="25">
+        <f>'energy stables'!E24</f>
+        <v>3.5302245250431775E-2</v>
+      </c>
+      <c r="N171" t="s">
+        <v>206</v>
+      </c>
+      <c r="O171" t="s">
+        <v>220</v>
+      </c>
+      <c r="P171" t="s">
         <v>239</v>
       </c>
-      <c r="L155" t="s">
-        <v>237</v>
-      </c>
-      <c r="M155" s="25">
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>207</v>
+      </c>
+      <c r="C172" t="s">
+        <v>201</v>
+      </c>
+      <c r="D172" t="s">
+        <v>210</v>
+      </c>
+      <c r="E172" t="s">
+        <v>211</v>
+      </c>
+      <c r="L172" t="s">
+        <v>232</v>
+      </c>
+      <c r="M172" s="24">
+        <f>'energy stables'!D26</f>
+        <v>308.33833333333342</v>
+      </c>
+      <c r="N172" t="s">
+        <v>321</v>
+      </c>
+      <c r="O172" t="s">
+        <v>240</v>
+      </c>
+      <c r="P172" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>205</v>
+      </c>
+      <c r="C173" t="s">
+        <v>201</v>
+      </c>
+      <c r="D173" t="s">
+        <v>210</v>
+      </c>
+      <c r="E173" t="s">
+        <v>211</v>
+      </c>
+      <c r="F173" t="s">
+        <v>236</v>
+      </c>
+      <c r="L173" t="s">
+        <v>234</v>
+      </c>
+      <c r="M173" s="25">
         <f>'energy stables'!E27</f>
-        <v>3.5302245250431775E-2</v>
-      </c>
-      <c r="N155" t="s">
+        <v>4.1036269430051814E-2</v>
+      </c>
+      <c r="N173" t="s">
         <v>206</v>
       </c>
-      <c r="O155" t="s">
-        <v>221</v>
-      </c>
-      <c r="P155" t="s">
+      <c r="P173" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>203</v>
+      </c>
+      <c r="C175" t="s">
+        <v>201</v>
+      </c>
+      <c r="L175" t="s">
+        <v>232</v>
+      </c>
+      <c r="M175" s="24">
+        <f>'energy stables'!D29</f>
+        <v>170.33333333333331</v>
+      </c>
+      <c r="N175" t="s">
+        <v>321</v>
+      </c>
+      <c r="O175" t="s">
+        <v>245</v>
+      </c>
+      <c r="P175" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>207</v>
+      </c>
+      <c r="C176" t="s">
+        <v>201</v>
+      </c>
+      <c r="L176" t="s">
+        <v>232</v>
+      </c>
+      <c r="M176" s="24">
+        <f>'energy stables'!D31</f>
+        <v>332.32333333333338</v>
+      </c>
+      <c r="N176" t="s">
+        <v>321</v>
+      </c>
+      <c r="O176" t="s">
+        <v>246</v>
+      </c>
+      <c r="P176" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M177" s="24"/>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>203</v>
+      </c>
+      <c r="C178" t="s">
+        <v>241</v>
+      </c>
+      <c r="D178" t="s">
+        <v>242</v>
+      </c>
+      <c r="E178" t="s">
+        <v>247</v>
+      </c>
+      <c r="L178" t="s">
+        <v>331</v>
+      </c>
+      <c r="M178" s="25">
+        <f>(290+1078)/100000</f>
+        <v>1.3679999999999999E-2</v>
+      </c>
+      <c r="N178" t="s">
+        <v>330</v>
+      </c>
+      <c r="O178" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="P178" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>204</v>
+      </c>
+      <c r="C179" t="s">
+        <v>241</v>
+      </c>
+      <c r="D179" t="s">
+        <v>242</v>
+      </c>
+      <c r="E179" t="s">
+        <v>247</v>
+      </c>
+      <c r="L179" t="s">
+        <v>331</v>
+      </c>
+      <c r="M179" s="25">
+        <f>77000/100000</f>
+        <v>0.77</v>
+      </c>
+      <c r="N179" t="s">
+        <v>330</v>
+      </c>
+      <c r="P179" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>207</v>
       </c>
-      <c r="C156" t="s">
-        <v>201</v>
-      </c>
-      <c r="D156" t="s">
-        <v>211</v>
-      </c>
-      <c r="E156" t="s">
-        <v>212</v>
-      </c>
-      <c r="L156" t="s">
-        <v>235</v>
-      </c>
-      <c r="M156" s="24">
-        <f>'energy stables'!D29</f>
-        <v>308.33833333333342</v>
-      </c>
-      <c r="N156" t="s">
-        <v>208</v>
-      </c>
-      <c r="O156" t="s">
+      <c r="C180" t="s">
+        <v>241</v>
+      </c>
+      <c r="D180" t="s">
+        <v>242</v>
+      </c>
+      <c r="E180" t="s">
+        <v>247</v>
+      </c>
+      <c r="L180" t="s">
+        <v>331</v>
+      </c>
+      <c r="M180" s="25">
+        <f>(3340+9790)/100000</f>
+        <v>0.1313</v>
+      </c>
+      <c r="N180" t="s">
+        <v>330</v>
+      </c>
+      <c r="O180" t="s">
         <v>244</v>
       </c>
-      <c r="P156" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>205</v>
-      </c>
-      <c r="C157" t="s">
-        <v>201</v>
-      </c>
-      <c r="D157" t="s">
-        <v>211</v>
-      </c>
-      <c r="E157" t="s">
-        <v>212</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="P180" t="s">
         <v>239</v>
       </c>
-      <c r="L157" t="s">
-        <v>237</v>
-      </c>
-      <c r="M157" s="25">
-        <f>'energy stables'!E30</f>
-        <v>4.1036269430051814E-2</v>
-      </c>
-      <c r="N157" t="s">
-        <v>206</v>
-      </c>
-      <c r="P157" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>203</v>
       </c>
-      <c r="C159" t="s">
-        <v>201</v>
-      </c>
-      <c r="L159" t="s">
-        <v>235</v>
-      </c>
-      <c r="M159" s="24">
-        <f>'energy stables'!D32</f>
-        <v>170.33333333333331</v>
-      </c>
-      <c r="N159" t="s">
-        <v>208</v>
-      </c>
-      <c r="O159" t="s">
-        <v>221</v>
-      </c>
-      <c r="P159" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="C182" t="s">
+        <v>248</v>
+      </c>
+      <c r="E182" t="s">
+        <v>324</v>
+      </c>
+      <c r="L182" t="s">
+        <v>331</v>
+      </c>
+      <c r="M182">
+        <f>'energy stables'!D49</f>
+        <v>3.5</v>
+      </c>
+      <c r="N182" t="s">
+        <v>330</v>
+      </c>
+      <c r="P182" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>204</v>
+      </c>
+      <c r="C183" t="s">
+        <v>248</v>
+      </c>
+      <c r="E183" t="s">
+        <v>324</v>
+      </c>
+      <c r="L183" t="s">
+        <v>331</v>
+      </c>
+      <c r="M183">
+        <f>'energy stables'!D50</f>
+        <v>12.5</v>
+      </c>
+      <c r="N183" t="s">
+        <v>330</v>
+      </c>
+      <c r="P183" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
         <v>207</v>
       </c>
-      <c r="C160" t="s">
-        <v>201</v>
-      </c>
-      <c r="L160" t="s">
-        <v>235</v>
-      </c>
-      <c r="M160" s="24">
-        <f>'energy stables'!D34</f>
-        <v>332.32333333333338</v>
-      </c>
-      <c r="N160" t="s">
-        <v>208</v>
-      </c>
-      <c r="O160" t="s">
-        <v>244</v>
-      </c>
-      <c r="P160" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="161" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M161" s="24"/>
+      <c r="C184" t="s">
+        <v>248</v>
+      </c>
+      <c r="E184" t="s">
+        <v>324</v>
+      </c>
+      <c r="L184" t="s">
+        <v>331</v>
+      </c>
+      <c r="M184">
+        <f>'energy stables'!D51</f>
+        <v>34</v>
+      </c>
+      <c r="N184" t="s">
+        <v>330</v>
+      </c>
+      <c r="P184" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>203</v>
+      </c>
+      <c r="C185" t="s">
+        <v>248</v>
+      </c>
+      <c r="E185" t="s">
+        <v>327</v>
+      </c>
+      <c r="L185" t="s">
+        <v>331</v>
+      </c>
+      <c r="M185">
+        <f>'energy stables'!D53</f>
+        <v>0.04</v>
+      </c>
+      <c r="N185" t="s">
+        <v>330</v>
+      </c>
+      <c r="P185" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>204</v>
+      </c>
+      <c r="C186" t="s">
+        <v>248</v>
+      </c>
+      <c r="E186" t="s">
+        <v>327</v>
+      </c>
+      <c r="L186" t="s">
+        <v>331</v>
+      </c>
+      <c r="M186" s="13">
+        <f>'energy stables'!D54</f>
+        <v>0.1</v>
+      </c>
+      <c r="N186" t="s">
+        <v>330</v>
+      </c>
+      <c r="P186" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>207</v>
+      </c>
+      <c r="C187" t="s">
+        <v>248</v>
+      </c>
+      <c r="E187" t="s">
+        <v>327</v>
+      </c>
+      <c r="L187" t="s">
+        <v>331</v>
+      </c>
+      <c r="M187" s="13">
+        <f>'energy stables'!D55</f>
+        <v>0.26</v>
+      </c>
+      <c r="N187" t="s">
+        <v>330</v>
+      </c>
+      <c r="P187" t="s">
+        <v>259</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4123,599 +5640,2012 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:S58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="13" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="49" t="s">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="53" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B4" s="51" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="27"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="46" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="27"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="47" t="s">
+      <c r="E5" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F9" s="30" t="s">
+      <c r="H5" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="31">
+        <v>150</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="4">
+        <v>220</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="31">
+        <v>150</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="4">
+        <v>220</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="31">
+        <v>10500</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="4">
+        <v>8800</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="31"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="31">
+        <v>652</v>
+      </c>
+      <c r="E10" s="33">
+        <f>D10*(2/3)</f>
+        <v>434.66666666666663</v>
+      </c>
+      <c r="F10" s="34">
+        <f>D10*(1/3)</f>
+        <v>217.33333333333331</v>
+      </c>
+      <c r="G10" s="4">
+        <v>370</v>
+      </c>
+      <c r="H10" s="33">
+        <f>G10*(2/3)</f>
+        <v>246.66666666666666</v>
+      </c>
+      <c r="I10" s="34">
+        <f>G10*(1/3)</f>
+        <v>123.33333333333333</v>
+      </c>
+      <c r="J10" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="I9" s="30" t="s">
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="31">
+        <v>3</v>
+      </c>
+      <c r="E11" s="33">
+        <f>(E$17-E$10-E$12-E$14) * (D11/SUM(D$11,D$13,D$15))</f>
+        <v>2.1908735632183913</v>
+      </c>
+      <c r="F11" s="34">
+        <f>(F$17-F$10-F$12-F$14) * (D11/SUM(D$11,D$13,D$15))</f>
+        <v>0.80912643678160945</v>
+      </c>
+      <c r="G11" s="4">
+        <v>74</v>
+      </c>
+      <c r="H11" s="33">
+        <f>(H$17-H$10-H$12-H$14) * (G11/SUM(G$11,G$13,G$15))</f>
+        <v>42.039127163280675</v>
+      </c>
+      <c r="I11" s="34">
+        <f>(I$17-I$10-I$12-I$14) * (G11/SUM(G$11,G$13,G$15))</f>
+        <v>31.960872836719343</v>
+      </c>
+      <c r="J11" s="26"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" s="31">
+        <v>40</v>
+      </c>
+      <c r="E12" s="33">
+        <f>D12*(2/3)</f>
+        <v>26.666666666666664</v>
+      </c>
+      <c r="F12" s="34">
+        <f>D12*(1/3)</f>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="G12" s="4">
+        <v>31</v>
+      </c>
+      <c r="H12" s="33">
+        <f>G12*(2/3)</f>
+        <v>20.666666666666664</v>
+      </c>
+      <c r="I12" s="34">
+        <f>G12*(1/3)</f>
+        <v>10.333333333333332</v>
+      </c>
+      <c r="J12" s="26" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="31" t="s">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="31">
         <v>216</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="D10" s="31">
-        <v>150</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="4">
-        <v>220</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="32"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="31">
-        <v>150</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="4">
-        <v>220</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="32"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="D12" s="31">
-        <v>10500</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="4">
-        <v>8800</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="32"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="31"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="32"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E13" s="33">
+        <f>(E$17-E$10-E$12-E$14) * (D13/SUM(D$11,D$13,D$15))</f>
+        <v>157.74289655172416</v>
+      </c>
+      <c r="F13" s="34">
+        <f>(F$17-F$10-F$12-F$14) * (D13/SUM(D$11,D$13,D$15))</f>
+        <v>58.257103448275878</v>
+      </c>
+      <c r="G13" s="4">
+        <v>224</v>
+      </c>
+      <c r="H13" s="33">
+        <f>(H$17-H$10-H$12-H$14) * (G13/SUM(G$11,G$13,G$15))</f>
+        <v>127.25357411587665</v>
+      </c>
+      <c r="I13" s="34">
+        <f>(I$17-I$10-I$12-I$14) * (G13/SUM(G$11,G$13,G$15))</f>
+        <v>96.746425884123411</v>
+      </c>
+      <c r="J13" s="26"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>230</v>
+        <v>224</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>229</v>
       </c>
       <c r="D14" s="31">
-        <v>652</v>
+        <v>386</v>
       </c>
       <c r="E14" s="33">
-        <f>D14*(2/3)</f>
-        <v>434.66666666666663</v>
+        <f>D14</f>
+        <v>386</v>
       </c>
       <c r="F14" s="34">
-        <f>D14*(1/3)</f>
-        <v>217.33333333333331</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="H14" s="33">
-        <f>G14*(2/3)</f>
-        <v>246.66666666666666</v>
+        <f>G14</f>
+        <v>406</v>
       </c>
       <c r="I14" s="34">
-        <f>G14*(1/3)</f>
-        <v>123.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>230</v>
+        <v>225</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>229</v>
       </c>
       <c r="D15" s="31">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="E15" s="33">
-        <f>(E$21-E$14-E$16-E$18) * (D15/SUM(D$15,D$17,D$19))</f>
-        <v>2.1908735632183913</v>
+        <f>(E$17-E$10-E$12-E$14) * (D15/SUM(D$11,D$13,D$15))</f>
+        <v>157.74289655172416</v>
       </c>
       <c r="F15" s="34">
-        <f>(F$21-F$14-F$16-F$18) * (D15/SUM(D$15,D$17,D$19))</f>
-        <v>0.80912643678160945</v>
+        <f>(F$17-F$10-F$12-F$14) * (D15/SUM(D$11,D$13,D$15))</f>
+        <v>58.257103448275878</v>
       </c>
       <c r="G15" s="4">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="H15" s="33">
-        <f>(H$21-H$14-H$16-H$18) * (G15/SUM(G$15,G$17,G$19))</f>
-        <v>42.039127163280675</v>
+        <f>(H$17-H$10-H$12-H$14) * (G15/SUM(G$11,G$13,G$15))</f>
+        <v>82.373965387509429</v>
       </c>
       <c r="I15" s="34">
-        <f>(I$21-I$14-I$16-I$18) * (G15/SUM(G$15,G$17,G$19))</f>
-        <v>31.960872836719343</v>
-      </c>
-      <c r="J15" s="26"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D16" s="31">
-        <v>40</v>
-      </c>
-      <c r="E16" s="33">
-        <f>D16*(2/3)</f>
-        <v>26.666666666666664</v>
-      </c>
-      <c r="F16" s="34">
-        <f>D16*(1/3)</f>
-        <v>13.333333333333332</v>
-      </c>
-      <c r="G16" s="4">
-        <v>31</v>
-      </c>
-      <c r="H16" s="33">
-        <f>G16*(2/3)</f>
-        <v>20.666666666666664</v>
-      </c>
-      <c r="I16" s="34">
-        <f>G16*(1/3)</f>
-        <v>10.333333333333332</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="31">
-        <v>216</v>
-      </c>
-      <c r="E17" s="33">
-        <f>(E$21-E$14-E$16-E$18) * (D17/SUM(D$15,D$17,D$19))</f>
-        <v>157.74289655172416</v>
-      </c>
-      <c r="F17" s="34">
-        <f>(F$21-F$14-F$16-F$18) * (D17/SUM(D$15,D$17,D$19))</f>
-        <v>58.257103448275878</v>
-      </c>
-      <c r="G17" s="4">
-        <v>224</v>
-      </c>
-      <c r="H17" s="33">
-        <f>(H$21-H$14-H$16-H$18) * (G17/SUM(G$15,G$17,G$19))</f>
-        <v>127.25357411587665</v>
-      </c>
-      <c r="I17" s="34">
-        <f>(I$21-I$14-I$16-I$18) * (G17/SUM(G$15,G$17,G$19))</f>
-        <v>96.746425884123411</v>
-      </c>
-      <c r="J17" s="26"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+        <f>(I$17-I$10-I$12-I$14) * (G15/SUM(G$11,G$13,G$15))</f>
+        <v>62.626034612490599</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="31"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" s="36">
+        <f>SUM(D10:D15)</f>
+        <v>1513</v>
+      </c>
+      <c r="E17" s="38">
+        <f t="shared" ref="E17" si="0">D17*(1-D$20/100)</f>
+        <v>1165.01</v>
+      </c>
+      <c r="F17" s="39">
+        <f>D17*(D$20/100)</f>
+        <v>347.99</v>
+      </c>
+      <c r="G17" s="37">
+        <f>SUM(G10:G15)</f>
+        <v>1250</v>
+      </c>
+      <c r="H17" s="38">
+        <f t="shared" ref="H17" si="1">G17*(1-G$20/100)</f>
+        <v>925</v>
+      </c>
+      <c r="I17" s="39">
+        <f>G17*(G$20/100)</f>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>230</v>
+        <v>227</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>229</v>
       </c>
       <c r="D18" s="31">
-        <v>386</v>
+        <v>868</v>
       </c>
       <c r="E18" s="33">
-        <f>D18</f>
-        <v>386</v>
+        <f>SUM(E11:E15)</f>
+        <v>730.34333333333336</v>
       </c>
       <c r="F18" s="34">
-        <v>0</v>
+        <f>SUM(F11:F15)</f>
+        <v>130.65666666666669</v>
       </c>
       <c r="G18" s="4">
-        <v>406</v>
+        <v>994</v>
       </c>
       <c r="H18" s="33">
-        <f>G18</f>
-        <v>406</v>
+        <f>SUM(H11:H15)</f>
+        <v>678.33333333333337</v>
       </c>
       <c r="I18" s="34">
-        <v>0</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" s="31">
-        <v>216</v>
-      </c>
-      <c r="E19" s="33">
-        <f>(E$21-E$14-E$16-E$18) * (D19/SUM(D$15,D$17,D$19))</f>
-        <v>157.74289655172416</v>
-      </c>
-      <c r="F19" s="34">
-        <f>(F$21-F$14-F$16-F$18) * (D19/SUM(D$15,D$17,D$19))</f>
-        <v>58.257103448275878</v>
-      </c>
-      <c r="G19" s="4">
-        <v>145</v>
-      </c>
-      <c r="H19" s="33">
-        <f>(H$21-H$14-H$16-H$18) * (G19/SUM(G$15,G$17,G$19))</f>
-        <v>82.373965387509429</v>
-      </c>
-      <c r="I19" s="34">
-        <f>(I$21-I$14-I$16-I$18) * (G19/SUM(G$15,G$17,G$19))</f>
-        <v>62.626034612490599</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="31"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="32"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D21" s="36">
-        <f>SUM(D14:D19)</f>
-        <v>1513</v>
-      </c>
-      <c r="E21" s="38">
-        <f t="shared" ref="E21" si="0">D21*(1-D$24/100)</f>
-        <v>1165.01</v>
-      </c>
-      <c r="F21" s="39">
-        <f>D21*(D$24/100)</f>
-        <v>347.99</v>
-      </c>
-      <c r="G21" s="37">
-        <f>SUM(G14:G19)</f>
-        <v>1250</v>
-      </c>
-      <c r="H21" s="38">
-        <f t="shared" ref="H21" si="1">G21*(1-G$24/100)</f>
-        <v>925</v>
-      </c>
-      <c r="I21" s="39">
-        <f>G21*(G$24/100)</f>
-        <v>325</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D22" s="31">
-        <v>868</v>
-      </c>
-      <c r="E22" s="33">
-        <f>SUM(E15:E19)</f>
-        <v>730.34333333333336</v>
-      </c>
-      <c r="F22" s="34">
-        <f>SUM(F15:F19)</f>
-        <v>130.65666666666669</v>
-      </c>
-      <c r="G22" s="4">
-        <v>994</v>
-      </c>
-      <c r="H22" s="33">
-        <f>SUM(H15:H19)</f>
-        <v>678.33333333333337</v>
-      </c>
-      <c r="I22" s="34">
-        <f>SUM(I15:I19)</f>
+        <f>SUM(I11:I15)</f>
         <v>201.66666666666669</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="31"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="48">
-        <f t="shared" ref="D23:I23" si="2">D22/D21</f>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="31"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="47">
+        <f t="shared" ref="D19:I19" si="2">D18/D17</f>
         <v>0.57369464639788503</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E19" s="40">
         <f t="shared" si="2"/>
         <v>0.62689876767867514</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F19" s="41">
         <f t="shared" si="2"/>
         <v>0.37546098067952149</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G19" s="40">
         <f t="shared" si="2"/>
         <v>0.79520000000000002</v>
       </c>
-      <c r="H23" s="40">
+      <c r="H19" s="40">
         <f t="shared" si="2"/>
         <v>0.73333333333333339</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I19" s="41">
         <f t="shared" si="2"/>
         <v>0.62051282051282053</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="C24" s="46" t="s">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D20" s="42">
         <v>23</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="14">
+      <c r="E20" s="14"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="14">
         <v>26</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="43"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="27"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="31" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="43"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="71" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="79"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="81" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="82" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="D27" s="4">
+      <c r="C24" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D24" s="72">
         <v>0</v>
       </c>
-      <c r="E27" s="44">
-        <f>(E14+H14)/(D12+G12)</f>
+      <c r="E24" s="73">
+        <f>(E10+H10)/(D8+G8)</f>
         <v>3.5302245250431775E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="31" t="s">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="C25" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="72">
         <v>0</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E25" s="74">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="31" t="s">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="C29" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="D29" s="35">
-        <f>SUM(E15:E17,E19,H15:H17,H19)/2</f>
+      <c r="C26" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="75">
+        <f>SUM(E11:E13,E15,H11:H13,H15)/2</f>
         <v>308.33833333333342</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E26" s="74">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="31" t="s">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="C30" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="D30" s="4">
+      <c r="C27" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="72">
         <v>0</v>
       </c>
-      <c r="E30" s="44">
-        <f>(E18+H18)/(D12+G12)</f>
+      <c r="E27" s="73">
+        <f>(E14+H14)/(D8+G8)</f>
         <v>4.1036269430051814E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="31"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="32"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="31" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="64"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="74"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="C32" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D32" s="35">
-        <f>SUM(F14,I14)/2</f>
+      <c r="C29" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D29" s="75">
+        <f>SUM(F10,I10)/2</f>
         <v>170.33333333333331</v>
       </c>
-      <c r="E32" s="32">
+      <c r="E29" s="74">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="31" t="s">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="C33" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D33" s="4">
+      <c r="C30" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" s="72">
         <v>0</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E30" s="74">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="31" t="s">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="C34" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D34" s="35">
-        <f>SUM(F15:F17,F19,I15:I17,I19)</f>
+      <c r="C31" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="75">
+        <f>SUM(F11:F13,F15,I11:I13,I15)</f>
         <v>332.32333333333338</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E31" s="74">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D35" s="14">
+      <c r="C32" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" s="76">
         <v>0</v>
       </c>
-      <c r="E35" s="43">
+      <c r="E32" s="77">
         <v>0</v>
       </c>
     </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B34" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="54"/>
+      <c r="N34" s="54"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="54"/>
+      <c r="Q34" s="54"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J35" s="51" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J36" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="N36" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="O36" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="P36" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="59" t="s">
+        <v>305</v>
+      </c>
+      <c r="N37" s="59" t="s">
+        <v>306</v>
+      </c>
+      <c r="O37" s="59" t="s">
+        <v>307</v>
+      </c>
+      <c r="P37" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B38" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="J38" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4">
+        <v>90</v>
+      </c>
+      <c r="N38" s="4">
+        <v>13</v>
+      </c>
+      <c r="O38" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="P38" s="32">
+        <v>242</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>318</v>
+      </c>
+      <c r="R38" s="58"/>
+      <c r="S38" s="58"/>
+    </row>
+    <row r="39" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4">
+        <v>50</v>
+      </c>
+      <c r="E39" s="32">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4">
+        <v>654</v>
+      </c>
+      <c r="N39" s="4">
+        <v>80</v>
+      </c>
+      <c r="O39" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="P39" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>318</v>
+      </c>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B40" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="E40" s="32">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J40" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4">
+        <v>11</v>
+      </c>
+      <c r="N40" s="4">
+        <v>12</v>
+      </c>
+      <c r="O40" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P40" s="32">
+        <v>43.2</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>318</v>
+      </c>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B41" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="E41" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="J41" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4">
+        <v>244</v>
+      </c>
+      <c r="N41" s="4">
+        <v>78</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="P41" s="32">
+        <v>340</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>318</v>
+      </c>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B42" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="E42" s="32">
+        <v>0.04</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4">
+        <v>992</v>
+      </c>
+      <c r="N42" s="4">
+        <v>93</v>
+      </c>
+      <c r="O42" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="P42" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>318</v>
+      </c>
+      <c r="R42" s="58"/>
+      <c r="S42" s="58"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B43" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="43">
+        <v>0.02</v>
+      </c>
+      <c r="J43" s="31"/>
+      <c r="M43" s="58">
+        <f>M42/M49</f>
+        <v>0.40772708590217838</v>
+      </c>
+      <c r="N43" s="58">
+        <f t="shared" ref="N43:O43" si="3">N42/N49</f>
+        <v>0.13497822931785197</v>
+      </c>
+      <c r="O43" s="58">
+        <f t="shared" si="3"/>
+        <v>0.21319796954314724</v>
+      </c>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="92">
+        <f>AVERAGE(M43:O43)</f>
+        <v>0.25196776158772582</v>
+      </c>
+      <c r="R43" s="58"/>
+      <c r="S43" s="58"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C44" s="68" t="s">
+        <v>322</v>
+      </c>
+      <c r="D44" s="69">
+        <f>D39*33+E39*26</f>
+        <v>1660.4</v>
+      </c>
+      <c r="E44" s="70" t="s">
+        <v>323</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="N44" s="4">
+        <v>4</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="P44" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>318</v>
+      </c>
+      <c r="R44" s="58"/>
+      <c r="S44" s="58"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J45" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4">
+        <v>79</v>
+      </c>
+      <c r="N45" s="4">
+        <v>7</v>
+      </c>
+      <c r="O45" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="P45" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>318</v>
+      </c>
+      <c r="R45" s="58"/>
+      <c r="S45" s="58"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B46" s="71" t="s">
+        <v>326</v>
+      </c>
+      <c r="J46" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="N46" s="4">
+        <v>11</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="P46" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>318</v>
+      </c>
+      <c r="R46" s="58"/>
+      <c r="S46" s="58"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B47" s="27"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="86" t="s">
+        <v>328</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="30"/>
+      <c r="J47" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4">
+        <v>38</v>
+      </c>
+      <c r="N47" s="4">
+        <v>15</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="P47" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>318</v>
+      </c>
+      <c r="R47" s="58"/>
+      <c r="S47" s="58"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B48" s="42"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="87" t="s">
+        <v>329</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="G48" s="83" t="s">
+        <v>155</v>
+      </c>
+      <c r="H48" s="84" t="s">
+        <v>150</v>
+      </c>
+      <c r="J48" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4">
+        <v>164</v>
+      </c>
+      <c r="N48" s="4">
+        <v>66</v>
+      </c>
+      <c r="O48" s="4">
+        <v>1</v>
+      </c>
+      <c r="P48" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>318</v>
+      </c>
+      <c r="R48" s="58"/>
+      <c r="S48" s="58"/>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B49" s="85" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="D49" s="88">
+        <f>D42</f>
+        <v>3.5</v>
+      </c>
+      <c r="E49" s="75">
+        <v>100</v>
+      </c>
+      <c r="F49" s="75">
+        <v>0</v>
+      </c>
+      <c r="G49" s="75">
+        <v>0</v>
+      </c>
+      <c r="H49" s="78">
+        <v>0</v>
+      </c>
+      <c r="J49" s="46" t="s">
+        <v>284</v>
+      </c>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29">
+        <v>2433</v>
+      </c>
+      <c r="N49" s="29">
+        <v>689</v>
+      </c>
+      <c r="O49" s="29">
+        <v>19.7</v>
+      </c>
+      <c r="P49" s="50">
+        <v>1252</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>318</v>
+      </c>
+      <c r="R49" s="58"/>
+      <c r="S49" s="58"/>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B50" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D50" s="88">
+        <f>D39*0.25</f>
+        <v>12.5</v>
+      </c>
+      <c r="E50" s="75">
+        <v>0</v>
+      </c>
+      <c r="F50" s="75">
+        <f>D43/D50*100</f>
+        <v>4</v>
+      </c>
+      <c r="G50" s="75">
+        <f>D41/D50*100</f>
+        <v>76</v>
+      </c>
+      <c r="H50" s="78">
+        <f>(D40-D51)/D50*100</f>
+        <v>20</v>
+      </c>
+      <c r="J50" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4">
+        <v>1441</v>
+      </c>
+      <c r="N50" s="4">
+        <v>689</v>
+      </c>
+      <c r="O50" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="P50" s="32">
+        <v>1218</v>
+      </c>
+      <c r="R50" s="58"/>
+      <c r="S50" s="58"/>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B51" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D51" s="89">
+        <f>D39-D49-D50</f>
+        <v>34</v>
+      </c>
+      <c r="E51" s="72">
+        <v>0</v>
+      </c>
+      <c r="F51" s="72">
+        <v>0</v>
+      </c>
+      <c r="G51" s="72">
+        <v>0</v>
+      </c>
+      <c r="H51" s="74">
+        <v>100</v>
+      </c>
+      <c r="J51" s="61" t="s">
+        <v>320</v>
+      </c>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="63">
+        <f>M49-M50</f>
+        <v>992</v>
+      </c>
+      <c r="N51" s="63">
+        <f>N49-N50</f>
+        <v>0</v>
+      </c>
+      <c r="O51" s="63">
+        <f>O49-O50</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="P51" s="62">
+        <f>P49-P50</f>
+        <v>34</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>318</v>
+      </c>
+      <c r="R51" s="58"/>
+      <c r="S51" s="58"/>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B52" s="31"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="88"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="72"/>
+      <c r="H52" s="74"/>
+      <c r="J52" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="K52" s="56"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="56">
+        <v>23</v>
+      </c>
+      <c r="N52" s="56">
+        <v>38</v>
+      </c>
+      <c r="O52" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="P52" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B53" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D53" s="88">
+        <f>E42</f>
+        <v>0.04</v>
+      </c>
+      <c r="E53" s="75">
+        <v>100</v>
+      </c>
+      <c r="F53" s="75">
+        <v>0</v>
+      </c>
+      <c r="G53" s="75">
+        <v>0</v>
+      </c>
+      <c r="H53" s="78">
+        <v>0</v>
+      </c>
+      <c r="J53" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="P53" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B54" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D54" s="90">
+        <f>E39*0.25</f>
+        <v>0.1</v>
+      </c>
+      <c r="E54" s="75">
+        <v>0</v>
+      </c>
+      <c r="F54" s="75">
+        <f>E43/D54*100</f>
+        <v>20</v>
+      </c>
+      <c r="G54" s="75">
+        <f>E41/D54*100</f>
+        <v>60</v>
+      </c>
+      <c r="H54" s="78">
+        <f>(E40-D55)/D54*100</f>
+        <v>20.000000000000018</v>
+      </c>
+      <c r="J54" s="31" t="s">
+        <v>314</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="P54" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B55" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D55" s="91">
+        <f>E39-D53-D54</f>
+        <v>0.26</v>
+      </c>
+      <c r="E55" s="76">
+        <v>0</v>
+      </c>
+      <c r="F55" s="76">
+        <v>0</v>
+      </c>
+      <c r="G55" s="76">
+        <v>0</v>
+      </c>
+      <c r="H55" s="77">
+        <v>100</v>
+      </c>
+      <c r="J55" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="P55" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J56" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14">
+        <v>1998</v>
+      </c>
+      <c r="N56" s="14">
+        <v>1999</v>
+      </c>
+      <c r="O56" s="14">
+        <v>1998</v>
+      </c>
+      <c r="P56" s="43">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
+      <c r="N58" s="52"/>
+      <c r="O58" s="52"/>
+      <c r="P58" s="52"/>
+      <c r="Q58" s="52"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:I5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="E3:T17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="36.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3">
+        <v>13</v>
+      </c>
+      <c r="H3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F4">
+        <v>654</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>269</v>
+      </c>
+      <c r="I5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F6" t="s">
+        <v>299</v>
+      </c>
+      <c r="G6" t="s">
+        <v>300</v>
+      </c>
+      <c r="H6" t="s">
+        <v>301</v>
+      </c>
+      <c r="I6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I7" t="s">
+        <v>272</v>
+      </c>
+      <c r="O7" t="s">
+        <v>273</v>
+      </c>
+      <c r="S7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>274</v>
+      </c>
+      <c r="H8" t="s">
+        <v>275</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="P8" t="s">
+        <v>276</v>
+      </c>
+      <c r="T8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>278</v>
+      </c>
+      <c r="H9">
+        <v>79</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="P9" t="s">
+        <v>279</v>
+      </c>
+      <c r="T9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10">
+        <v>11</v>
+      </c>
+      <c r="P10" t="s">
+        <v>87</v>
+      </c>
+      <c r="T10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11">
+        <v>38</v>
+      </c>
+      <c r="K11">
+        <v>15</v>
+      </c>
+      <c r="P11" t="s">
+        <v>282</v>
+      </c>
+      <c r="T11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>263</v>
+      </c>
+      <c r="H12">
+        <v>164</v>
+      </c>
+      <c r="K12">
+        <v>66</v>
+      </c>
+      <c r="P12" t="s">
+        <v>283</v>
+      </c>
+      <c r="T12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>284</v>
+      </c>
+      <c r="H13">
+        <v>2433</v>
+      </c>
+      <c r="K13">
+        <v>689</v>
+      </c>
+      <c r="P13" t="s">
+        <v>285</v>
+      </c>
+      <c r="T13">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="14" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>286</v>
+      </c>
+      <c r="H14">
+        <v>1441</v>
+      </c>
+      <c r="K14">
+        <v>689</v>
+      </c>
+      <c r="P14" t="s">
+        <v>287</v>
+      </c>
+      <c r="T14">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="15" spans="5:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>288</v>
+      </c>
+      <c r="L15" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="5:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>291</v>
+      </c>
+      <c r="H16" t="s">
+        <v>292</v>
+      </c>
+      <c r="K16" t="s">
+        <v>292</v>
+      </c>
+      <c r="P16" t="s">
+        <v>87</v>
+      </c>
+      <c r="T16" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="5:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H17" t="s">
+        <v>294</v>
+      </c>
+      <c r="K17" t="s">
+        <v>295</v>
+      </c>
+      <c r="P17" t="s">
+        <v>296</v>
+      </c>
+      <c r="T17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:J21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>309</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>311</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="J3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H4" t="s">
+        <v>307</v>
+      </c>
+      <c r="I4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5">
+        <v>90</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I5">
+        <v>242</v>
+      </c>
+      <c r="J5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6">
+        <v>654</v>
+      </c>
+      <c r="G6">
+        <v>80</v>
+      </c>
+      <c r="H6">
+        <v>9.6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>267</v>
+      </c>
+      <c r="J6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>0.1</v>
+      </c>
+      <c r="I7">
+        <v>43.2</v>
+      </c>
+      <c r="J7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8">
+        <v>244</v>
+      </c>
+      <c r="G8">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>1.8</v>
+      </c>
+      <c r="I8">
+        <v>340</v>
+      </c>
+      <c r="J8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9">
+        <v>992</v>
+      </c>
+      <c r="G9">
+        <v>93</v>
+      </c>
+      <c r="H9">
+        <v>4.2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>262</v>
+      </c>
+      <c r="J9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I10" t="s">
+        <v>277</v>
+      </c>
+      <c r="J10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11">
+        <v>79</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11">
+        <v>0.7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>267</v>
+      </c>
+      <c r="J11" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
+        <v>267</v>
+      </c>
+      <c r="J12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>281</v>
+      </c>
+      <c r="F13">
+        <v>38</v>
+      </c>
+      <c r="G13">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>282</v>
+      </c>
+      <c r="I13" t="s">
+        <v>267</v>
+      </c>
+      <c r="J13" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>263</v>
+      </c>
+      <c r="F14">
+        <v>164</v>
+      </c>
+      <c r="G14">
+        <v>66</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>267</v>
+      </c>
+      <c r="J14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F15">
+        <v>2433</v>
+      </c>
+      <c r="G15">
+        <v>689</v>
+      </c>
+      <c r="H15">
+        <v>19.7</v>
+      </c>
+      <c r="I15">
+        <v>1252</v>
+      </c>
+      <c r="J15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>286</v>
+      </c>
+      <c r="F16">
+        <v>1441</v>
+      </c>
+      <c r="G16">
+        <v>689</v>
+      </c>
+      <c r="H16">
+        <v>15.5</v>
+      </c>
+      <c r="I16">
+        <v>1218</v>
+      </c>
+      <c r="J16" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>303</v>
+      </c>
+      <c r="F17">
+        <v>23</v>
+      </c>
+      <c r="G17">
+        <v>38</v>
+      </c>
+      <c r="H17" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s">
+        <v>313</v>
+      </c>
+      <c r="J17" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>291</v>
+      </c>
+      <c r="F18" t="s">
+        <v>292</v>
+      </c>
+      <c r="G18" t="s">
+        <v>292</v>
+      </c>
+      <c r="H18" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" t="s">
+        <v>292</v>
+      </c>
+      <c r="J18" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F19" t="s">
+        <v>292</v>
+      </c>
+      <c r="G19" t="s">
+        <v>317</v>
+      </c>
+      <c r="H19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" t="s">
+        <v>292</v>
+      </c>
+      <c r="J19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>315</v>
+      </c>
+      <c r="F20" t="s">
+        <v>292</v>
+      </c>
+      <c r="H20" t="s">
+        <v>292</v>
+      </c>
+      <c r="I20" t="s">
+        <v>292</v>
+      </c>
+      <c r="J20" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F21">
+        <v>1998</v>
+      </c>
+      <c r="G21">
+        <v>1999</v>
+      </c>
+      <c r="H21">
+        <v>1998</v>
+      </c>
+      <c r="I21">
+        <v>2008</v>
+      </c>
+      <c r="J21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -4769,8 +7699,13 @@
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
-        <v>242</v>
+      <c r="A11" s="48" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="48" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
